--- a/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
+++ b/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
@@ -4,21 +4,25 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="总体描述" sheetId="1" r:id="rId1"/>
     <sheet name="故障点分析" sheetId="2" r:id="rId2"/>
     <sheet name="用例正交表" sheetId="3" r:id="rId3"/>
-    <sheet name="工具需求" sheetId="4" r:id="rId4"/>
+    <sheet name="详细用例" sheetId="5" r:id="rId4"/>
+    <sheet name="工具需求" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">详细用例!$A$3:$G$3</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="213">
   <si>
     <t>测试功能点：查询、插入、更新、分区</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -212,10 +216,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>系统异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>系统掉电</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -276,11 +276,474 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁盘坏道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络错包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网卡故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统掉电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两台机器之间的网络</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障三台机器之间的网络</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障一台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障三台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预期结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实测结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行步骤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前置条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例编号规则见用例正交表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例编号规则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_AAA_BBB_CCC_DDD：AAA取并发任务序号，BBB取故障场景序号，CCC取业务场景序号,DDD在前三个基础上的细分场景.如sequoiadb_fault_001_001_001_001则为3个insert，不做split，使用kill -15故障一个主节点的场景。还要考虑故障交叉组合的场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群正常，已经split完成，3个并发插入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行1之后操作会报失败，并且在执行步骤2之前会恢复正常，之后一直正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有步骤2之后才能恢复正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一直正常</t>
+  </si>
+  <si>
+    <t>一直正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 主节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 两个主节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 三个主节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 一个备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 同一组内的两个备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 两个不同组的备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 三个不同组的备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ycsb查询、插入、更新有没有超时，超时时间多久？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一直正常(可能有超时)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_014_010_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，重启一台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.重启一台机器; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重启之后恢复正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_014_011_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_014_012_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，重启两台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，重启三台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.重启两台机器; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.重启三台机器; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优先级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 同一组内的两个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 两个不同组的备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 三个不同组的备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作会报失败，自动恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一直正常，且节点自动恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，一个主节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，两个主节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，三个主节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，一个备节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，两个备节点磁盘满（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，两个备节点磁盘满（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，三个备节点磁盘满（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.两个主节点磁盘满; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.三个主节点磁盘满; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.一个备节点磁盘满; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.两个备节点磁盘满（同一组）; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.两个备节点磁盘满（不同组）; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.三个备节点磁盘满（不同组）; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_002_001_001 kill -11待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>慢盘</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>umount</t>
+    <t>sequoiadb_fault_001_005_001_001 慢盘待补</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -288,87 +751,127 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>磁盘坏道</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络拥塞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络丢包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络错包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网卡故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统掉电</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障一个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障一个备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障三个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两个备节点（同一组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障三个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两台机器之间的网络</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障三台机器之间的网络</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障一台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障三台机器</t>
+    <t>sequoiadb_fault_001_006_001_001 umount待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉一个主节点所在的磁盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉两个主节点所在的磁盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉三个主节点所在的磁盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉一个备节点所在的磁盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉两个备节点所在的磁盘（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉两个备节点所在的磁盘（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉三个备节点所在的磁盘（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.一个主节点磁盘满（往磁盘上灌数据，同时可以看做是慢盘了）; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉一个主节点所在的磁盘; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉两个主节点所在的磁盘; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉三个主节点所在的磁盘; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉一个备节点所在的磁盘; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉两个备节点所在的磁盘（同一组）; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉两个备节点所在的磁盘（不同组）; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉三个备节点所在的磁盘（不同组）; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行1之后操作会报失败，并且在执行步骤2之前会恢复正常，之后一直正常？？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有步骤2之后才能恢复正常？？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_008_001_001磁盘坏道待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_009_008_001网络拥塞待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_010_008_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，造成两台机器之间丢包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.注入网络丢包; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试环境:192.168.20.169/170/171 root:sequoiadb</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -376,7 +879,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,6 +937,21 @@
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -575,13 +1093,25 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -589,13 +1119,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="2" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -607,11 +1130,38 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1291,10 +1841,10 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -1308,8 +1858,8 @@
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
@@ -1317,8 +1867,8 @@
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
@@ -1326,8 +1876,8 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="7"/>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="15"/>
+      <c r="B5" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -1341,8 +1891,8 @@
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
       <c r="C6" s="5" t="s">
         <v>39</v>
       </c>
@@ -1354,8 +1904,8 @@
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -1363,7 +1913,7 @@
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="7"/>
+      <c r="A8" s="15"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1372,7 +1922,7 @@
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="8"/>
+      <c r="A9" s="16"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1381,10 +1931,10 @@
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -1398,8 +1948,8 @@
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -1407,8 +1957,8 @@
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="7"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -1416,8 +1966,8 @@
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="7"/>
-      <c r="B13" s="6" t="s">
+      <c r="A13" s="15"/>
+      <c r="B13" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -1431,12 +1981,12 @@
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
       <c r="C14" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E14" s="5"/>
@@ -1444,8 +1994,8 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -1453,8 +2003,8 @@
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="7"/>
-      <c r="B16" s="8"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="16"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -1462,14 +2012,14 @@
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="7"/>
-      <c r="B17" s="6" t="s">
+      <c r="A17" s="15"/>
+      <c r="B17" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="6" t="s">
         <v>32</v>
       </c>
       <c r="E17" s="5"/>
@@ -1477,12 +2027,12 @@
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
       <c r="C18" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="8" t="s">
         <v>33</v>
       </c>
       <c r="E18" s="5"/>
@@ -1490,8 +2040,8 @@
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -1499,8 +2049,8 @@
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -1508,10 +2058,10 @@
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="5" t="s">
@@ -1525,8 +2075,8 @@
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
       <c r="C22" s="5" t="s">
         <v>44</v>
       </c>
@@ -1538,8 +2088,8 @@
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
       <c r="C23" s="5" t="s">
         <v>45</v>
       </c>
@@ -1551,8 +2101,8 @@
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -1560,8 +2110,8 @@
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="7"/>
-      <c r="B25" s="8"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="16"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -1569,8 +2119,8 @@
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="7"/>
-      <c r="B26" s="6" t="s">
+      <c r="A26" s="15"/>
+      <c r="B26" s="14" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="5" t="s">
@@ -1584,8 +2134,8 @@
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
       <c r="C27" s="5" t="s">
         <v>47</v>
       </c>
@@ -1597,8 +2147,8 @@
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -1606,12 +2156,12 @@
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>37</v>
@@ -1621,10 +2171,10 @@
       <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="7"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>37</v>
@@ -1634,7 +2184,7 @@
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="7"/>
+      <c r="A31" s="15"/>
       <c r="B31" s="3"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -1643,7 +2193,7 @@
       <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="8"/>
+      <c r="A32" s="16"/>
       <c r="B32" s="3"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -1673,49 +2223,50 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="3" width="9" style="12"/>
-    <col min="4" max="4" width="10" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.375" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9" style="12"/>
-    <col min="8" max="8" width="4.75" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.375" style="12" customWidth="1"/>
-    <col min="10" max="10" width="10.375" style="12" customWidth="1"/>
-    <col min="11" max="11" width="4.75" style="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.25" style="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="12"/>
+    <col min="1" max="1" width="11.375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9" style="9"/>
+    <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.375" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9" style="9"/>
+    <col min="8" max="8" width="4.75" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.375" style="9" customWidth="1"/>
+    <col min="10" max="10" width="10.375" style="9" customWidth="1"/>
+    <col min="11" max="11" width="4.75" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="10" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="13" t="s">
+      <c r="B3" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="C3" s="18"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17" t="s">
+      <c r="H3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="K3" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1723,28 +2274,28 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="H4" s="3">
         <v>1</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K4" s="3">
         <v>1</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1752,28 +2303,28 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="H5" s="3">
         <v>2</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K5" s="3">
         <v>2</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1781,28 +2332,28 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>56</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>57</v>
       </c>
       <c r="H6" s="3">
         <v>3</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K6" s="3">
         <v>3</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1810,28 +2361,28 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="H7" s="3">
         <v>4</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K7" s="3">
         <v>4</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1839,28 +2390,28 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H8" s="3">
         <v>5</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>64</v>
+        <v>179</v>
       </c>
       <c r="K8" s="3">
         <v>5</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1868,28 +2419,28 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H9" s="3">
         <v>6</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K9" s="3">
         <v>6</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1897,28 +2448,28 @@
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H10" s="3">
         <v>7</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>66</v>
+        <v>181</v>
       </c>
       <c r="K10" s="3">
         <v>7</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1926,200 +2477,200 @@
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H11" s="3">
         <v>8</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>68</v>
+      <c r="B12" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="3">
         <v>10</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="19" t="s">
+      <c r="B13" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>68</v>
+      <c r="E13" s="13" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="3">
         <v>11</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>68</v>
+      <c r="B14" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="H14" s="3">
         <v>9</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K14" s="3">
         <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="3">
         <v>12</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>68</v>
+      <c r="B15" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="H15" s="3">
         <v>10</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="K15" s="3">
         <v>9</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="3">
         <v>13</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="19" t="s">
+      <c r="B16" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>68</v>
+      <c r="C16" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="H16" s="3">
         <v>11</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="3">
         <v>14</v>
       </c>
-      <c r="B17" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="19" t="s">
+      <c r="B17" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="19" t="s">
-        <v>68</v>
+      <c r="C17" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="H17" s="3">
         <v>12</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="3">
         <v>15</v>
       </c>
-      <c r="B18" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>68</v>
+      <c r="B18" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="H18" s="3">
         <v>13</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="3">
         <v>16</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>68</v>
+      <c r="B19" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -2139,13 +2690,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="K21" s="3">
         <v>10</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -2153,13 +2704,13 @@
         <v>15</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="K22" s="3">
         <v>11</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2167,7 +2718,15 @@
         <v>12</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2182,45 +2741,1119 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:G63"/>
+  <sheetFormatPr defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="27.875" style="9" customWidth="1"/>
+    <col min="2" max="2" width="6.125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="25.75" style="23" customWidth="1"/>
+    <col min="4" max="4" width="26" style="23" customWidth="1"/>
+    <col min="5" max="5" width="40.625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="30" style="23" customWidth="1"/>
+    <col min="7" max="7" width="23.625" style="9" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="29" customFormat="1" ht="24">
+      <c r="A4" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="27"/>
+      <c r="C4" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="G4" s="27"/>
+    </row>
+    <row r="5" spans="1:7" s="29" customFormat="1" ht="24">
+      <c r="A5" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="27"/>
+      <c r="C5" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="G5" s="27"/>
+    </row>
+    <row r="6" spans="1:7" s="29" customFormat="1" ht="24">
+      <c r="A6" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="27"/>
+      <c r="C6" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="G6" s="27"/>
+    </row>
+    <row r="7" spans="1:7" s="29" customFormat="1" ht="24">
+      <c r="A7" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="27"/>
+      <c r="C7" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="27"/>
+    </row>
+    <row r="8" spans="1:7" ht="24">
+      <c r="A8" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="27"/>
+      <c r="C8" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:7" ht="24">
+      <c r="A9" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="27"/>
+      <c r="C9" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:7" ht="24">
+      <c r="A10" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="27"/>
+      <c r="C10" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:7" ht="24">
+      <c r="A11" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="25"/>
+    </row>
+    <row r="12" spans="1:7" ht="24">
+      <c r="A12" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" s="27"/>
+      <c r="C12" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="G12" s="27"/>
+    </row>
+    <row r="13" spans="1:7" ht="24">
+      <c r="A13" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13" s="27"/>
+      <c r="C13" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="G13" s="27"/>
+    </row>
+    <row r="14" spans="1:7" ht="24">
+      <c r="A14" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" s="27"/>
+      <c r="C14" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="G14" s="27"/>
+    </row>
+    <row r="15" spans="1:7" ht="24">
+      <c r="A15" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="B15" s="27"/>
+      <c r="C15" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="G15" s="27"/>
+    </row>
+    <row r="16" spans="1:7" ht="24">
+      <c r="A16" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B16" s="27"/>
+      <c r="C16" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="G16" s="27"/>
+    </row>
+    <row r="17" spans="1:7" ht="24">
+      <c r="A17" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="B17" s="27"/>
+      <c r="C17" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="G17" s="27"/>
+    </row>
+    <row r="18" spans="1:7" ht="24">
+      <c r="A18" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" s="27"/>
+      <c r="C18" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="G18" s="27"/>
+    </row>
+    <row r="19" spans="1:7" ht="24">
+      <c r="A19" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="B19" s="25"/>
+      <c r="C19" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="25"/>
+    </row>
+    <row r="20" spans="1:7" ht="24">
+      <c r="A20" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="B20" s="25"/>
+      <c r="C20" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="25"/>
+    </row>
+    <row r="21" spans="1:7" ht="24">
+      <c r="A21" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="B21" s="25"/>
+      <c r="C21" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G21" s="25"/>
+    </row>
+    <row r="22" spans="1:7" ht="24">
+      <c r="A22" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="B22" s="25"/>
+      <c r="C22" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G22" s="25"/>
+    </row>
+    <row r="23" spans="1:7" ht="24">
+      <c r="A23" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="B23" s="25"/>
+      <c r="C23" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23" s="25"/>
+    </row>
+    <row r="24" spans="1:7" ht="24">
+      <c r="A24" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="B24" s="25"/>
+      <c r="C24" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="25"/>
+    </row>
+    <row r="25" spans="1:7" ht="24">
+      <c r="A25" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" s="25"/>
+      <c r="C25" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G25" s="25"/>
+    </row>
+    <row r="26" spans="1:7" ht="24">
+      <c r="A26" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="B26" s="20"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="20"/>
+    </row>
+    <row r="27" spans="1:7" ht="24">
+      <c r="A27" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="B27" s="20"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="20"/>
+    </row>
+    <row r="28" spans="1:7" ht="24">
+      <c r="A28" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" s="25"/>
+      <c r="C28" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="G28" s="25"/>
+    </row>
+    <row r="29" spans="1:7" ht="24">
+      <c r="A29" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" s="25"/>
+      <c r="C29" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="G29" s="25"/>
+    </row>
+    <row r="30" spans="1:7" ht="24">
+      <c r="A30" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="B30" s="25"/>
+      <c r="C30" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="G30" s="25"/>
+    </row>
+    <row r="31" spans="1:7" ht="24">
+      <c r="A31" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="B31" s="25"/>
+      <c r="C31" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="F31" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="G31" s="25"/>
+    </row>
+    <row r="32" spans="1:7" ht="24">
+      <c r="A32" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="B32" s="25"/>
+      <c r="C32" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="F32" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="G32" s="25"/>
+    </row>
+    <row r="33" spans="1:7" ht="24">
+      <c r="A33" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="B33" s="25"/>
+      <c r="C33" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="F33" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="G33" s="25"/>
+    </row>
+    <row r="34" spans="1:7" ht="24">
+      <c r="A34" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="B34" s="25"/>
+      <c r="C34" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="F34" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="G34" s="25"/>
+    </row>
+    <row r="35" spans="1:7" ht="24">
+      <c r="A35" s="31" t="s">
+        <v>207</v>
+      </c>
+      <c r="B35" s="20"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="20"/>
+    </row>
+    <row r="36" spans="1:7" ht="24">
+      <c r="A36" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="B36" s="20"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="20"/>
+    </row>
+    <row r="37" spans="1:7" ht="24">
+      <c r="A37" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="B37" s="27"/>
+      <c r="C37" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="F37" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="G37" s="20"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="22"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="20"/>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="22"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="20"/>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="27"/>
+      <c r="B41" s="27"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="20"/>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="20"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="20"/>
+    </row>
+    <row r="43" spans="1:7" ht="24">
+      <c r="A43" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" s="27"/>
+      <c r="C43" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="D43" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="E43" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="F43" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="G43" s="20"/>
+    </row>
+    <row r="44" spans="1:7" ht="24">
+      <c r="A44" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="B44" s="27"/>
+      <c r="C44" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="D44" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="E44" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="F44" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="G44" s="20"/>
+    </row>
+    <row r="45" spans="1:7" ht="24">
+      <c r="A45" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="B45" s="27"/>
+      <c r="C45" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="D45" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="E45" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="F45" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="G45" s="20"/>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="20"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="20"/>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="20"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="20"/>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="20"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="20"/>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="20"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="20"/>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="20"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="20"/>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="20"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="20"/>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="20"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="20"/>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="20"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="20"/>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="20"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="20"/>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="20"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="20"/>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="20"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="20"/>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="20"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="20"/>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="20"/>
+      <c r="B58" s="20"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="20"/>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="20"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="20"/>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="20"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="20"/>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="20"/>
+      <c r="B61" s="20"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="20"/>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="20"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="20"/>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="20"/>
+      <c r="B63" s="20"/>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="20"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:G3"/>
+  <dataConsolidate/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="69.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2">
+      <c r="B1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+      <c r="B5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>212</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="3">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3">
+        <v>7</v>
+      </c>
+      <c r="C7" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="3">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
+++ b/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="216">
   <si>
     <t>测试功能点：查询、插入、更新、分区</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -872,6 +872,18 @@
   </si>
   <si>
     <t>测试环境:192.168.20.169/170/171 root:sequoiadb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谭钊波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ycsb</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1093,7 +1105,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1112,24 +1124,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1162,6 +1156,25 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1841,10 +1854,10 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="28" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -1858,8 +1871,8 @@
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
@@ -1867,8 +1880,8 @@
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="15"/>
-      <c r="B4" s="16"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="30"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
@@ -1876,8 +1889,8 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="15"/>
-      <c r="B5" s="14" t="s">
+      <c r="A5" s="29"/>
+      <c r="B5" s="28" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -1891,8 +1904,8 @@
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
       <c r="C6" s="5" t="s">
         <v>39</v>
       </c>
@@ -1904,8 +1917,8 @@
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="30"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -1913,7 +1926,7 @@
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="15"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1922,7 +1935,7 @@
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="16"/>
+      <c r="A9" s="30"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1931,10 +1944,10 @@
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="28" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -1948,8 +1961,8 @@
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="29"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -1957,8 +1970,8 @@
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="15"/>
-      <c r="B12" s="16"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="30"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -1966,8 +1979,8 @@
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="15"/>
-      <c r="B13" s="14" t="s">
+      <c r="A13" s="29"/>
+      <c r="B13" s="28" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -1981,8 +1994,8 @@
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="29"/>
       <c r="C14" s="5" t="s">
         <v>41</v>
       </c>
@@ -1994,8 +2007,8 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
+      <c r="A15" s="29"/>
+      <c r="B15" s="29"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -2003,8 +2016,8 @@
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="15"/>
-      <c r="B16" s="16"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="30"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -2012,8 +2025,8 @@
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="15"/>
-      <c r="B17" s="14" t="s">
+      <c r="A17" s="29"/>
+      <c r="B17" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -2027,8 +2040,8 @@
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="29"/>
       <c r="C18" s="5" t="s">
         <v>14</v>
       </c>
@@ -2040,8 +2053,8 @@
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="29"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -2049,8 +2062,8 @@
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -2058,10 +2071,10 @@
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="28" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="5" t="s">
@@ -2075,8 +2088,8 @@
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
       <c r="C22" s="5" t="s">
         <v>44</v>
       </c>
@@ -2088,8 +2101,8 @@
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="29"/>
       <c r="C23" s="5" t="s">
         <v>45</v>
       </c>
@@ -2101,8 +2114,8 @@
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
+      <c r="A24" s="29"/>
+      <c r="B24" s="29"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -2110,8 +2123,8 @@
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="15"/>
-      <c r="B25" s="16"/>
+      <c r="A25" s="29"/>
+      <c r="B25" s="30"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -2119,8 +2132,8 @@
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="15"/>
-      <c r="B26" s="14" t="s">
+      <c r="A26" s="29"/>
+      <c r="B26" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="5" t="s">
@@ -2134,8 +2147,8 @@
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15"/>
+      <c r="A27" s="29"/>
+      <c r="B27" s="29"/>
       <c r="C27" s="5" t="s">
         <v>47</v>
       </c>
@@ -2147,8 +2160,8 @@
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="30"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -2156,7 +2169,7 @@
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="28" t="s">
         <v>19</v>
       </c>
       <c r="B29" s="5"/>
@@ -2171,7 +2184,7 @@
       <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="15"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
         <v>48</v>
@@ -2184,7 +2197,7 @@
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="15"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="3"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -2193,7 +2206,7 @@
       <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="16"/>
+      <c r="A32" s="30"/>
       <c r="B32" s="3"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -2248,11 +2261,11 @@
       <c r="A3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="19"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="33"/>
       <c r="E3" s="11" t="s">
         <v>52</v>
       </c>
@@ -2725,7 +2738,7 @@
       <c r="A29" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B29" s="24" t="s">
+      <c r="B29" s="18" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2746,10 +2759,10 @@
   <cols>
     <col min="1" max="1" width="27.875" style="9" customWidth="1"/>
     <col min="2" max="2" width="6.125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="25.75" style="23" customWidth="1"/>
-    <col min="4" max="4" width="26" style="23" customWidth="1"/>
-    <col min="5" max="5" width="40.625" style="23" customWidth="1"/>
-    <col min="6" max="6" width="30" style="23" customWidth="1"/>
+    <col min="3" max="3" width="25.75" style="17" customWidth="1"/>
+    <col min="4" max="4" width="26" style="17" customWidth="1"/>
+    <col min="5" max="5" width="40.625" style="17" customWidth="1"/>
+    <col min="6" max="6" width="30" style="17" customWidth="1"/>
     <col min="7" max="7" width="23.625" style="9" customWidth="1"/>
     <col min="8" max="16384" width="9" style="9"/>
   </cols>
@@ -2766,645 +2779,645 @@
       <c r="B3" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="15" t="s">
         <v>84</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="29" customFormat="1" ht="24">
-      <c r="A4" s="27" t="s">
+    <row r="4" spans="1:7" s="23" customFormat="1" ht="24">
+      <c r="A4" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="28" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="G4" s="27"/>
-    </row>
-    <row r="5" spans="1:7" s="29" customFormat="1" ht="24">
-      <c r="A5" s="27" t="s">
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="1:7" s="23" customFormat="1" ht="24">
+      <c r="A5" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="28" t="s">
+      <c r="B5" s="21"/>
+      <c r="C5" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="G5" s="27"/>
-    </row>
-    <row r="6" spans="1:7" s="29" customFormat="1" ht="24">
-      <c r="A6" s="27" t="s">
+      <c r="G5" s="21"/>
+    </row>
+    <row r="6" spans="1:7" s="23" customFormat="1" ht="24">
+      <c r="A6" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="28" t="s">
+      <c r="B6" s="21"/>
+      <c r="C6" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="G6" s="27"/>
-    </row>
-    <row r="7" spans="1:7" s="29" customFormat="1" ht="24">
-      <c r="A7" s="27" t="s">
+      <c r="G6" s="21"/>
+    </row>
+    <row r="7" spans="1:7" s="23" customFormat="1" ht="24">
+      <c r="A7" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="28" t="s">
+      <c r="B7" s="21"/>
+      <c r="C7" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="21"/>
     </row>
     <row r="8" spans="1:7" ht="24">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="22" t="s">
+      <c r="B8" s="21"/>
+      <c r="C8" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="G8" s="20"/>
+      <c r="G8" s="14"/>
     </row>
     <row r="9" spans="1:7" ht="24">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="22" t="s">
+      <c r="B9" s="21"/>
+      <c r="C9" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="G9" s="20"/>
+      <c r="G9" s="14"/>
     </row>
     <row r="10" spans="1:7" ht="24">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="B10" s="27"/>
-      <c r="C10" s="22" t="s">
+      <c r="B10" s="21"/>
+      <c r="C10" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="G10" s="20"/>
+      <c r="G10" s="14"/>
     </row>
     <row r="11" spans="1:7" ht="24">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="25"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="19"/>
     </row>
     <row r="12" spans="1:7" ht="24">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="28" t="s">
+      <c r="B12" s="21"/>
+      <c r="C12" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="G12" s="27"/>
+      <c r="G12" s="21"/>
     </row>
     <row r="13" spans="1:7" ht="24">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="28" t="s">
+      <c r="B13" s="21"/>
+      <c r="C13" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="G13" s="27"/>
+      <c r="G13" s="21"/>
     </row>
     <row r="14" spans="1:7" ht="24">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="27"/>
-      <c r="C14" s="28" t="s">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E14" s="28" t="s">
+      <c r="E14" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="21"/>
     </row>
     <row r="15" spans="1:7" ht="24">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="28" t="s">
+      <c r="B15" s="21"/>
+      <c r="C15" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="E15" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="F15" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="G15" s="27"/>
+      <c r="G15" s="21"/>
     </row>
     <row r="16" spans="1:7" ht="24">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="28" t="s">
+      <c r="B16" s="21"/>
+      <c r="C16" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E16" s="28" t="s">
+      <c r="E16" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="F16" s="28" t="s">
+      <c r="F16" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="G16" s="27"/>
+      <c r="G16" s="21"/>
     </row>
     <row r="17" spans="1:7" ht="24">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="28" t="s">
+      <c r="B17" s="21"/>
+      <c r="C17" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="F17" s="28" t="s">
+      <c r="F17" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="G17" s="27"/>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" spans="1:7" ht="24">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="28" t="s">
+      <c r="B18" s="21"/>
+      <c r="C18" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E18" s="28" t="s">
+      <c r="E18" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="F18" s="28" t="s">
+      <c r="F18" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="G18" s="27"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" spans="1:7" ht="24">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="26" t="s">
+      <c r="B19" s="19"/>
+      <c r="C19" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="E19" s="26" t="s">
+      <c r="E19" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="F19" s="26" t="s">
+      <c r="F19" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="G19" s="25"/>
+      <c r="G19" s="19"/>
     </row>
     <row r="20" spans="1:7" ht="24">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="26" t="s">
+      <c r="B20" s="19"/>
+      <c r="C20" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="F20" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="G20" s="25"/>
+      <c r="G20" s="19"/>
     </row>
     <row r="21" spans="1:7" ht="24">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="B21" s="25"/>
-      <c r="C21" s="26" t="s">
+      <c r="B21" s="19"/>
+      <c r="C21" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="E21" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="F21" s="26" t="s">
+      <c r="F21" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="G21" s="25"/>
+      <c r="G21" s="19"/>
     </row>
     <row r="22" spans="1:7" ht="24">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="26" t="s">
+      <c r="B22" s="19"/>
+      <c r="C22" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="D22" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E22" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="F22" s="26" t="s">
+      <c r="F22" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="G22" s="25"/>
+      <c r="G22" s="19"/>
     </row>
     <row r="23" spans="1:7" ht="24">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="26" t="s">
+      <c r="B23" s="19"/>
+      <c r="C23" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="D23" s="26" t="s">
+      <c r="D23" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F23" s="26" t="s">
+      <c r="F23" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="G23" s="25"/>
+      <c r="G23" s="19"/>
     </row>
     <row r="24" spans="1:7" ht="24">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="B24" s="25"/>
-      <c r="C24" s="26" t="s">
+      <c r="B24" s="19"/>
+      <c r="C24" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="D24" s="26" t="s">
+      <c r="D24" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="26" t="s">
+      <c r="E24" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="F24" s="26" t="s">
+      <c r="F24" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="G24" s="25"/>
+      <c r="G24" s="19"/>
     </row>
     <row r="25" spans="1:7" ht="24">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="B25" s="25"/>
-      <c r="C25" s="26" t="s">
+      <c r="B25" s="19"/>
+      <c r="C25" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="D25" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="E25" s="26" t="s">
+      <c r="E25" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="G25" s="25"/>
+      <c r="G25" s="19"/>
     </row>
     <row r="26" spans="1:7" ht="24">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="20"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="14"/>
     </row>
     <row r="27" spans="1:7" ht="24">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="B27" s="20"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="20"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="14"/>
     </row>
     <row r="28" spans="1:7" ht="24">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B28" s="25"/>
-      <c r="C28" s="26" t="s">
+      <c r="B28" s="19"/>
+      <c r="C28" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="D28" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="E28" s="26" t="s">
+      <c r="E28" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="F28" s="26" t="s">
+      <c r="F28" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="G28" s="25"/>
+      <c r="G28" s="19"/>
     </row>
     <row r="29" spans="1:7" ht="24">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="B29" s="25"/>
-      <c r="C29" s="26" t="s">
+      <c r="B29" s="19"/>
+      <c r="C29" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="D29" s="26" t="s">
+      <c r="D29" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="E29" s="26" t="s">
+      <c r="E29" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="F29" s="26" t="s">
+      <c r="F29" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="G29" s="25"/>
+      <c r="G29" s="19"/>
     </row>
     <row r="30" spans="1:7" ht="24">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="B30" s="25"/>
-      <c r="C30" s="26" t="s">
+      <c r="B30" s="19"/>
+      <c r="C30" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D30" s="26" t="s">
+      <c r="D30" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="E30" s="26" t="s">
+      <c r="E30" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="F30" s="26" t="s">
+      <c r="F30" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="G30" s="25"/>
+      <c r="G30" s="19"/>
     </row>
     <row r="31" spans="1:7" ht="24">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="B31" s="25"/>
-      <c r="C31" s="26" t="s">
+      <c r="B31" s="19"/>
+      <c r="C31" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="D31" s="26" t="s">
+      <c r="D31" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="E31" s="26" t="s">
+      <c r="E31" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="F31" s="26" t="s">
+      <c r="F31" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="G31" s="25"/>
+      <c r="G31" s="19"/>
     </row>
     <row r="32" spans="1:7" ht="24">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="B32" s="25"/>
-      <c r="C32" s="26" t="s">
+      <c r="B32" s="19"/>
+      <c r="C32" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="D32" s="26" t="s">
+      <c r="D32" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="E32" s="26" t="s">
+      <c r="E32" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="F32" s="26" t="s">
+      <c r="F32" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="G32" s="25"/>
+      <c r="G32" s="19"/>
     </row>
     <row r="33" spans="1:7" ht="24">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="B33" s="25"/>
-      <c r="C33" s="26" t="s">
+      <c r="B33" s="19"/>
+      <c r="C33" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="D33" s="26" t="s">
+      <c r="D33" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="E33" s="26" t="s">
+      <c r="E33" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="F33" s="26" t="s">
+      <c r="F33" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="G33" s="25"/>
+      <c r="G33" s="19"/>
     </row>
     <row r="34" spans="1:7" ht="24">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="26" t="s">
+      <c r="B34" s="19"/>
+      <c r="C34" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="D34" s="26" t="s">
+      <c r="D34" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="E34" s="26" t="s">
+      <c r="E34" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="F34" s="26" t="s">
+      <c r="F34" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="G34" s="25"/>
+      <c r="G34" s="19"/>
     </row>
     <row r="35" spans="1:7" ht="24">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="B35" s="20"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="20"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="14"/>
     </row>
     <row r="36" spans="1:7" ht="24">
-      <c r="A36" s="33" t="s">
+      <c r="A36" s="27" t="s">
         <v>208</v>
       </c>
-      <c r="B36" s="20"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="20"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="14"/>
     </row>
     <row r="37" spans="1:7" ht="24">
-      <c r="A37" s="27" t="s">
+      <c r="A37" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="22" t="s">
+      <c r="B37" s="21"/>
+      <c r="C37" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="D37" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="E37" s="22" t="s">
+      <c r="E37" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="F37" s="22" t="s">
+      <c r="F37" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="G37" s="20"/>
+      <c r="G37" s="14"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="22"/>
-      <c r="B38" s="20"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="20"/>
+      <c r="A38" s="16"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="14"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="22"/>
-      <c r="B39" s="20"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="20"/>
+      <c r="A39" s="16"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="14"/>
     </row>
     <row r="40" spans="1:7">
       <c r="C40" s="9"/>
@@ -3413,241 +3426,241 @@
       <c r="F40" s="9"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="27"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="20"/>
+      <c r="A41" s="21"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="14"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="20"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="20"/>
+      <c r="A42" s="14"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="14"/>
     </row>
     <row r="43" spans="1:7" ht="24">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="22" t="s">
+      <c r="B43" s="21"/>
+      <c r="C43" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="D43" s="22" t="s">
+      <c r="D43" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="E43" s="22" t="s">
+      <c r="E43" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="F43" s="22" t="s">
+      <c r="F43" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="G43" s="20"/>
+      <c r="G43" s="14"/>
     </row>
     <row r="44" spans="1:7" ht="24">
-      <c r="A44" s="27" t="s">
+      <c r="A44" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="B44" s="27"/>
-      <c r="C44" s="22" t="s">
+      <c r="B44" s="21"/>
+      <c r="C44" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="D44" s="22" t="s">
+      <c r="D44" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="E44" s="22" t="s">
+      <c r="E44" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="F44" s="22" t="s">
+      <c r="F44" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="G44" s="20"/>
+      <c r="G44" s="14"/>
     </row>
     <row r="45" spans="1:7" ht="24">
-      <c r="A45" s="27" t="s">
+      <c r="A45" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="B45" s="27"/>
-      <c r="C45" s="22" t="s">
+      <c r="B45" s="21"/>
+      <c r="C45" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="D45" s="22" t="s">
+      <c r="D45" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="E45" s="22" t="s">
+      <c r="E45" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="F45" s="22" t="s">
+      <c r="F45" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="G45" s="20"/>
+      <c r="G45" s="14"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="20"/>
-      <c r="B46" s="20"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="20"/>
+      <c r="A46" s="14"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="14"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="20"/>
-      <c r="B47" s="20"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="20"/>
+      <c r="A47" s="14"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="14"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="20"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="20"/>
+      <c r="A48" s="14"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="14"/>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="20"/>
-      <c r="B49" s="20"/>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="20"/>
+      <c r="A49" s="14"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="14"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="20"/>
-      <c r="B50" s="20"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="20"/>
+      <c r="A50" s="14"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="14"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="20"/>
-      <c r="B51" s="20"/>
-      <c r="C51" s="22"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22"/>
-      <c r="G51" s="20"/>
+      <c r="A51" s="14"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="14"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="20"/>
-      <c r="B52" s="20"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="20"/>
+      <c r="A52" s="14"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="14"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="20"/>
-      <c r="B53" s="20"/>
-      <c r="C53" s="22"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="20"/>
+      <c r="A53" s="14"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="14"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="20"/>
-      <c r="B54" s="20"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="20"/>
+      <c r="A54" s="14"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="14"/>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="20"/>
-      <c r="B55" s="20"/>
-      <c r="C55" s="22"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="20"/>
+      <c r="A55" s="14"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="14"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="20"/>
-      <c r="B56" s="20"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="20"/>
+      <c r="A56" s="14"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="16"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="14"/>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="20"/>
-      <c r="B57" s="20"/>
-      <c r="C57" s="22"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="20"/>
+      <c r="A57" s="14"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="14"/>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="20"/>
-      <c r="B58" s="20"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="20"/>
+      <c r="A58" s="14"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="14"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="20"/>
-      <c r="B59" s="20"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="20"/>
+      <c r="A59" s="14"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="14"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="20"/>
-      <c r="B60" s="20"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="20"/>
+      <c r="A60" s="14"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="14"/>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="20"/>
-      <c r="B61" s="20"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="20"/>
+      <c r="A61" s="14"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="14"/>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="20"/>
-      <c r="B62" s="20"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="20"/>
+      <c r="A62" s="14"/>
+      <c r="B62" s="14"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="14"/>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="20"/>
-      <c r="B63" s="20"/>
-      <c r="C63" s="22"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="20"/>
+      <c r="A63" s="14"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="16"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="14"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:G3"/>
@@ -3660,64 +3673,151 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="69.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="B1" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="34"/>
+      <c r="B1" s="34" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="C1" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="D1" s="34"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="34" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="34" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="34" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="34"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="34" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
+      <c r="B7" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="D7" s="34"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="34" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
+      <c r="B8" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="34"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="34" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
+      <c r="B9" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" s="34"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="34" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
+      <c r="B10" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="D10" s="34"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="34" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
+      <c r="B11" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="D11" s="34"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="34" t="s">
         <v>212</v>
       </c>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
+++ b/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="218">
   <si>
     <t>测试功能点：查询、插入、更新、分区</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -116,774 +116,782 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>ycsb查询/插入/更新失败时，多久会重试一次，能否设置重试的时间间隔？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ycsb查询出错了，是接着之前的记录往下查？ 还是重新查？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手工拉起进程后正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统自动拉起进程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清理多余磁盘空间后正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重新mount上是否能正常？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>即使不恢复也应该正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入后能否恢复正常？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>？？？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>去除拥塞后应恢复正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应该正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复后正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重启后正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进程异常 kill -9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进程异常 kill -11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拔盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络丢包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络错包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网卡故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统掉电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三组3节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否做split</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>业务场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kill -15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kill -11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kill -9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁盘坏道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络错包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网卡故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统掉电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两台机器之间的网络</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障三台机器之间的网络</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障一台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障三台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预期结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实测结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行步骤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前置条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例编号规则见用例正交表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例编号规则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_AAA_BBB_CCC_DDD：AAA取并发任务序号，BBB取故障场景序号，CCC取业务场景序号,DDD在前三个基础上的细分场景.如sequoiadb_fault_001_001_001_001则为3个insert，不做split，使用kill -15故障一个主节点的场景。还要考虑故障交叉组合的场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群正常，已经split完成，3个并发插入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行1之后操作会报失败，并且在执行步骤2之前会恢复正常，之后一直正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有步骤2之后才能恢复正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一直正常</t>
+  </si>
+  <si>
+    <t>一直正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 主节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 两个主节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 三个主节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 一个备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 同一组内的两个备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 两个不同组的备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 三个不同组的备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ycsb查询、插入、更新有没有超时，超时时间多久？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一直正常(可能有超时)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_014_010_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，重启一台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.重启一台机器; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重启之后恢复正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_014_011_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_014_012_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，重启两台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，重启三台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.重启两台机器; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.重启三台机器; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优先级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 同一组内的两个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 两个不同组的备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 三个不同组的备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作会报失败，自动恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一直正常，且节点自动恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，一个主节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，两个主节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，三个主节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，一个备节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，两个备节点磁盘满（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，两个备节点磁盘满（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，三个备节点磁盘满（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.两个主节点磁盘满; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.三个主节点磁盘满; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.一个备节点磁盘满; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.两个备节点磁盘满（同一组）; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.两个备节点磁盘满（不同组）; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.三个备节点磁盘满（不同组）; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_002_001_001 kill -11待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>慢盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_005_001_001 慢盘待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拔盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_006_001_001 umount待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉一个主节点所在的磁盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉两个主节点所在的磁盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉三个主节点所在的磁盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉一个备节点所在的磁盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉两个备节点所在的磁盘（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉两个备节点所在的磁盘（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉三个备节点所在的磁盘（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.一个主节点磁盘满（往磁盘上灌数据，同时可以看做是慢盘了）; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉一个主节点所在的磁盘; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉两个主节点所在的磁盘; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉三个主节点所在的磁盘; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉一个备节点所在的磁盘; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉两个备节点所在的磁盘（同一组）; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉两个备节点所在的磁盘（不同组）; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉三个备节点所在的磁盘（不同组）; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行1之后操作会报失败，并且在执行步骤2之前会恢复正常，之后一直正常？？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有步骤2之后才能恢复正常？？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_008_001_001磁盘坏道待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_009_008_001网络拥塞待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_010_008_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，造成两台机器之间丢包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.注入网络丢包; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试环境:192.168.20.169/170/171 root:sequoiadb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谭钊波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ycsb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>ycsb查询/插入/更新的结果报告格式</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ycsb查询/插入/更新失败时，多久会重试一次，能否设置重试的时间间隔？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ycsb是否有数据对比工具，比较的流程是什么样的？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ycsb查询出错了，是接着之前的记录往下查？ 还是重新查？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>手工拉起进程后正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统自动拉起进程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>清理多余磁盘空间后正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重新mount上是否能正常？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>即使不恢复也应该正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>插入后能否恢复正常？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>？？？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>去除拥塞后应恢复正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>应该正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复后正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重启后正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进程异常 kill -9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进程异常 kill -11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>umount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拔盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络拥塞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络丢包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络错包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网卡故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统掉电</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三组3节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>并发任务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否做split</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障场景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>业务场景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>insert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kill -15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kill -11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kill -9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>umount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>磁盘坏道</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络拥塞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络错包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网卡故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统掉电</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障一个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障一个备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障三个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两个备节点（同一组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障三个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两台机器之间的网络</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障三台机器之间的网络</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障一台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障三台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>预期结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>实测结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>执行步骤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>前置条件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill一个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例编号规则见用例正交表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例编号规则</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_001_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_AAA_BBB_CCC_DDD：AAA取并发任务序号，BBB取故障场景序号，CCC取业务场景序号,DDD在前三个基础上的细分场景.如sequoiadb_fault_001_001_001_001则为3个insert，不做split，使用kill -15故障一个主节点的场景。还要考虑故障交叉组合的场景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_002_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_003_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill两个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill三个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_004_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_005_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_006_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_007_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill一个备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill两个备节点（同一组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill两个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill三个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>集群正常，已经split完成，3个并发插入</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>执行1之后操作会报失败，并且在执行步骤2之前会恢复正常，之后一直正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只有步骤2之后才能恢复正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一直正常</t>
-  </si>
-  <si>
-    <t>一直正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 主节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 两个主节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 三个主节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 一个备节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 同一组内的两个备节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 两个不同组的备节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 三个不同组的备节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ycsb查询、插入、更新有没有超时，超时时间多久？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一直正常(可能有超时)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_014_010_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，重启一台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.重启一台机器; </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重启之后恢复正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_014_011_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_014_012_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，重启两台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，重启三台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.重启两台机器; </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.重启三台机器; </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>优先级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_007_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_001_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_002_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_003_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_004_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_005_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_006_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀一个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀两个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀三个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀一个备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀两个备节点（同一组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀两个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀三个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 两个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 三个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 一个备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 同一组内的两个备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 两个不同组的备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 三个不同组的备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>操作会报失败，自动恢复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一直正常，且节点自动恢复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_001_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_002_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_003_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_004_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_005_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_006_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_007_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，一个主节点磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，两个主节点磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，三个主节点磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，一个备节点磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，两个备节点磁盘满（同一组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，两个备节点磁盘满（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，三个备节点磁盘满（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.两个主节点磁盘满; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.三个主节点磁盘满; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.一个备节点磁盘满; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.两个备节点磁盘满（同一组）; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.两个备节点磁盘满（不同组）; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.三个备节点磁盘满（不同组）; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_002_001_001 kill -11待补</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>慢盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_005_001_001 慢盘待补</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拔盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_006_001_001 umount待补</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_001_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_002_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_003_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_004_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_005_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_006_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_007_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉一个主节点所在的磁盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉两个主节点所在的磁盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉三个主节点所在的磁盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉一个备节点所在的磁盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉两个备节点所在的磁盘（同一组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉两个备节点所在的磁盘（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉三个备节点所在的磁盘（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.一个主节点磁盘满（往磁盘上灌数据，同时可以看做是慢盘了）; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉一个主节点所在的磁盘; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉两个主节点所在的磁盘; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉三个主节点所在的磁盘; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉一个备节点所在的磁盘; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉两个备节点所在的磁盘（同一组）; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉两个备节点所在的磁盘（不同组）; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉三个备节点所在的磁盘（不同组）; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>执行1之后操作会报失败，并且在执行步骤2之前会恢复正常，之后一直正常？？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只有步骤2之后才能恢复正常？？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_008_001_001磁盘坏道待补</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_009_008_001网络拥塞待补</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_010_008_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，造成两台机器之间丢包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.注入网络丢包; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试环境:192.168.20.169/170/171 root:sequoiadb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>责任人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>谭钊波</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ycsb</t>
+    <t>如何指定表名，表的split信息等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如何指定表中字段的类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1156,6 +1164,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1174,7 +1183,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1854,25 +1862,25 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="29" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
@@ -1880,8 +1888,8 @@
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="29"/>
-      <c r="B4" s="30"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="31"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
@@ -1889,36 +1897,36 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="29"/>
-      <c r="B5" s="28" t="s">
+      <c r="A5" s="30"/>
+      <c r="B5" s="29" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="29"/>
-      <c r="B6" s="29"/>
+      <c r="A6" s="30"/>
+      <c r="B6" s="30"/>
       <c r="C6" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="29"/>
-      <c r="B7" s="30"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="31"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -1926,7 +1934,7 @@
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="29"/>
+      <c r="A8" s="30"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1935,7 +1943,7 @@
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="30"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1944,25 +1952,25 @@
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="29" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="29"/>
-      <c r="B11" s="29"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -1970,8 +1978,8 @@
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="29"/>
-      <c r="B12" s="30"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="31"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -1979,36 +1987,36 @@
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="29"/>
-      <c r="B13" s="28" t="s">
+      <c r="A13" s="30"/>
+      <c r="B13" s="29" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="30"/>
       <c r="C14" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="29"/>
-      <c r="B15" s="29"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="30"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -2016,8 +2024,8 @@
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="29"/>
-      <c r="B16" s="30"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="31"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -2025,36 +2033,36 @@
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="29"/>
-      <c r="B17" s="28" t="s">
+      <c r="A17" s="30"/>
+      <c r="B17" s="29" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="29"/>
-      <c r="B18" s="29"/>
+      <c r="A18" s="30"/>
+      <c r="B18" s="30"/>
       <c r="C18" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="29"/>
-      <c r="B19" s="29"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="30"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -2062,8 +2070,8 @@
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="30"/>
-      <c r="B20" s="30"/>
+      <c r="A20" s="31"/>
+      <c r="B20" s="31"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -2071,51 +2079,51 @@
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="29" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="29"/>
-      <c r="B22" s="29"/>
+      <c r="A22" s="30"/>
+      <c r="B22" s="30"/>
       <c r="C22" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="29"/>
-      <c r="B23" s="29"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
       <c r="C23" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="29"/>
-      <c r="B24" s="29"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="30"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -2123,8 +2131,8 @@
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="29"/>
-      <c r="B25" s="30"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="31"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -2132,36 +2140,36 @@
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="29"/>
-      <c r="B26" s="28" t="s">
+      <c r="A26" s="30"/>
+      <c r="B26" s="29" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="29"/>
-      <c r="B27" s="29"/>
+      <c r="A27" s="30"/>
+      <c r="B27" s="30"/>
       <c r="C27" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="30"/>
-      <c r="B28" s="30"/>
+      <c r="A28" s="31"/>
+      <c r="B28" s="31"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -2169,35 +2177,35 @@
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="29" t="s">
         <v>19</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="29"/>
+      <c r="A30" s="30"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="29"/>
+      <c r="A31" s="30"/>
       <c r="B31" s="3"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -2206,7 +2214,7 @@
       <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="30"/>
+      <c r="A32" s="31"/>
       <c r="B32" s="3"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -2254,32 +2262,32 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="D1" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="33"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="H3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="11" t="s">
+      <c r="K3" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2287,28 +2295,28 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H4" s="3">
         <v>1</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K4" s="3">
         <v>1</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2316,28 +2324,28 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H5" s="3">
         <v>2</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K5" s="3">
         <v>2</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2345,28 +2353,28 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H6" s="3">
         <v>3</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K6" s="3">
         <v>3</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2374,28 +2382,28 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H7" s="3">
         <v>4</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K7" s="3">
         <v>4</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2403,28 +2411,28 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H8" s="3">
         <v>5</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K8" s="3">
         <v>5</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2432,28 +2440,28 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H9" s="3">
         <v>6</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K9" s="3">
         <v>6</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2461,28 +2469,28 @@
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H10" s="3">
         <v>7</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="K10" s="3">
         <v>7</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2490,22 +2498,22 @@
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H11" s="3">
         <v>8</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2513,16 +2521,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2530,16 +2538,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2547,28 +2555,28 @@
         <v>11</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H14" s="3">
         <v>9</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K14" s="3">
         <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2576,28 +2584,28 @@
         <v>12</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H15" s="3">
         <v>10</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K15" s="3">
         <v>9</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2605,22 +2613,22 @@
         <v>13</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H16" s="3">
         <v>11</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -2628,22 +2636,22 @@
         <v>14</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H17" s="3">
         <v>12</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -2651,22 +2659,22 @@
         <v>15</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H18" s="3">
         <v>13</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -2674,16 +2682,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -2703,13 +2711,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K21" s="3">
         <v>10</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -2717,13 +2725,13 @@
         <v>15</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K22" s="3">
         <v>11</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2731,15 +2739,15 @@
         <v>12</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="18" t="s">
         <v>91</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2769,168 +2777,168 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A4" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B4" s="21"/>
       <c r="C4" s="22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G4" s="21"/>
     </row>
     <row r="5" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A5" s="21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G5" s="21"/>
     </row>
     <row r="6" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A6" s="21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="22" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G6" s="21"/>
     </row>
     <row r="7" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A7" s="21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B7" s="21"/>
       <c r="C7" s="22" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G7" s="21"/>
     </row>
     <row r="8" spans="1:7" ht="24">
       <c r="A8" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B8" s="21"/>
       <c r="C8" s="16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D8" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" s="16" t="s">
         <v>108</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>110</v>
       </c>
       <c r="G8" s="14"/>
     </row>
     <row r="9" spans="1:7" ht="24">
       <c r="A9" s="21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B9" s="21"/>
       <c r="C9" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="22" t="s">
-        <v>108</v>
-      </c>
       <c r="E9" s="16" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G9" s="14"/>
     </row>
     <row r="10" spans="1:7" ht="24">
       <c r="A10" s="21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G10" s="14"/>
     </row>
     <row r="11" spans="1:7" ht="24">
       <c r="A11" s="24" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="20"/>
@@ -2941,273 +2949,273 @@
     </row>
     <row r="12" spans="1:7" ht="24">
       <c r="A12" s="21" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G12" s="21"/>
     </row>
     <row r="13" spans="1:7" ht="24">
       <c r="A13" s="21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="22" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G13" s="21"/>
     </row>
     <row r="14" spans="1:7" ht="24">
       <c r="A14" s="21" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="22" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G14" s="21"/>
     </row>
     <row r="15" spans="1:7" ht="24">
       <c r="A15" s="21" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="22" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G15" s="21"/>
     </row>
     <row r="16" spans="1:7" ht="24">
       <c r="A16" s="21" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="22" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G16" s="21"/>
     </row>
     <row r="17" spans="1:7" ht="24">
       <c r="A17" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="22" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G17" s="21"/>
     </row>
     <row r="18" spans="1:7" ht="24">
       <c r="A18" s="21" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B18" s="21"/>
       <c r="C18" s="22" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E18" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="F18" s="22" t="s">
         <v>155</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>157</v>
       </c>
       <c r="G18" s="21"/>
     </row>
     <row r="19" spans="1:7" ht="24">
       <c r="A19" s="19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G19" s="19"/>
     </row>
     <row r="20" spans="1:7" ht="24">
       <c r="A20" s="19" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="20" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G20" s="19"/>
     </row>
     <row r="21" spans="1:7" ht="24">
       <c r="A21" s="19" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="20" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G21" s="19"/>
     </row>
     <row r="22" spans="1:7" ht="24">
       <c r="A22" s="19" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="20" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G22" s="19"/>
     </row>
     <row r="23" spans="1:7" ht="24">
       <c r="A23" s="19" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G23" s="19"/>
     </row>
     <row r="24" spans="1:7" ht="24">
       <c r="A24" s="19" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="20" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G24" s="19"/>
     </row>
     <row r="25" spans="1:7" ht="24">
       <c r="A25" s="19" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B25" s="19"/>
       <c r="C25" s="20" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G25" s="19"/>
     </row>
     <row r="26" spans="1:7" ht="24">
       <c r="A26" s="25" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="16"/>
@@ -3218,7 +3226,7 @@
     </row>
     <row r="27" spans="1:7" ht="24">
       <c r="A27" s="26" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="16"/>
@@ -3229,140 +3237,140 @@
     </row>
     <row r="28" spans="1:7" ht="24">
       <c r="A28" s="19" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="20" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G28" s="19"/>
     </row>
     <row r="29" spans="1:7" ht="24">
       <c r="A29" s="19" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B29" s="19"/>
       <c r="C29" s="20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G29" s="19"/>
     </row>
     <row r="30" spans="1:7" ht="24">
       <c r="A30" s="19" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B30" s="19"/>
       <c r="C30" s="20" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G30" s="19"/>
     </row>
     <row r="31" spans="1:7" ht="24">
       <c r="A31" s="19" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B31" s="19"/>
       <c r="C31" s="20" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G31" s="19"/>
     </row>
     <row r="32" spans="1:7" ht="24">
       <c r="A32" s="19" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="20" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G32" s="19"/>
     </row>
     <row r="33" spans="1:7" ht="24">
       <c r="A33" s="19" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B33" s="19"/>
       <c r="C33" s="20" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G33" s="19"/>
     </row>
     <row r="34" spans="1:7" ht="24">
       <c r="A34" s="19" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="20" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G34" s="19"/>
     </row>
     <row r="35" spans="1:7" ht="24">
       <c r="A35" s="25" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B35" s="14"/>
       <c r="C35" s="16"/>
@@ -3373,7 +3381,7 @@
     </row>
     <row r="36" spans="1:7" ht="24">
       <c r="A36" s="27" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B36" s="14"/>
       <c r="C36" s="16"/>
@@ -3384,20 +3392,20 @@
     </row>
     <row r="37" spans="1:7" ht="24">
       <c r="A37" s="21" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G37" s="14"/>
     </row>
@@ -3445,58 +3453,58 @@
     </row>
     <row r="43" spans="1:7" ht="24">
       <c r="A43" s="21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B43" s="21"/>
       <c r="C43" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="F43" s="16" t="s">
         <v>125</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="F43" s="16" t="s">
-        <v>127</v>
       </c>
       <c r="G43" s="14"/>
     </row>
     <row r="44" spans="1:7" ht="24">
       <c r="A44" s="21" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E44" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="D44" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="E44" s="16" t="s">
-        <v>132</v>
-      </c>
       <c r="F44" s="16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G44" s="14"/>
     </row>
     <row r="45" spans="1:7" ht="24">
       <c r="A45" s="21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E45" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="D45" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="E45" s="16" t="s">
-        <v>133</v>
-      </c>
       <c r="F45" s="16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G45" s="14"/>
     </row>
@@ -3673,151 +3681,172 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="69.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="34"/>
-      <c r="B1" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="C1" s="34" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="28"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="E1" s="28"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="D1" s="34"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="34"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="34" t="s">
+      <c r="D7" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="E7" s="28"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" s="28"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="E9" s="28"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="34" t="s">
-        <v>215</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>214</v>
-      </c>
-      <c r="D7" s="34"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>215</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>214</v>
-      </c>
-      <c r="D8" s="34"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>215</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>214</v>
-      </c>
-      <c r="D9" s="34"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>215</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>214</v>
-      </c>
-      <c r="D10" s="34"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>215</v>
-      </c>
-      <c r="C11" s="34" t="s">
-        <v>214</v>
-      </c>
-      <c r="D11" s="34"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="34"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="34"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="34"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="34" t="s">
+      <c r="B10" s="28"/>
+      <c r="C10" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="D10" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
+      <c r="E10" s="28"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="E11" s="28"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="28"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="28"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
+++ b/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="223">
   <si>
     <t>测试功能点：查询、插入、更新、分区</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -104,6 +104,741 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>手工拉起进程后正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统自动拉起进程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清理多余磁盘空间后正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重新mount上是否能正常？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>即使不恢复也应该正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入后能否恢复正常？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>？？？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>去除拥塞后应恢复正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应该正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复后正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重启后正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进程异常 kill -9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进程异常 kill -11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拔盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络丢包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络错包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网卡故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统掉电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三组3节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否做split</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>业务场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kill -15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kill -11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kill -9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁盘坏道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络错包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网卡故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统掉电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两台机器之间的网络</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障三台机器之间的网络</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障一台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障三台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预期结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实测结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行步骤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前置条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例编号规则见用例正交表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例编号规则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_AAA_BBB_CCC_DDD：AAA取并发任务序号，BBB取故障场景序号，CCC取业务场景序号,DDD在前三个基础上的细分场景.如sequoiadb_fault_001_001_001_001则为3个insert，不做split，使用kill -15故障一个主节点的场景。还要考虑故障交叉组合的场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群正常，已经split完成，3个并发插入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行1之后操作会报失败，并且在执行步骤2之前会恢复正常，之后一直正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有步骤2之后才能恢复正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一直正常</t>
+  </si>
+  <si>
+    <t>一直正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 主节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 两个主节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 三个主节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 一个备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 同一组内的两个备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 两个不同组的备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 三个不同组的备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一直正常(可能有超时)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_014_010_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，重启一台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.重启一台机器; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重启之后恢复正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_014_011_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_014_012_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，重启两台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，重启三台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.重启两台机器; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.重启三台机器; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优先级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 同一组内的两个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 两个不同组的备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 三个不同组的备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作会报失败，自动恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一直正常，且节点自动恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，一个主节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，两个主节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，三个主节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，一个备节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，两个备节点磁盘满（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，两个备节点磁盘满（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，三个备节点磁盘满（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.两个主节点磁盘满; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.三个主节点磁盘满; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.一个备节点磁盘满; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.两个备节点磁盘满（同一组）; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.两个备节点磁盘满（不同组）; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.三个备节点磁盘满（不同组）; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_002_001_001 kill -11待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>慢盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_005_001_001 慢盘待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拔盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_006_001_001 umount待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉一个主节点所在的磁盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉两个主节点所在的磁盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉三个主节点所在的磁盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉一个备节点所在的磁盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉两个备节点所在的磁盘（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉两个备节点所在的磁盘（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉三个备节点所在的磁盘（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.一个主节点磁盘满（往磁盘上灌数据，同时可以看做是慢盘了）; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉一个主节点所在的磁盘; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉两个主节点所在的磁盘; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉三个主节点所在的磁盘; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉一个备节点所在的磁盘; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉两个备节点所在的磁盘（同一组）; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉两个备节点所在的磁盘（不同组）; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉三个备节点所在的磁盘（不同组）; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行1之后操作会报失败，并且在执行步骤2之前会恢复正常，之后一直正常？？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有步骤2之后才能恢复正常？？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_008_001_001磁盘坏道待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_009_008_001网络拥塞待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_010_008_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，造成两台机器之间丢包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.注入网络丢包; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>磁盘坏道模拟工具</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -116,382 +851,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>tc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>ycsb查询/插入/更新失败时，多久会重试一次，能否设置重试的时间间隔？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>ycsb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谭钊波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ycsb分为两个阶段:load和run。第一阶段装置数据如果出错，将报错，并停止执行。第二阶段跑性能测试（其基本操作有read,scan,insert,update,delete ）。第二阶段如果出错，将忽略错误继续进行，并在结果中告知出错的数量。目前没有发现ycsb可以设置重试的选项。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ycsb查询/插入/更新的结果报告格式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ycsb的报告主要包含：总耗时（Runtime），平均吞吐量（Throughput）,总操作数（Operations）,平均耗时（AverageLatency）,最小耗时（MinLatency）,最大耗时（MaxLatency）,整体运行情况（失败多少，成功多少），及性能统计数据（有两种方式呈现，具体请附件1，附件2）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ycsb是否有数据对比工具，比较的流程是什么样的？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂时没发现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>ycsb查询出错了，是接着之前的记录往下查？ 还是重新查？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>手工拉起进程后正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统自动拉起进程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>清理多余磁盘空间后正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重新mount上是否能正常？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>即使不恢复也应该正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>插入后能否恢复正常？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>？？？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>去除拥塞后应恢复正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>应该正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复后正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重启后正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进程异常 kill -9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进程异常 kill -11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>umount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拔盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络拥塞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络丢包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络错包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网卡故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统掉电</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三组3节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>并发任务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否做split</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障场景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>业务场景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>insert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kill -15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kill -11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kill -9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>umount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>磁盘坏道</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络拥塞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络错包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网卡故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统掉电</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障一个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障一个备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障三个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两个备节点（同一组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障三个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两台机器之间的网络</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障三台机器之间的网络</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障一台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障三台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>预期结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>实测结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>执行步骤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>前置条件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill一个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例编号规则见用例正交表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例编号规则</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_001_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_AAA_BBB_CCC_DDD：AAA取并发任务序号，BBB取故障场景序号，CCC取业务场景序号,DDD在前三个基础上的细分场景.如sequoiadb_fault_001_001_001_001则为3个insert，不做split，使用kill -15故障一个主节点的场景。还要考虑故障交叉组合的场景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_002_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_003_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill两个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill三个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_004_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_005_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_006_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_007_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill一个备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill两个备节点（同一组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill两个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill三个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>集群正常，已经split完成，3个并发插入</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>执行1之后操作会报失败，并且在执行步骤2之前会恢复正常，之后一直正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只有步骤2之后才能恢复正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一直正常</t>
-  </si>
-  <si>
-    <t>一直正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 主节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 两个主节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 三个主节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 一个备节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 同一组内的两个备节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 两个不同组的备节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 三个不同组的备节点; 2.过一定时间恢复故障</t>
+    <t>单看查询（就是在run阶段），出错了，是继续往下进行的。它只会把这个查询出错的operation记录一下。我们从结果报告中的Return一项可以看到有多少operation失败了。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -499,367 +899,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>一直正常(可能有超时)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_014_010_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，重启一台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.重启一台机器; </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重启之后恢复正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_014_011_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_014_012_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，重启两台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，重启三台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.重启两台机器; </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.重启三台机器; </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>优先级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_007_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_001_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_002_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_003_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_004_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_005_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_006_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀一个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀两个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀三个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀一个备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀两个备节点（同一组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀两个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀三个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 两个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 三个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 一个备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 同一组内的两个备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 两个不同组的备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 三个不同组的备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>操作会报失败，自动恢复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一直正常，且节点自动恢复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_001_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_002_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_003_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_004_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_005_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_006_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_007_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，一个主节点磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，两个主节点磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，三个主节点磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，一个备节点磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，两个备节点磁盘满（同一组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，两个备节点磁盘满（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，三个备节点磁盘满（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.两个主节点磁盘满; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.三个主节点磁盘满; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.一个备节点磁盘满; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.两个备节点磁盘满（同一组）; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.两个备节点磁盘满（不同组）; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.三个备节点磁盘满（不同组）; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_002_001_001 kill -11待补</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>慢盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_005_001_001 慢盘待补</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拔盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_006_001_001 umount待补</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_001_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_002_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_003_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_004_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_005_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_006_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_007_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉一个主节点所在的磁盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉两个主节点所在的磁盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉三个主节点所在的磁盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉一个备节点所在的磁盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉两个备节点所在的磁盘（同一组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉两个备节点所在的磁盘（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉三个备节点所在的磁盘（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.一个主节点磁盘满（往磁盘上灌数据，同时可以看做是慢盘了）; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉一个主节点所在的磁盘; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉两个主节点所在的磁盘; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉三个主节点所在的磁盘; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉一个备节点所在的磁盘; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉两个备节点所在的磁盘（同一组）; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉两个备节点所在的磁盘（不同组）; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉三个备节点所在的磁盘（不同组）; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>执行1之后操作会报失败，并且在执行步骤2之前会恢复正常，之后一直正常？？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只有步骤2之后才能恢复正常？？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_008_001_001磁盘坏道待补</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_009_008_001网络拥塞待补</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_010_008_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，造成两台机器之间丢包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.注入网络丢包; 2.过一定时间恢复故障</t>
+    <t>目前没发现。超时了估计当错误处理。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -867,31 +907,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>责任人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>谭钊波</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ycsb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ycsb查询/插入/更新的结果报告格式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ycsb是否有数据对比工具，比较的流程是什么样的？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如何指定表名，表的split信息等</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如何指定表中字段的类型</t>
+    <t>附件一：以下性能数据表明0-1ms跑完operation的数量为464；1-2ms跑完operation的数据为27；...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>附件二：以下性能数据表明0-2000ms内跑完operation的比例为2.2%；…</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1113,7 +1133,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1164,7 +1184,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1183,6 +1202,18 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1191,74 +1222,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -1515,6 +1478,87 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>75439</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>94853</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="1.png"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7200900"/>
+          <a:ext cx="6095239" cy="3180953"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>56391</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>94638</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2" descr="2.png"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="10629900"/>
+          <a:ext cx="6076191" cy="4895238"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1523,7 +1567,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1862,25 +1906,25 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="28" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="30"/>
-      <c r="B3" s="30"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
@@ -1888,8 +1932,8 @@
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="30"/>
-      <c r="B4" s="31"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="30"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
@@ -1897,36 +1941,36 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="30"/>
-      <c r="B5" s="29" t="s">
+      <c r="A5" s="29"/>
+      <c r="B5" s="28" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="30"/>
-      <c r="B6" s="30"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
       <c r="C6" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="30"/>
-      <c r="B7" s="31"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="30"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -1934,7 +1978,7 @@
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="30"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1943,7 +1987,7 @@
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="31"/>
+      <c r="A9" s="30"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1952,25 +1996,25 @@
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="28" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="29"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -1978,8 +2022,8 @@
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="30"/>
-      <c r="B12" s="31"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="30"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -1987,36 +2031,36 @@
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="30"/>
-      <c r="B13" s="29" t="s">
+      <c r="A13" s="29"/>
+      <c r="B13" s="28" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="29"/>
       <c r="C14" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
+      <c r="A15" s="29"/>
+      <c r="B15" s="29"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -2024,8 +2068,8 @@
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="30"/>
-      <c r="B16" s="31"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="30"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -2033,36 +2077,36 @@
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="30"/>
-      <c r="B17" s="29" t="s">
+      <c r="A17" s="29"/>
+      <c r="B17" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="30"/>
-      <c r="B18" s="30"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="29"/>
       <c r="C18" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="30"/>
-      <c r="B19" s="30"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="29"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -2070,8 +2114,8 @@
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="31"/>
-      <c r="B20" s="31"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -2079,51 +2123,51 @@
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="28" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="30"/>
-      <c r="B22" s="30"/>
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
       <c r="C22" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="29"/>
       <c r="C23" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
+      <c r="A24" s="29"/>
+      <c r="B24" s="29"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -2131,8 +2175,8 @@
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="30"/>
-      <c r="B25" s="31"/>
+      <c r="A25" s="29"/>
+      <c r="B25" s="30"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -2140,36 +2184,36 @@
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="30"/>
-      <c r="B26" s="29" t="s">
+      <c r="A26" s="29"/>
+      <c r="B26" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
+      <c r="A27" s="29"/>
+      <c r="B27" s="29"/>
       <c r="C27" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="31"/>
-      <c r="B28" s="31"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="30"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -2177,35 +2221,35 @@
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="28" t="s">
         <v>19</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="30"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="30"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="3"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -2214,7 +2258,7 @@
       <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="31"/>
+      <c r="A32" s="30"/>
       <c r="B32" s="3"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -2262,32 +2306,32 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="D1" s="9" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
+        <v>43</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="32"/>
+      <c r="D3" s="33"/>
       <c r="E3" s="11" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2295,28 +2339,28 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H4" s="3">
         <v>1</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="K4" s="3">
         <v>1</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2324,28 +2368,28 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H5" s="3">
         <v>2</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="K5" s="3">
         <v>2</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2353,28 +2397,28 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H6" s="3">
         <v>3</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K6" s="3">
         <v>3</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2382,28 +2426,28 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H7" s="3">
         <v>4</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K7" s="3">
         <v>4</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2411,28 +2455,28 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H8" s="3">
         <v>5</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="K8" s="3">
         <v>5</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2440,28 +2484,28 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H9" s="3">
         <v>6</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="K9" s="3">
         <v>6</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2469,28 +2513,28 @@
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H10" s="3">
         <v>7</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="K10" s="3">
         <v>7</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2498,22 +2542,22 @@
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H11" s="3">
         <v>8</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2521,16 +2565,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2538,16 +2582,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2555,28 +2599,28 @@
         <v>11</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H14" s="3">
         <v>9</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="K14" s="3">
         <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2584,28 +2628,28 @@
         <v>12</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H15" s="3">
         <v>10</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K15" s="3">
         <v>9</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2613,22 +2657,22 @@
         <v>13</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H16" s="3">
         <v>11</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -2636,22 +2680,22 @@
         <v>14</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H17" s="3">
         <v>12</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -2659,22 +2703,22 @@
         <v>15</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H18" s="3">
         <v>13</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -2682,16 +2726,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -2711,13 +2755,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="K21" s="3">
         <v>10</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -2725,13 +2769,13 @@
         <v>15</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="K22" s="3">
         <v>11</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2739,15 +2783,15 @@
         <v>12</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="9" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2777,168 +2821,168 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="9" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>86</v>
-      </c>
       <c r="E3" s="15" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A4" s="21" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B4" s="21"/>
       <c r="C4" s="22" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="G4" s="21"/>
     </row>
     <row r="5" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A5" s="21" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="22" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="G5" s="21"/>
     </row>
     <row r="6" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A6" s="21" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="22" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D6" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="22" t="s">
-        <v>113</v>
-      </c>
       <c r="F6" s="22" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="G6" s="21"/>
     </row>
     <row r="7" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A7" s="21" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B7" s="21"/>
       <c r="C7" s="22" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G7" s="21"/>
     </row>
     <row r="8" spans="1:7" ht="24">
       <c r="A8" s="21" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B8" s="21"/>
       <c r="C8" s="16" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="G8" s="14"/>
     </row>
     <row r="9" spans="1:7" ht="24">
       <c r="A9" s="21" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B9" s="21"/>
       <c r="C9" s="16" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G9" s="14"/>
     </row>
     <row r="10" spans="1:7" ht="24">
       <c r="A10" s="21" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="16" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G10" s="14"/>
     </row>
     <row r="11" spans="1:7" ht="24">
       <c r="A11" s="24" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="20"/>
@@ -2949,273 +2993,273 @@
     </row>
     <row r="12" spans="1:7" ht="24">
       <c r="A12" s="21" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="22" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G12" s="21"/>
     </row>
     <row r="13" spans="1:7" ht="24">
       <c r="A13" s="21" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="22" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G13" s="21"/>
     </row>
     <row r="14" spans="1:7" ht="24">
       <c r="A14" s="21" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="22" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G14" s="21"/>
     </row>
     <row r="15" spans="1:7" ht="24">
       <c r="A15" s="21" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="22" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="G15" s="21"/>
     </row>
     <row r="16" spans="1:7" ht="24">
       <c r="A16" s="21" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="22" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G16" s="21"/>
     </row>
     <row r="17" spans="1:7" ht="24">
       <c r="A17" s="21" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="22" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="G17" s="21"/>
     </row>
     <row r="18" spans="1:7" ht="24">
       <c r="A18" s="21" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B18" s="21"/>
       <c r="C18" s="22" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="G18" s="21"/>
     </row>
     <row r="19" spans="1:7" ht="24">
       <c r="A19" s="19" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="20" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G19" s="19"/>
     </row>
     <row r="20" spans="1:7" ht="24">
       <c r="A20" s="19" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="20" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G20" s="19"/>
     </row>
     <row r="21" spans="1:7" ht="24">
       <c r="A21" s="19" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="20" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G21" s="19"/>
     </row>
     <row r="22" spans="1:7" ht="24">
       <c r="A22" s="19" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="20" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G22" s="19"/>
     </row>
     <row r="23" spans="1:7" ht="24">
       <c r="A23" s="19" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="20" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G23" s="19"/>
     </row>
     <row r="24" spans="1:7" ht="24">
       <c r="A24" s="19" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="20" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G24" s="19"/>
     </row>
     <row r="25" spans="1:7" ht="24">
       <c r="A25" s="19" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B25" s="19"/>
       <c r="C25" s="20" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G25" s="19"/>
     </row>
     <row r="26" spans="1:7" ht="24">
       <c r="A26" s="25" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="16"/>
@@ -3226,7 +3270,7 @@
     </row>
     <row r="27" spans="1:7" ht="24">
       <c r="A27" s="26" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="16"/>
@@ -3237,140 +3281,140 @@
     </row>
     <row r="28" spans="1:7" ht="24">
       <c r="A28" s="19" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="D28" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>196</v>
-      </c>
       <c r="F28" s="20" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="G28" s="19"/>
     </row>
     <row r="29" spans="1:7" ht="24">
       <c r="A29" s="19" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B29" s="19"/>
       <c r="C29" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E29" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="D29" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>197</v>
-      </c>
       <c r="F29" s="20" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="G29" s="19"/>
     </row>
     <row r="30" spans="1:7" ht="24">
       <c r="A30" s="19" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B30" s="19"/>
       <c r="C30" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E30" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="D30" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" s="20" t="s">
-        <v>198</v>
-      </c>
       <c r="F30" s="20" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="G30" s="19"/>
     </row>
     <row r="31" spans="1:7" ht="24">
       <c r="A31" s="19" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B31" s="19"/>
       <c r="C31" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E31" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="D31" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>199</v>
-      </c>
       <c r="F31" s="20" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="G31" s="19"/>
     </row>
     <row r="32" spans="1:7" ht="24">
       <c r="A32" s="19" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E32" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D32" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="20" t="s">
-        <v>200</v>
-      </c>
       <c r="F32" s="20" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G32" s="19"/>
     </row>
     <row r="33" spans="1:7" ht="24">
       <c r="A33" s="19" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B33" s="19"/>
       <c r="C33" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="D33" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>201</v>
-      </c>
       <c r="F33" s="20" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="G33" s="19"/>
     </row>
     <row r="34" spans="1:7" ht="24">
       <c r="A34" s="19" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E34" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="D34" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E34" s="20" t="s">
-        <v>202</v>
-      </c>
       <c r="F34" s="20" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="G34" s="19"/>
     </row>
     <row r="35" spans="1:7" ht="24">
       <c r="A35" s="25" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B35" s="14"/>
       <c r="C35" s="16"/>
@@ -3381,7 +3425,7 @@
     </row>
     <row r="36" spans="1:7" ht="24">
       <c r="A36" s="27" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B36" s="14"/>
       <c r="C36" s="16"/>
@@ -3392,20 +3436,20 @@
     </row>
     <row r="37" spans="1:7" ht="24">
       <c r="A37" s="21" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="16" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="G37" s="14"/>
     </row>
@@ -3453,58 +3497,58 @@
     </row>
     <row r="43" spans="1:7" ht="24">
       <c r="A43" s="21" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B43" s="21"/>
       <c r="C43" s="16" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="G43" s="14"/>
     </row>
     <row r="44" spans="1:7" ht="24">
       <c r="A44" s="21" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="16" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="G44" s="14"/>
     </row>
     <row r="45" spans="1:7" ht="24">
       <c r="A45" s="21" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="16" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="G45" s="14"/>
     </row>
@@ -3681,177 +3725,180 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="69.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.625" customWidth="1"/>
+    <col min="1" max="1" width="69.625" style="37" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9" style="36"/>
+    <col min="4" max="4" width="45.25" style="37" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="28"/>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="D1" s="28" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="34"/>
+      <c r="B1" s="35" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>203</v>
+      </c>
+      <c r="D1" s="34"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="34"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="34"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="34"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="34"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="34" t="s">
+        <v>206</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="34"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="34"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="34"/>
+    </row>
+    <row r="7" spans="1:4" ht="81">
+      <c r="A7" s="34" t="s">
+        <v>208</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="D7" s="34" t="s">
         <v>211</v>
       </c>
-      <c r="E1" s="28"/>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="28"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="81">
+      <c r="A8" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="D8" s="34" t="s">
         <v>213</v>
       </c>
-      <c r="D7" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="E7" s="28"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="28" t="s">
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="34" t="s">
         <v>214</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="E8" s="28"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="28" t="s">
+      <c r="B9" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="D9" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="E9" s="28"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="E10" s="28"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="E11" s="28"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="28" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="54">
+      <c r="A10" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="28" t="s">
+      <c r="B10" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="D10" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="28"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="28" t="s">
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" s="35" t="s">
         <v>210</v>
       </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
+      <c r="D11" s="34" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="34"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="34"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="34"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="34"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="34"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="34"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="34"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="34"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="34"/>
+    </row>
+    <row r="28" spans="1:1" ht="27">
+      <c r="A28" s="37" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="37" t="s">
+        <v>222</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
+++ b/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="4"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="总体描述" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="228">
   <si>
     <t>测试功能点：查询、插入、更新、分区</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -204,714 +204,757 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>故障场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>业务场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kill -15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kill -11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kill -9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁盘坏道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络错包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网卡故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统掉电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两台机器之间的网络</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障三台机器之间的网络</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障一台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障两台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障三台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预期结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实测结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行步骤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前置条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例编号规则见用例正交表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例编号规则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_AAA_BBB_CCC_DDD：AAA取并发任务序号，BBB取故障场景序号，CCC取业务场景序号,DDD在前三个基础上的细分场景.如sequoiadb_fault_001_001_001_001则为3个insert，不做split，使用kill -15故障一个主节点的场景。还要考虑故障交叉组合的场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_001_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，kill三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群正常，已经split完成，3个并发插入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行1之后操作会报失败，并且在执行步骤2之前会恢复正常，之后一直正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有步骤2之后才能恢复正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一直正常</t>
+  </si>
+  <si>
+    <t>一直正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 主节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 两个主节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 三个主节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 一个备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 同一组内的两个备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 两个不同组的备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 三个不同组的备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一直正常(可能有超时)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_014_010_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，重启一台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.重启一台机器; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重启之后恢复正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_014_011_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_014_012_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，重启两台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，重启三台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.重启两台机器; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.重启三台机器; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优先级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，强杀三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 同一组内的两个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 两个不同组的备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -9 三个不同组的备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作会报失败，自动恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一直正常，且节点自动恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_004_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，一个主节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，两个主节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，三个主节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，一个备节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，两个备节点磁盘满（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，两个备节点磁盘满（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，三个备节点磁盘满（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.两个主节点磁盘满; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.三个主节点磁盘满; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.一个备节点磁盘满; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.两个备节点磁盘满（同一组）; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.两个备节点磁盘满（不同组）; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.三个备节点磁盘满（不同组）; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_002_001_001 kill -11待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>慢盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_005_001_001 慢盘待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拔盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_006_001_001 umount待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_007_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉一个主节点所在的磁盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉两个主节点所在的磁盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉三个主节点所在的磁盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉一个备节点所在的磁盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉两个备节点所在的磁盘（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉两个备节点所在的磁盘（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，拔掉三个备节点所在的磁盘（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.一个主节点磁盘满（往磁盘上灌数据，同时可以看做是慢盘了）; 2.过一定时间恢复磁盘空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉一个主节点所在的磁盘; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉两个主节点所在的磁盘; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉三个主节点所在的磁盘; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉一个备节点所在的磁盘; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉两个备节点所在的磁盘（同一组）; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉两个备节点所在的磁盘（不同组）; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.拔掉三个备节点所在的磁盘（不同组）; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行1之后操作会报失败，并且在执行步骤2之前会恢复正常，之后一直正常？？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有步骤2之后才能恢复正常？？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_008_001_001磁盘坏道待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_009_008_001网络拥塞待补</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_010_008_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发插入过程中，造成两台机器之间丢包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.注入网络丢包; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁盘坏道模拟工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>慢盘模拟工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络丢包、重包、拥塞工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ycsb查询/插入/更新失败时，多久会重试一次，能否设置重试的时间间隔？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ycsb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谭钊波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ycsb分为两个阶段:load和run。第一阶段装置数据如果出错，将报错，并停止执行。第二阶段跑性能测试（其基本操作有read,scan,insert,update,delete ）。第二阶段如果出错，将忽略错误继续进行，并在结果中告知出错的数量。目前没有发现ycsb可以设置重试的选项。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ycsb查询/插入/更新的结果报告格式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ycsb的报告主要包含：总耗时（Runtime），平均吞吐量（Throughput）,总操作数（Operations）,平均耗时（AverageLatency）,最小耗时（MinLatency）,最大耗时（MaxLatency）,整体运行情况（失败多少，成功多少），及性能统计数据（有两种方式呈现，具体请附件1，附件2）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ycsb是否有数据对比工具，比较的流程是什么样的？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂时没发现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ycsb查询出错了，是接着之前的记录往下查？ 还是重新查？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单看查询（就是在run阶段），出错了，是继续往下进行的。它只会把这个查询出错的operation记录一下。我们从结果报告中的Return一项可以看到有多少operation失败了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ycsb查询、插入、更新有没有超时，超时时间多久？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前没发现。超时了估计当错误处理。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试环境:192.168.20.169/170/171 root:sequoiadb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>附件一：以下性能数据表明0-1ms跑完operation的数量为464；1-2ms跑完operation的数据为27；...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>附件二：以下性能数据表明0-2000ms内跑完operation的比例为2.2%；…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>是否做split</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>故障场景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>业务场景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>insert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kill -15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kill -11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kill -9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>umount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>磁盘坏道</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络拥塞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络错包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网卡故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统掉电</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障一个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障一个备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障三个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两个备节点（同一组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障三个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两台机器之间的网络</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障三台机器之间的网络</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障一台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障两台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障三台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>预期结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>实测结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>执行步骤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>前置条件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill一个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例编号规则见用例正交表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例编号规则</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_001_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_AAA_BBB_CCC_DDD：AAA取并发任务序号，BBB取故障场景序号，CCC取业务场景序号,DDD在前三个基础上的细分场景.如sequoiadb_fault_001_001_001_001则为3个insert，不做split，使用kill -15故障一个主节点的场景。还要考虑故障交叉组合的场景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_002_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_003_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill两个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill三个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_004_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_005_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_006_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_001_007_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill一个备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill两个备节点（同一组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill两个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，kill三个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>集群正常，已经split完成，3个并发插入</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>执行1之后操作会报失败，并且在执行步骤2之前会恢复正常，之后一直正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只有步骤2之后才能恢复正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一直正常</t>
-  </si>
-  <si>
-    <t>一直正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 主节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 两个主节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 三个主节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 一个备节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 同一组内的两个备节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 两个不同组的备节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -15 三个不同组的备节点; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一直正常(可能有超时)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_014_010_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，重启一台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.重启一台机器; </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重启之后恢复正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_014_011_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_014_012_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，重启两台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，重启三台机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.重启两台机器; </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.重启三台机器; </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>优先级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_007_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_001_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_002_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_003_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_004_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_005_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_006_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀一个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀两个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀三个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀一个备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀两个备节点（同一组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀两个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，强杀三个备节点（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 两个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 三个主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 一个备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 同一组内的两个备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 两个不同组的备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.kill -9 三个不同组的备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>操作会报失败，自动恢复</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>一直正常，且节点自动恢复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_001_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_002_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_003_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_004_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_005_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_006_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_004_007_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，一个主节点磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，两个主节点磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，三个主节点磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，一个备节点磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，两个备节点磁盘满（同一组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，两个备节点磁盘满（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，三个备节点磁盘满（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.两个主节点磁盘满; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.三个主节点磁盘满; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.一个备节点磁盘满; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.两个备节点磁盘满（同一组）; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.两个备节点磁盘满（不同组）; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.三个备节点磁盘满（不同组）; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_002_001_001 kill -11待补</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>慢盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_005_001_001 慢盘待补</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拔盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_006_001_001 umount待补</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_001_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_002_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_003_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_004_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_005_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_006_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_007_007_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉一个主节点所在的磁盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉两个主节点所在的磁盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉三个主节点所在的磁盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉一个备节点所在的磁盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉两个备节点所在的磁盘（同一组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉两个备节点所在的磁盘（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，拔掉三个备节点所在的磁盘（不同组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.一个主节点磁盘满（往磁盘上灌数据，同时可以看做是慢盘了）; 2.过一定时间恢复磁盘空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉一个主节点所在的磁盘; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉两个主节点所在的磁盘; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉三个主节点所在的磁盘; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉一个备节点所在的磁盘; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉两个备节点所在的磁盘（同一组）; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉两个备节点所在的磁盘（不同组）; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.拔掉三个备节点所在的磁盘（不同组）; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>执行1之后操作会报失败，并且在执行步骤2之前会恢复正常，之后一直正常？？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只有步骤2之后才能恢复正常？？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_008_001_001磁盘坏道待补</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_009_008_001网络拥塞待补</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_010_008_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3个并发插入过程中，造成两台机器之间丢包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.注入网络丢包; 2.过一定时间恢复故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>责任人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>磁盘坏道模拟工具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>慢盘模拟工具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络丢包、重包、拥塞工具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ycsb查询/插入/更新失败时，多久会重试一次，能否设置重试的时间间隔？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ycsb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>谭钊波</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ycsb分为两个阶段:load和run。第一阶段装置数据如果出错，将报错，并停止执行。第二阶段跑性能测试（其基本操作有read,scan,insert,update,delete ）。第二阶段如果出错，将忽略错误继续进行，并在结果中告知出错的数量。目前没有发现ycsb可以设置重试的选项。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ycsb查询/插入/更新的结果报告格式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ycsb的报告主要包含：总耗时（Runtime），平均吞吐量（Throughput）,总操作数（Operations）,平均耗时（AverageLatency）,最小耗时（MinLatency）,最大耗时（MaxLatency）,整体运行情况（失败多少，成功多少），及性能统计数据（有两种方式呈现，具体请附件1，附件2）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ycsb是否有数据对比工具，比较的流程是什么样的？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暂时没发现</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ycsb查询出错了，是接着之前的记录往下查？ 还是重新查？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单看查询（就是在run阶段），出错了，是继续往下进行的。它只会把这个查询出错的operation记录一下。我们从结果报告中的Return一项可以看到有多少operation失败了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ycsb查询、插入、更新有没有超时，超时时间多久？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目前没发现。超时了估计当错误处理。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试环境:192.168.20.169/170/171 root:sequoiadb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>附件一：以下性能数据表明0-1ms跑完operation的数量为464；1-2ms跑完operation的数据为27；...</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>附件二：以下性能数据表明0-2000ms内跑完operation的比例为2.2%；…</t>
+    <r>
+      <t>插入操作会报错。当组选出主之后，恢复正常。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>试了4次，其中第一次发现数据库少了一条记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入操作会报错。当组选出主之后，恢复正常。试了2次，其中第二次进行了两次双强杀的操作。发现数据库少了两条记录。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入操作会报错。当组选出主之后，恢复正常。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>符合预期。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1184,6 +1227,18 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1201,18 +1256,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1906,10 +1949,10 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="32" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -1923,8 +1966,8 @@
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
+      <c r="A3" s="33"/>
+      <c r="B3" s="33"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
@@ -1932,8 +1975,8 @@
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="29"/>
-      <c r="B4" s="30"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="34"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
@@ -1941,8 +1984,8 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="29"/>
-      <c r="B5" s="28" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="32" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -1956,8 +1999,8 @@
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="29"/>
-      <c r="B6" s="29"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="5" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2012,8 @@
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="29"/>
-      <c r="B7" s="30"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -1978,7 +2021,7 @@
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="29"/>
+      <c r="A8" s="33"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1987,7 +2030,7 @@
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="30"/>
+      <c r="A9" s="34"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1996,10 +2039,10 @@
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="32" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -2013,8 +2056,8 @@
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="29"/>
-      <c r="B11" s="29"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="33"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -2022,8 +2065,8 @@
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="29"/>
-      <c r="B12" s="30"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="34"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -2031,8 +2074,8 @@
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="29"/>
-      <c r="B13" s="28" t="s">
+      <c r="A13" s="33"/>
+      <c r="B13" s="32" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -2046,8 +2089,8 @@
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="33"/>
       <c r="C14" s="5" t="s">
         <v>34</v>
       </c>
@@ -2059,8 +2102,8 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="29"/>
-      <c r="B15" s="29"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="33"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -2068,8 +2111,8 @@
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="29"/>
-      <c r="B16" s="30"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="34"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -2077,8 +2120,8 @@
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="29"/>
-      <c r="B17" s="28" t="s">
+      <c r="A17" s="33"/>
+      <c r="B17" s="32" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -2092,8 +2135,8 @@
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="29"/>
-      <c r="B18" s="29"/>
+      <c r="A18" s="33"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="5" t="s">
         <v>14</v>
       </c>
@@ -2105,8 +2148,8 @@
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="29"/>
-      <c r="B19" s="29"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -2114,8 +2157,8 @@
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="30"/>
-      <c r="B20" s="30"/>
+      <c r="A20" s="34"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -2123,10 +2166,10 @@
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="32" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="5" t="s">
@@ -2140,8 +2183,8 @@
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="29"/>
-      <c r="B22" s="29"/>
+      <c r="A22" s="33"/>
+      <c r="B22" s="33"/>
       <c r="C22" s="5" t="s">
         <v>37</v>
       </c>
@@ -2153,8 +2196,8 @@
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="29"/>
-      <c r="B23" s="29"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="33"/>
       <c r="C23" s="5" t="s">
         <v>38</v>
       </c>
@@ -2166,8 +2209,8 @@
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="29"/>
-      <c r="B24" s="29"/>
+      <c r="A24" s="33"/>
+      <c r="B24" s="33"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -2175,8 +2218,8 @@
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="29"/>
-      <c r="B25" s="30"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="34"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -2184,8 +2227,8 @@
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="29"/>
-      <c r="B26" s="28" t="s">
+      <c r="A26" s="33"/>
+      <c r="B26" s="32" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="5" t="s">
@@ -2199,8 +2242,8 @@
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="29"/>
-      <c r="B27" s="29"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="33"/>
       <c r="C27" s="5" t="s">
         <v>40</v>
       </c>
@@ -2212,8 +2255,8 @@
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="30"/>
-      <c r="B28" s="30"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="34"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -2221,12 +2264,12 @@
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="32" t="s">
         <v>19</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>30</v>
@@ -2236,7 +2279,7 @@
       <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="29"/>
+      <c r="A30" s="33"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
         <v>41</v>
@@ -2249,7 +2292,7 @@
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="29"/>
+      <c r="A31" s="33"/>
       <c r="B31" s="3"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -2258,7 +2301,7 @@
       <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="30"/>
+      <c r="A32" s="34"/>
       <c r="B32" s="3"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -2313,25 +2356,25 @@
       <c r="A3" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="33"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="37"/>
       <c r="E3" s="11" t="s">
-        <v>45</v>
+        <v>222</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>43</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K3" s="10" t="s">
         <v>31</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2339,28 +2382,28 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="H4" s="3">
         <v>1</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K4" s="3">
         <v>1</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2368,28 +2411,28 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="H5" s="3">
         <v>2</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K5" s="3">
         <v>2</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2397,28 +2440,28 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>48</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>49</v>
       </c>
       <c r="H6" s="3">
         <v>3</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K6" s="3">
         <v>3</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2426,28 +2469,28 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="H7" s="3">
         <v>4</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K7" s="3">
         <v>4</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2455,28 +2498,28 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H8" s="3">
         <v>5</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K8" s="3">
         <v>5</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2484,28 +2527,28 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H9" s="3">
         <v>6</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K9" s="3">
         <v>6</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2513,28 +2556,28 @@
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H10" s="3">
         <v>7</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K10" s="3">
         <v>7</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2542,22 +2585,22 @@
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H11" s="3">
         <v>8</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2565,16 +2608,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2582,16 +2625,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>52</v>
-      </c>
       <c r="E13" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2599,28 +2642,28 @@
         <v>11</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H14" s="3">
         <v>9</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K14" s="3">
         <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2628,16 +2671,16 @@
         <v>12</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H15" s="3">
         <v>10</v>
@@ -2649,7 +2692,7 @@
         <v>9</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2657,22 +2700,22 @@
         <v>13</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H16" s="3">
         <v>11</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -2680,22 +2723,22 @@
         <v>14</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H17" s="3">
         <v>12</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -2703,22 +2746,22 @@
         <v>15</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H18" s="3">
         <v>13</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -2726,16 +2769,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -2755,13 +2798,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K21" s="3">
         <v>10</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -2769,13 +2812,13 @@
         <v>15</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K22" s="3">
         <v>11</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2783,15 +2826,15 @@
         <v>12</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2815,643 +2858,657 @@
     <col min="4" max="4" width="26" style="17" customWidth="1"/>
     <col min="5" max="5" width="40.625" style="17" customWidth="1"/>
     <col min="6" max="6" width="30" style="17" customWidth="1"/>
-    <col min="7" max="7" width="23.625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="23.625" style="17" customWidth="1"/>
     <col min="8" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="F3" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>77</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A4" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B4" s="21"/>
       <c r="C4" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="F4" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="G4" s="21"/>
+      <c r="G4" s="22"/>
     </row>
     <row r="5" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A5" s="21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D5" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="G5" s="21"/>
+      <c r="G5" s="22"/>
     </row>
     <row r="6" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A6" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D6" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="E6" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="G6" s="21"/>
+      <c r="G6" s="22"/>
     </row>
     <row r="7" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A7" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B7" s="21"/>
       <c r="C7" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="G7" s="21"/>
+        <v>102</v>
+      </c>
+      <c r="G7" s="22"/>
     </row>
     <row r="8" spans="1:7" ht="24">
       <c r="A8" s="21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B8" s="21"/>
       <c r="C8" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="G8" s="14"/>
+        <v>100</v>
+      </c>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:7" ht="24">
       <c r="A9" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" s="21"/>
       <c r="C9" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="G9" s="14"/>
+        <v>102</v>
+      </c>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7" ht="24">
       <c r="A10" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="D10" s="22" t="s">
-        <v>99</v>
-      </c>
       <c r="E10" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="G10" s="14"/>
+        <v>102</v>
+      </c>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7" ht="24">
       <c r="A11" s="24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="20"/>
       <c r="D11" s="20"/>
       <c r="E11" s="20"/>
       <c r="F11" s="20"/>
-      <c r="G11" s="19"/>
-    </row>
-    <row r="12" spans="1:7" ht="24">
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:7" ht="48">
       <c r="A12" s="21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="G12" s="21"/>
-    </row>
-    <row r="13" spans="1:7" ht="24">
+        <v>223</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="48">
       <c r="A13" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="G13" s="21"/>
+        <v>145</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="24">
       <c r="A14" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="G14" s="21"/>
+        <v>145</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="24">
       <c r="A15" s="21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="G15" s="21"/>
+        <v>146</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="24">
       <c r="A16" s="21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="G16" s="21"/>
+        <v>145</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="17" spans="1:7" ht="24">
       <c r="A17" s="21" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="G17" s="21"/>
+        <v>146</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="18" spans="1:7" ht="24">
       <c r="A18" s="21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B18" s="21"/>
       <c r="C18" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="G18" s="21"/>
+        <v>146</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="19" spans="1:7" ht="24">
       <c r="A19" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="19"/>
+      <c r="G19" s="20"/>
     </row>
     <row r="20" spans="1:7" ht="24">
       <c r="A20" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F20" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="19"/>
+      <c r="G20" s="20"/>
     </row>
     <row r="21" spans="1:7" ht="24">
       <c r="A21" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="19"/>
+      <c r="G21" s="20"/>
     </row>
     <row r="22" spans="1:7" ht="24">
       <c r="A22" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="G22" s="19"/>
+        <v>102</v>
+      </c>
+      <c r="G22" s="20"/>
     </row>
     <row r="23" spans="1:7" ht="24">
       <c r="A23" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="G23" s="19"/>
+        <v>102</v>
+      </c>
+      <c r="G23" s="20"/>
     </row>
     <row r="24" spans="1:7" ht="24">
       <c r="A24" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="G24" s="19"/>
+        <v>102</v>
+      </c>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" spans="1:7" ht="24">
       <c r="A25" s="19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B25" s="19"/>
       <c r="C25" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="G25" s="19"/>
+        <v>102</v>
+      </c>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:7" ht="24">
       <c r="A26" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
-      <c r="G26" s="14"/>
+      <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" ht="24">
       <c r="A27" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
-      <c r="G27" s="14"/>
+      <c r="G27" s="16"/>
     </row>
     <row r="28" spans="1:7" ht="24">
       <c r="A28" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="G28" s="19"/>
+        <v>194</v>
+      </c>
+      <c r="G28" s="20"/>
     </row>
     <row r="29" spans="1:7" ht="24">
       <c r="A29" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B29" s="19"/>
       <c r="C29" s="20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="G29" s="19"/>
+        <v>194</v>
+      </c>
+      <c r="G29" s="20"/>
     </row>
     <row r="30" spans="1:7" ht="24">
       <c r="A30" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B30" s="19"/>
       <c r="C30" s="20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="G30" s="19"/>
+        <v>194</v>
+      </c>
+      <c r="G30" s="20"/>
     </row>
     <row r="31" spans="1:7" ht="24">
       <c r="A31" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B31" s="19"/>
       <c r="C31" s="20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G31" s="19"/>
+        <v>101</v>
+      </c>
+      <c r="G31" s="20"/>
     </row>
     <row r="32" spans="1:7" ht="24">
       <c r="A32" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="G32" s="19"/>
+        <v>195</v>
+      </c>
+      <c r="G32" s="20"/>
     </row>
     <row r="33" spans="1:7" ht="24">
       <c r="A33" s="19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B33" s="19"/>
       <c r="C33" s="20" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G33" s="19"/>
+        <v>101</v>
+      </c>
+      <c r="G33" s="20"/>
     </row>
     <row r="34" spans="1:7" ht="24">
       <c r="A34" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G34" s="19"/>
+        <v>101</v>
+      </c>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" spans="1:7" ht="24">
       <c r="A35" s="25" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B35" s="14"/>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
       <c r="F35" s="16"/>
-      <c r="G35" s="14"/>
+      <c r="G35" s="16"/>
     </row>
     <row r="36" spans="1:7" ht="24">
       <c r="A36" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B36" s="14"/>
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
       <c r="F36" s="16"/>
-      <c r="G36" s="14"/>
+      <c r="G36" s="16"/>
     </row>
     <row r="37" spans="1:7" ht="24">
       <c r="A37" s="21" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E37" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="D37" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>201</v>
-      </c>
       <c r="F37" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="G37" s="14"/>
+        <v>110</v>
+      </c>
+      <c r="G37" s="16"/>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="16"/>
@@ -3460,7 +3517,7 @@
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="16"/>
-      <c r="G38" s="14"/>
+      <c r="G38" s="16"/>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="16"/>
@@ -3469,7 +3526,7 @@
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="16"/>
-      <c r="G39" s="14"/>
+      <c r="G39" s="16"/>
     </row>
     <row r="40" spans="1:7">
       <c r="C40" s="9"/>
@@ -3484,7 +3541,7 @@
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
       <c r="F41" s="16"/>
-      <c r="G41" s="14"/>
+      <c r="G41" s="16"/>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="14"/>
@@ -3493,64 +3550,64 @@
       <c r="D42" s="16"/>
       <c r="E42" s="16"/>
       <c r="F42" s="16"/>
-      <c r="G42" s="14"/>
+      <c r="G42" s="16"/>
     </row>
     <row r="43" spans="1:7" ht="24">
       <c r="A43" s="21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B43" s="21"/>
       <c r="C43" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E43" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="D43" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="E43" s="16" t="s">
+      <c r="F43" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="F43" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="G43" s="14"/>
+      <c r="G43" s="16"/>
     </row>
     <row r="44" spans="1:7" ht="24">
       <c r="A44" s="21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="G44" s="14"/>
+        <v>116</v>
+      </c>
+      <c r="G44" s="16"/>
     </row>
     <row r="45" spans="1:7" ht="24">
       <c r="A45" s="21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="G45" s="14"/>
+        <v>116</v>
+      </c>
+      <c r="G45" s="16"/>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="14"/>
@@ -3559,7 +3616,7 @@
       <c r="D46" s="16"/>
       <c r="E46" s="16"/>
       <c r="F46" s="16"/>
-      <c r="G46" s="14"/>
+      <c r="G46" s="16"/>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="14"/>
@@ -3568,7 +3625,7 @@
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
       <c r="F47" s="16"/>
-      <c r="G47" s="14"/>
+      <c r="G47" s="16"/>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="14"/>
@@ -3577,7 +3634,7 @@
       <c r="D48" s="16"/>
       <c r="E48" s="16"/>
       <c r="F48" s="16"/>
-      <c r="G48" s="14"/>
+      <c r="G48" s="16"/>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="14"/>
@@ -3586,7 +3643,7 @@
       <c r="D49" s="16"/>
       <c r="E49" s="16"/>
       <c r="F49" s="16"/>
-      <c r="G49" s="14"/>
+      <c r="G49" s="16"/>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="14"/>
@@ -3595,7 +3652,7 @@
       <c r="D50" s="16"/>
       <c r="E50" s="16"/>
       <c r="F50" s="16"/>
-      <c r="G50" s="14"/>
+      <c r="G50" s="16"/>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="14"/>
@@ -3604,7 +3661,7 @@
       <c r="D51" s="16"/>
       <c r="E51" s="16"/>
       <c r="F51" s="16"/>
-      <c r="G51" s="14"/>
+      <c r="G51" s="16"/>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="14"/>
@@ -3613,7 +3670,7 @@
       <c r="D52" s="16"/>
       <c r="E52" s="16"/>
       <c r="F52" s="16"/>
-      <c r="G52" s="14"/>
+      <c r="G52" s="16"/>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="14"/>
@@ -3622,7 +3679,7 @@
       <c r="D53" s="16"/>
       <c r="E53" s="16"/>
       <c r="F53" s="16"/>
-      <c r="G53" s="14"/>
+      <c r="G53" s="16"/>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="14"/>
@@ -3631,7 +3688,7 @@
       <c r="D54" s="16"/>
       <c r="E54" s="16"/>
       <c r="F54" s="16"/>
-      <c r="G54" s="14"/>
+      <c r="G54" s="16"/>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="14"/>
@@ -3640,7 +3697,7 @@
       <c r="D55" s="16"/>
       <c r="E55" s="16"/>
       <c r="F55" s="16"/>
-      <c r="G55" s="14"/>
+      <c r="G55" s="16"/>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="14"/>
@@ -3649,7 +3706,7 @@
       <c r="D56" s="16"/>
       <c r="E56" s="16"/>
       <c r="F56" s="16"/>
-      <c r="G56" s="14"/>
+      <c r="G56" s="16"/>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="14"/>
@@ -3658,7 +3715,7 @@
       <c r="D57" s="16"/>
       <c r="E57" s="16"/>
       <c r="F57" s="16"/>
-      <c r="G57" s="14"/>
+      <c r="G57" s="16"/>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="14"/>
@@ -3667,7 +3724,7 @@
       <c r="D58" s="16"/>
       <c r="E58" s="16"/>
       <c r="F58" s="16"/>
-      <c r="G58" s="14"/>
+      <c r="G58" s="16"/>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="14"/>
@@ -3676,7 +3733,7 @@
       <c r="D59" s="16"/>
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
-      <c r="G59" s="14"/>
+      <c r="G59" s="16"/>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="14"/>
@@ -3685,7 +3742,7 @@
       <c r="D60" s="16"/>
       <c r="E60" s="16"/>
       <c r="F60" s="16"/>
-      <c r="G60" s="14"/>
+      <c r="G60" s="16"/>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="14"/>
@@ -3694,7 +3751,7 @@
       <c r="D61" s="16"/>
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
-      <c r="G61" s="14"/>
+      <c r="G61" s="16"/>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="14"/>
@@ -3703,7 +3760,7 @@
       <c r="D62" s="16"/>
       <c r="E62" s="16"/>
       <c r="F62" s="16"/>
-      <c r="G62" s="14"/>
+      <c r="G62" s="16"/>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="14"/>
@@ -3712,7 +3769,7 @@
       <c r="D63" s="16"/>
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
-      <c r="G63" s="14"/>
+      <c r="G63" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:G3"/>
@@ -3728,170 +3785,170 @@
   <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="69.625" style="37" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9" style="36"/>
-    <col min="4" max="4" width="45.25" style="37" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="36"/>
+    <col min="1" max="1" width="69.625" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9" style="30"/>
+    <col min="4" max="4" width="45.25" style="31" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="30"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="34"/>
-      <c r="B1" s="35" t="s">
+      <c r="A1" s="28"/>
+      <c r="B1" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="D1" s="28"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="D1" s="34"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="34" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="28"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="34"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="34" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="28"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="28"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="28"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="34"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="34"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="34"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="34" t="s">
+      <c r="B5" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="C5" s="29"/>
+      <c r="D5" s="28"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="28"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="28"/>
+    </row>
+    <row r="7" spans="1:4" ht="81">
+      <c r="A7" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="34"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="34"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="34"/>
-    </row>
-    <row r="7" spans="1:4" ht="81">
-      <c r="A7" s="34" t="s">
+      <c r="B7" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="C7" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="D7" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="D7" s="34" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="81">
+      <c r="A8" s="28" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="81">
-      <c r="A8" s="34" t="s">
+      <c r="B8" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="D8" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="B8" s="35" t="s">
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="C9" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="C8" s="35" t="s">
-        <v>210</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="34" t="s">
+      <c r="D9" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="B9" s="35" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="54">
+      <c r="A10" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="C10" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="C9" s="35" t="s">
-        <v>210</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="54">
-      <c r="A10" s="34" t="s">
+      <c r="D10" s="28" t="s">
         <v>216</v>
       </c>
-      <c r="B10" s="35" t="s">
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="C11" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="C10" s="35" t="s">
-        <v>210</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="34" t="s">
+      <c r="D11" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="B11" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>210</v>
-      </c>
-      <c r="D11" s="34" t="s">
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="28"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="28"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="28"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="28"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="28"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="28"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="28" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="34"/>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="34"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="34"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="34"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="34"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="34"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="34"/>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="34"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="34" t="s">
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="28"/>
+    </row>
+    <row r="28" spans="1:1" ht="27">
+      <c r="A28" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="34"/>
-    </row>
-    <row r="28" spans="1:1" ht="27">
-      <c r="A28" s="37" t="s">
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="31" t="s">
         <v>221</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="37" t="s">
-        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
+++ b/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="273">
   <si>
     <t>测试功能点：查询、插入、更新、分区</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -955,6 +955,186 @@
   </si>
   <si>
     <t>符合预期。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_001_00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_002_00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_003_00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_004_00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_005_00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_006_00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_007_00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群正常，已经split完成，已经入库100000条数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群正常，已经split完成，3已经入库100000条数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作有可能（当从该主读时）会报失败，自动恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作有可能（当从该备读时）会报失败，自动恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>符合预期。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_001_007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_002_007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_003_007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_004_007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_005_007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_006_007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_007_007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_001_008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_002_008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_003_008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_004_008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_005_008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_006_008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_007_008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_001_00X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发查询过程中，强杀一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发查询过程中，强杀两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发查询过程中，强杀三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发查询过程中，强杀一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发查询过程中，强杀两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发查询过程中，强杀两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发查询过程中，强杀三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发更新过程中，强杀一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发更新过程中，强杀两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发更新过程中，强杀三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发更新过程中，强杀一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发更新过程中，强杀两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发更新过程中，强杀两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3个并发更新过程中，强杀三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作会报失败，被强杀的节点自动恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作正常，被强杀的节点自动恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预期剩下的主节点会在心跳时间间隔内能正常工作，若在心跳时间间隔内两备被拉起，整个集群就像没发生过故障一样。若在心跳时间间隔内，两备没被拉起，主节点将降备，操作异常，但最终整个组能恢复正常。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2385,10 +2565,10 @@
         <v>47</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>47</v>
+        <v>240</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>47</v>
+        <v>240</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>48</v>
@@ -2849,7 +3029,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="27.875" style="9" customWidth="1"/>
@@ -3182,507 +3362,702 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="24">
-      <c r="A19" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G19" s="20"/>
+      <c r="A19" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="20" spans="1:7" ht="24">
-      <c r="A20" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G20" s="20"/>
+      <c r="A20" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="21" spans="1:7" ht="24">
-      <c r="A21" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G21" s="20"/>
+      <c r="A21" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="22" spans="1:7" ht="24">
-      <c r="A22" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G22" s="20"/>
+      <c r="A22" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="G22" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="23" spans="1:7" ht="24">
-      <c r="A23" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G23" s="20"/>
+      <c r="A23" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="24" spans="1:7" ht="24">
-      <c r="A24" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G24" s="20"/>
+      <c r="A24" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="25" spans="1:7" ht="24">
-      <c r="A25" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G25" s="20"/>
+      <c r="A25" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="26" spans="1:7" ht="24">
-      <c r="A26" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
+      <c r="A26" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="27" spans="1:7" ht="24">
-      <c r="A27" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
+      <c r="A27" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="28" spans="1:7" ht="24">
-      <c r="A28" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="F28" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="G28" s="20"/>
+      <c r="A28" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="G28" s="22" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="29" spans="1:7" ht="24">
-      <c r="A29" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="F29" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="G29" s="20"/>
-    </row>
-    <row r="30" spans="1:7" ht="24">
-      <c r="A30" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E30" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="G30" s="20"/>
+      <c r="A29" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="72">
+      <c r="A30" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="B30" s="21"/>
+      <c r="C30" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="G30" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="31" spans="1:7" ht="24">
-      <c r="A31" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="B31" s="19"/>
-      <c r="C31" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="G31" s="20"/>
+      <c r="A31" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="G31" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="32" spans="1:7" ht="24">
-      <c r="A32" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E32" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="F32" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="G32" s="20"/>
+      <c r="A32" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F32" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="G32" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="33" spans="1:7" ht="24">
-      <c r="A33" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="G33" s="20"/>
+      <c r="A33" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="B33" s="21"/>
+      <c r="C33" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="34" spans="1:7" ht="24">
-      <c r="A34" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E34" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="F34" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="G34" s="20"/>
+      <c r="A34" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="B34" s="21"/>
+      <c r="C34" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="35" spans="1:7" ht="24">
-      <c r="A35" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
+      <c r="A35" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="36" spans="1:7" ht="24">
-      <c r="A36" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
+      <c r="A36" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="37" spans="1:7" ht="24">
       <c r="A37" s="21" t="s">
-        <v>198</v>
+        <v>232</v>
       </c>
       <c r="B37" s="21"/>
-      <c r="C37" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="F37" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="G37" s="16"/>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="16"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="16"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="21"/>
+      <c r="C37" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="24">
+      <c r="A38" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="24">
+      <c r="A39" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="B39" s="21"/>
+      <c r="C39" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="24">
+      <c r="A40" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="B40" s="21"/>
+      <c r="C40" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E40" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="24">
+      <c r="A41" s="21" t="s">
+        <v>229</v>
+      </c>
       <c r="B41" s="21"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="14"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
+      <c r="C41" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="D41" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E41" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="24">
+      <c r="A42" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B42" s="21"/>
+      <c r="C42" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="D42" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E42" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="43" spans="1:7" ht="24">
       <c r="A43" s="21" t="s">
-        <v>113</v>
+        <v>231</v>
       </c>
       <c r="B43" s="21"/>
-      <c r="C43" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="F43" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="G43" s="16"/>
+      <c r="C43" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="D43" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E43" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="44" spans="1:7" ht="24">
       <c r="A44" s="21" t="s">
-        <v>117</v>
+        <v>232</v>
       </c>
       <c r="B44" s="21"/>
-      <c r="C44" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E44" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="F44" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="G44" s="16"/>
+      <c r="C44" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="D44" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E44" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="45" spans="1:7" ht="24">
       <c r="A45" s="21" t="s">
-        <v>118</v>
+        <v>233</v>
       </c>
       <c r="B45" s="21"/>
-      <c r="C45" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="D45" s="16" t="s">
+      <c r="C45" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="D45" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="E45" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="24">
+      <c r="A46" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="B46" s="21"/>
+      <c r="C46" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="D46" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E46" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="24">
+      <c r="A47" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B47" s="19"/>
+      <c r="C47" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="D47" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E45" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F45" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="G45" s="16"/>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="14"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="14"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="14"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="14"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="14"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="14"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="14"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="14"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="14"/>
+      <c r="E47" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G47" s="20"/>
+    </row>
+    <row r="48" spans="1:7" ht="24">
+      <c r="A48" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="B48" s="19"/>
+      <c r="C48" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G48" s="20"/>
+    </row>
+    <row r="49" spans="1:7" ht="24">
+      <c r="A49" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" s="19"/>
+      <c r="C49" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="D49" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G49" s="20"/>
+    </row>
+    <row r="50" spans="1:7" ht="24">
+      <c r="A50" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" s="19"/>
+      <c r="C50" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G50" s="20"/>
+    </row>
+    <row r="51" spans="1:7" ht="24">
+      <c r="A51" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="B51" s="19"/>
+      <c r="C51" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="D51" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="F51" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G51" s="20"/>
+    </row>
+    <row r="52" spans="1:7" ht="24">
+      <c r="A52" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="B52" s="19"/>
+      <c r="C52" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="D52" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="F52" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G52" s="20"/>
+    </row>
+    <row r="53" spans="1:7" ht="24">
+      <c r="A53" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B53" s="19"/>
+      <c r="C53" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="D53" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F53" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G53" s="20"/>
+    </row>
+    <row r="54" spans="1:7" ht="24">
+      <c r="A54" s="25" t="s">
+        <v>169</v>
+      </c>
       <c r="B54" s="14"/>
       <c r="C54" s="16"/>
       <c r="D54" s="16"/>
@@ -3690,8 +4065,10 @@
       <c r="F54" s="16"/>
       <c r="G54" s="16"/>
     </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="14"/>
+    <row r="55" spans="1:7" ht="24">
+      <c r="A55" s="26" t="s">
+        <v>171</v>
+      </c>
       <c r="B55" s="14"/>
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
@@ -3699,77 +4076,440 @@
       <c r="F55" s="16"/>
       <c r="G55" s="16"/>
     </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="14"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="14"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16"/>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="14"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="14"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="14"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="16"/>
-      <c r="D60" s="16"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16"/>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="14"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="16"/>
-      <c r="D61" s="16"/>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="16"/>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="14"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="16"/>
-      <c r="D62" s="16"/>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="16"/>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="14"/>
+    <row r="56" spans="1:7" ht="24">
+      <c r="A56" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="B56" s="19"/>
+      <c r="C56" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="D56" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="F56" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G56" s="20"/>
+    </row>
+    <row r="57" spans="1:7" ht="24">
+      <c r="A57" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="B57" s="19"/>
+      <c r="C57" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="D57" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="F57" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G57" s="20"/>
+    </row>
+    <row r="58" spans="1:7" ht="24">
+      <c r="A58" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58" s="19"/>
+      <c r="C58" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="D58" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="F58" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G58" s="20"/>
+    </row>
+    <row r="59" spans="1:7" ht="24">
+      <c r="A59" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" s="19"/>
+      <c r="C59" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="D59" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="F59" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="G59" s="20"/>
+    </row>
+    <row r="60" spans="1:7" ht="24">
+      <c r="A60" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B60" s="19"/>
+      <c r="C60" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="D60" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="F60" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="G60" s="20"/>
+    </row>
+    <row r="61" spans="1:7" ht="24">
+      <c r="A61" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B61" s="19"/>
+      <c r="C61" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D61" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="F61" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="G61" s="20"/>
+    </row>
+    <row r="62" spans="1:7" ht="24">
+      <c r="A62" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B62" s="19"/>
+      <c r="C62" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="D62" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F62" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="G62" s="20"/>
+    </row>
+    <row r="63" spans="1:7" ht="24">
+      <c r="A63" s="25" t="s">
+        <v>196</v>
+      </c>
       <c r="B63" s="14"/>
       <c r="C63" s="16"/>
       <c r="D63" s="16"/>
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
       <c r="G63" s="16"/>
+    </row>
+    <row r="64" spans="1:7" ht="24">
+      <c r="A64" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="B64" s="14"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="16"/>
+    </row>
+    <row r="65" spans="1:7" ht="24">
+      <c r="A65" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="B65" s="21"/>
+      <c r="C65" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="D65" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E65" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="F65" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G65" s="16"/>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="16"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="16"/>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="16"/>
+      <c r="B67" s="14"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="16"/>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="9"/>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="21"/>
+      <c r="B69" s="21"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="16"/>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="14"/>
+      <c r="B70" s="14"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="16"/>
+    </row>
+    <row r="71" spans="1:7" ht="24">
+      <c r="A71" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B71" s="21"/>
+      <c r="C71" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E71" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="F71" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="G71" s="16"/>
+    </row>
+    <row r="72" spans="1:7" ht="24">
+      <c r="A72" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B72" s="21"/>
+      <c r="C72" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E72" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F72" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="G72" s="16"/>
+    </row>
+    <row r="73" spans="1:7" ht="24">
+      <c r="A73" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B73" s="21"/>
+      <c r="C73" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D73" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E73" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F73" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="G73" s="16"/>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="14"/>
+      <c r="B74" s="14"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="14"/>
+      <c r="B75" s="14"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16"/>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="14"/>
+      <c r="B76" s="14"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="16"/>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="14"/>
+      <c r="B77" s="14"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="16"/>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="14"/>
+      <c r="B78" s="14"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16"/>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="14"/>
+      <c r="B79" s="14"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16"/>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="14"/>
+      <c r="B80" s="14"/>
+      <c r="C80" s="16"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="16"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="16"/>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="14"/>
+      <c r="B81" s="14"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="16"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="16"/>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="14"/>
+      <c r="B82" s="14"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="16"/>
+      <c r="E82" s="16"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="16"/>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="14"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16"/>
+      <c r="F83" s="16"/>
+      <c r="G83" s="16"/>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="14"/>
+      <c r="B84" s="14"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="16"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="16"/>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="14"/>
+      <c r="B85" s="14"/>
+      <c r="C85" s="16"/>
+      <c r="D85" s="16"/>
+      <c r="E85" s="16"/>
+      <c r="F85" s="16"/>
+      <c r="G85" s="16"/>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="14"/>
+      <c r="B86" s="14"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="16"/>
+      <c r="E86" s="16"/>
+      <c r="F86" s="16"/>
+      <c r="G86" s="16"/>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="14"/>
+      <c r="B87" s="14"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="16"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="16"/>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="14"/>
+      <c r="B88" s="14"/>
+      <c r="C88" s="16"/>
+      <c r="D88" s="16"/>
+      <c r="E88" s="16"/>
+      <c r="F88" s="16"/>
+      <c r="G88" s="16"/>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="14"/>
+      <c r="B89" s="14"/>
+      <c r="C89" s="16"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="16"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="16"/>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="14"/>
+      <c r="B90" s="14"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="16"/>
+      <c r="E90" s="16"/>
+      <c r="F90" s="16"/>
+      <c r="G90" s="16"/>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="14"/>
+      <c r="B91" s="14"/>
+      <c r="C91" s="16"/>
+      <c r="D91" s="16"/>
+      <c r="E91" s="16"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:G3"/>

--- a/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
+++ b/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="349">
   <si>
     <t>测试功能点：查询、插入、更新、分区</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1135,6 +1135,310 @@
   </si>
   <si>
     <t>预期剩下的主节点会在心跳时间间隔内能正常工作，若在心跳时间间隔内两备被拉起，整个集群就像没发生过故障一样。若在心跳时间间隔内，两备没被拉起，主节点将降备，操作异常，但最终整个组能恢复正常。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_001_002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_002_002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_003_002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_004_002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_005_002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_006_002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_007_002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_001_003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_002_003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_003_003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_004_003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_005_003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_006_003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_007_003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作会报失败，自动恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作会报失败，自动恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_001_004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_002_004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_003_004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_004_004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_005_004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_006_004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_007_004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_001_005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_002_005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_003_005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_004_005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_005_005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_006_005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_007_005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_001_006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_002_006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_003_006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_004_006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_005_006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_006_006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_007_006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入、更新（3.3:6.7）过程中，强杀一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入、更新（3.3:6.7）过程中，强杀两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入、更新（3.3:6.7）过程中，强杀三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入、更新（3.3:6.7）过程中，强杀一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入、更新（3.3:6.7）过程中，强杀两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入、更新（3.3:6.7）过程中，强杀两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入、更新（3.3:6.7）过程中，强杀三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一直正常，且节点自动恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预期剩下的主节点会在心跳时间间隔内能正常工作，若在心跳时间间隔内两备被拉起，整个集群就像没发生过故障一样。若在心跳时间间隔内，两备没被拉起，主节点将降备，操作异常，但最终整个组能恢复正常。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入、查询（3.3:6.7）过程中，强杀一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入、查询（3.3:6.7）过程中，强杀两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入、查询（3.3:6.7）过程中，强杀三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入、查询（3.3:6.7）过程中，强杀一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入、查询（3.3:6.7）过程中，强杀两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入、查询（3.3:6.7）过程中，强杀两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入、查询（3.3:6.7）过程中，强杀三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做查询，更新（3.3:6.7）过程中，强杀一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做查询，更新（3.3:6.7）过程中，强杀两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做查询，更新（3.3:6.7）过程中，强杀三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做查询，更新（3.3:6.7）过程中，强杀一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做查询，更新（3.3:6.7）过程中，强杀两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做查询，更新（3.3:6.7）过程中，强杀两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做查询，更新（3.3:6.7）过程中，强杀三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做查询，更新（6.7：3.3）过程中，强杀一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做查询，更新（6.7：3.3）过程中，强杀两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做查询，更新（6.7：3.3）过程中，强杀三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做查询，更新（6.7：3.3）过程中，强杀一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做查询，更新（6.7：3.3）过程中，强杀两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做查询，更新（6.7：3.3）过程中，强杀两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做查询，更新（6.7：3.3）过程中，强杀三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入，更新，查询（3.4:3.3:3.3）过程中，强杀一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入，更新，查询（3.4:3.3:3.3）过程中，强杀两个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入，更新，查询（3.4:3.3:3.3）过程中，强杀三个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入，更新，查询（3.4:3.3:3.3）过程中，强杀一个备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入，更新，查询（3.4:3.3:3.3）过程中，强杀两个备节点（同一组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入，更新，查询（3.4:3.3:3.3）过程中，强杀两个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发做插入，更新，查询（3.4:3.3:3.3）过程中，强杀三个备节点（不同组）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当查询发生在该备上时，操作会失败。失败后，节点自动恢复。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当查询发生在这些备上时，操作会失败。失败后，节点自动恢复。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1356,7 +1660,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1436,6 +1740,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3029,7 +3336,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="27.875" style="9" customWidth="1"/>
@@ -3250,7 +3557,7 @@
         <v>139</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>145</v>
+        <v>287</v>
       </c>
       <c r="G13" s="22" t="s">
         <v>225</v>
@@ -3361,13 +3668,13 @@
         <v>227</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="24">
+    <row r="19" spans="1:7" ht="36">
       <c r="A19" s="21" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="22" t="s">
-        <v>256</v>
+        <v>340</v>
       </c>
       <c r="D19" s="22" t="s">
         <v>235</v>
@@ -3376,19 +3683,19 @@
         <v>138</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>237</v>
+        <v>288</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="24">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="36">
       <c r="A20" s="21" t="s">
-        <v>242</v>
+        <v>274</v>
       </c>
       <c r="B20" s="21"/>
       <c r="C20" s="22" t="s">
-        <v>257</v>
+        <v>341</v>
       </c>
       <c r="D20" s="22" t="s">
         <v>235</v>
@@ -3397,19 +3704,19 @@
         <v>139</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>237</v>
+        <v>288</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="24">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="36">
       <c r="A21" s="21" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="22" t="s">
-        <v>258</v>
+        <v>342</v>
       </c>
       <c r="D21" s="22" t="s">
         <v>235</v>
@@ -3418,19 +3725,19 @@
         <v>140</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>237</v>
+        <v>288</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="24">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="36">
       <c r="A22" s="21" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="B22" s="21"/>
       <c r="C22" s="22" t="s">
-        <v>259</v>
+        <v>343</v>
       </c>
       <c r="D22" s="22" t="s">
         <v>235</v>
@@ -3439,19 +3746,19 @@
         <v>141</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>238</v>
+        <v>317</v>
       </c>
       <c r="G22" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="24">
+    <row r="23" spans="1:7" ht="72">
       <c r="A23" s="21" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="B23" s="21"/>
       <c r="C23" s="22" t="s">
-        <v>260</v>
+        <v>344</v>
       </c>
       <c r="D23" s="22" t="s">
         <v>235</v>
@@ -3460,19 +3767,19 @@
         <v>142</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>238</v>
+        <v>318</v>
       </c>
       <c r="G23" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="24">
+    <row r="24" spans="1:7" ht="36">
       <c r="A24" s="21" t="s">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="22" t="s">
-        <v>261</v>
+        <v>345</v>
       </c>
       <c r="D24" s="22" t="s">
         <v>236</v>
@@ -3481,19 +3788,19 @@
         <v>143</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>238</v>
+        <v>317</v>
       </c>
       <c r="G24" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="24">
+    <row r="25" spans="1:7" ht="36">
       <c r="A25" s="21" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="22" t="s">
-        <v>262</v>
+        <v>346</v>
       </c>
       <c r="D25" s="22" t="s">
         <v>235</v>
@@ -3502,19 +3809,19 @@
         <v>144</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>238</v>
+        <v>317</v>
       </c>
       <c r="G25" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="24">
+    <row r="26" spans="1:7" ht="36">
       <c r="A26" s="21" t="s">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="22" t="s">
-        <v>263</v>
+        <v>310</v>
       </c>
       <c r="D26" s="22" t="s">
         <v>235</v>
@@ -3523,19 +3830,19 @@
         <v>138</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="24">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="36">
       <c r="A27" s="21" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="22" t="s">
-        <v>264</v>
+        <v>311</v>
       </c>
       <c r="D27" s="22" t="s">
         <v>235</v>
@@ -3544,19 +3851,19 @@
         <v>139</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="24">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="36">
       <c r="A28" s="21" t="s">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="22" t="s">
-        <v>265</v>
+        <v>312</v>
       </c>
       <c r="D28" s="22" t="s">
         <v>235</v>
@@ -3565,19 +3872,19 @@
         <v>140</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="24">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="36">
       <c r="A29" s="21" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="22" t="s">
-        <v>266</v>
+        <v>313</v>
       </c>
       <c r="D29" s="22" t="s">
         <v>235</v>
@@ -3586,7 +3893,7 @@
         <v>141</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>271</v>
+        <v>317</v>
       </c>
       <c r="G29" s="22" t="s">
         <v>227</v>
@@ -3594,11 +3901,11 @@
     </row>
     <row r="30" spans="1:7" ht="72">
       <c r="A30" s="21" t="s">
-        <v>252</v>
+        <v>284</v>
       </c>
       <c r="B30" s="21"/>
       <c r="C30" s="22" t="s">
-        <v>267</v>
+        <v>314</v>
       </c>
       <c r="D30" s="22" t="s">
         <v>235</v>
@@ -3607,19 +3914,19 @@
         <v>142</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>272</v>
+        <v>318</v>
       </c>
       <c r="G30" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="24">
+    <row r="31" spans="1:7" ht="36">
       <c r="A31" s="21" t="s">
-        <v>253</v>
+        <v>285</v>
       </c>
       <c r="B31" s="21"/>
       <c r="C31" s="22" t="s">
-        <v>268</v>
+        <v>315</v>
       </c>
       <c r="D31" s="22" t="s">
         <v>236</v>
@@ -3628,19 +3935,19 @@
         <v>143</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>271</v>
+        <v>317</v>
       </c>
       <c r="G31" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="24">
+    <row r="32" spans="1:7" ht="36">
       <c r="A32" s="21" t="s">
-        <v>254</v>
+        <v>286</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="22" t="s">
-        <v>269</v>
+        <v>316</v>
       </c>
       <c r="D32" s="22" t="s">
         <v>235</v>
@@ -3649,19 +3956,19 @@
         <v>144</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>271</v>
+        <v>317</v>
       </c>
       <c r="G32" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="24">
+    <row r="33" spans="1:7" ht="36">
       <c r="A33" s="21" t="s">
-        <v>228</v>
+        <v>289</v>
       </c>
       <c r="B33" s="21"/>
       <c r="C33" s="22" t="s">
-        <v>131</v>
+        <v>319</v>
       </c>
       <c r="D33" s="22" t="s">
         <v>235</v>
@@ -3669,18 +3976,20 @@
       <c r="E33" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="F33" s="22"/>
+      <c r="F33" s="22" t="s">
+        <v>288</v>
+      </c>
       <c r="G33" s="22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="24">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="36">
       <c r="A34" s="21" t="s">
-        <v>229</v>
+        <v>290</v>
       </c>
       <c r="B34" s="21"/>
       <c r="C34" s="22" t="s">
-        <v>132</v>
+        <v>320</v>
       </c>
       <c r="D34" s="22" t="s">
         <v>235</v>
@@ -3688,18 +3997,20 @@
       <c r="E34" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="F34" s="22"/>
+      <c r="F34" s="22" t="s">
+        <v>288</v>
+      </c>
       <c r="G34" s="22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="24">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="36">
       <c r="A35" s="21" t="s">
-        <v>230</v>
+        <v>291</v>
       </c>
       <c r="B35" s="21"/>
       <c r="C35" s="22" t="s">
-        <v>133</v>
+        <v>321</v>
       </c>
       <c r="D35" s="22" t="s">
         <v>235</v>
@@ -3707,18 +4018,20 @@
       <c r="E35" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="F35" s="22"/>
+      <c r="F35" s="22" t="s">
+        <v>288</v>
+      </c>
       <c r="G35" s="22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="24">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="36">
       <c r="A36" s="21" t="s">
-        <v>231</v>
+        <v>292</v>
       </c>
       <c r="B36" s="21"/>
       <c r="C36" s="22" t="s">
-        <v>134</v>
+        <v>322</v>
       </c>
       <c r="D36" s="22" t="s">
         <v>235</v>
@@ -3726,18 +4039,20 @@
       <c r="E36" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="F36" s="22"/>
+      <c r="F36" s="22" t="s">
+        <v>317</v>
+      </c>
       <c r="G36" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="24">
+    <row r="37" spans="1:7" ht="72">
       <c r="A37" s="21" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="22" t="s">
-        <v>135</v>
+        <v>323</v>
       </c>
       <c r="D37" s="22" t="s">
         <v>235</v>
@@ -3745,18 +4060,20 @@
       <c r="E37" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="F37" s="22"/>
+      <c r="F37" s="22" t="s">
+        <v>318</v>
+      </c>
       <c r="G37" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="24">
+    <row r="38" spans="1:7" ht="36">
       <c r="A38" s="21" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="B38" s="21"/>
       <c r="C38" s="22" t="s">
-        <v>136</v>
+        <v>324</v>
       </c>
       <c r="D38" s="22" t="s">
         <v>236</v>
@@ -3764,18 +4081,20 @@
       <c r="E38" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="F38" s="22"/>
+      <c r="F38" s="22" t="s">
+        <v>317</v>
+      </c>
       <c r="G38" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="24">
+    <row r="39" spans="1:7" ht="36">
       <c r="A39" s="21" t="s">
-        <v>234</v>
+        <v>295</v>
       </c>
       <c r="B39" s="21"/>
       <c r="C39" s="22" t="s">
-        <v>137</v>
+        <v>325</v>
       </c>
       <c r="D39" s="22" t="s">
         <v>235</v>
@@ -3783,18 +4102,20 @@
       <c r="E39" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="F39" s="22"/>
+      <c r="F39" s="22" t="s">
+        <v>317</v>
+      </c>
       <c r="G39" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="24">
+    <row r="40" spans="1:7" ht="36">
       <c r="A40" s="21" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="B40" s="21"/>
       <c r="C40" s="22" t="s">
-        <v>131</v>
+        <v>326</v>
       </c>
       <c r="D40" s="22" t="s">
         <v>235</v>
@@ -3802,18 +4123,20 @@
       <c r="E40" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="F40" s="22"/>
+      <c r="F40" s="22" t="s">
+        <v>288</v>
+      </c>
       <c r="G40" s="22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="24">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="36">
       <c r="A41" s="21" t="s">
-        <v>229</v>
+        <v>297</v>
       </c>
       <c r="B41" s="21"/>
       <c r="C41" s="22" t="s">
-        <v>132</v>
+        <v>327</v>
       </c>
       <c r="D41" s="22" t="s">
         <v>235</v>
@@ -3821,18 +4144,20 @@
       <c r="E41" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="F41" s="22"/>
+      <c r="F41" s="38" t="s">
+        <v>288</v>
+      </c>
       <c r="G41" s="22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="24">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="36">
       <c r="A42" s="21" t="s">
-        <v>230</v>
+        <v>298</v>
       </c>
       <c r="B42" s="21"/>
       <c r="C42" s="22" t="s">
-        <v>133</v>
+        <v>328</v>
       </c>
       <c r="D42" s="22" t="s">
         <v>235</v>
@@ -3840,18 +4165,20 @@
       <c r="E42" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="F42" s="22"/>
+      <c r="F42" s="22" t="s">
+        <v>288</v>
+      </c>
       <c r="G42" s="22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="24">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="36">
       <c r="A43" s="21" t="s">
-        <v>231</v>
+        <v>299</v>
       </c>
       <c r="B43" s="21"/>
       <c r="C43" s="22" t="s">
-        <v>134</v>
+        <v>329</v>
       </c>
       <c r="D43" s="22" t="s">
         <v>235</v>
@@ -3859,18 +4186,20 @@
       <c r="E43" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="F43" s="22"/>
+      <c r="F43" s="22" t="s">
+        <v>347</v>
+      </c>
       <c r="G43" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="24">
+    <row r="44" spans="1:7" ht="36">
       <c r="A44" s="21" t="s">
-        <v>232</v>
+        <v>300</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="22" t="s">
-        <v>135</v>
+        <v>330</v>
       </c>
       <c r="D44" s="22" t="s">
         <v>235</v>
@@ -3878,18 +4207,20 @@
       <c r="E44" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="F44" s="22"/>
+      <c r="F44" s="22" t="s">
+        <v>348</v>
+      </c>
       <c r="G44" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="24">
+    <row r="45" spans="1:7" ht="36">
       <c r="A45" s="21" t="s">
-        <v>233</v>
+        <v>301</v>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="22" t="s">
-        <v>136</v>
+        <v>331</v>
       </c>
       <c r="D45" s="22" t="s">
         <v>236</v>
@@ -3897,18 +4228,20 @@
       <c r="E45" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="F45" s="22"/>
+      <c r="F45" s="22" t="s">
+        <v>348</v>
+      </c>
       <c r="G45" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="24">
+    <row r="46" spans="1:7" ht="36">
       <c r="A46" s="21" t="s">
-        <v>234</v>
+        <v>302</v>
       </c>
       <c r="B46" s="21"/>
       <c r="C46" s="22" t="s">
-        <v>137</v>
+        <v>332</v>
       </c>
       <c r="D46" s="22" t="s">
         <v>235</v>
@@ -3916,576 +4249,857 @@
       <c r="E46" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="F46" s="22"/>
+      <c r="F46" s="22" t="s">
+        <v>348</v>
+      </c>
       <c r="G46" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="24">
-      <c r="A47" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="B47" s="19"/>
-      <c r="C47" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E47" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="F47" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G47" s="20"/>
-    </row>
-    <row r="48" spans="1:7" ht="24">
-      <c r="A48" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="B48" s="19"/>
-      <c r="C48" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="D48" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E48" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="F48" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G48" s="20"/>
-    </row>
-    <row r="49" spans="1:7" ht="24">
-      <c r="A49" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="B49" s="19"/>
-      <c r="C49" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="D49" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E49" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G49" s="20"/>
-    </row>
-    <row r="50" spans="1:7" ht="24">
-      <c r="A50" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="B50" s="19"/>
-      <c r="C50" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="D50" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E50" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="F50" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G50" s="20"/>
-    </row>
-    <row r="51" spans="1:7" ht="24">
-      <c r="A51" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="B51" s="19"/>
-      <c r="C51" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="D51" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E51" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="F51" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G51" s="20"/>
-    </row>
-    <row r="52" spans="1:7" ht="24">
-      <c r="A52" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="B52" s="19"/>
-      <c r="C52" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="D52" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E52" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="F52" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G52" s="20"/>
-    </row>
-    <row r="53" spans="1:7" ht="24">
-      <c r="A53" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="B53" s="19"/>
-      <c r="C53" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="D53" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E53" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="F53" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G53" s="20"/>
+    <row r="47" spans="1:7" ht="36">
+      <c r="A47" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="B47" s="21"/>
+      <c r="C47" s="22" t="s">
+        <v>333</v>
+      </c>
+      <c r="D47" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E47" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F47" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="G47" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="36">
+      <c r="A48" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="B48" s="21"/>
+      <c r="C48" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="D48" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E48" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="F48" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="G48" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="36">
+      <c r="A49" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="B49" s="21"/>
+      <c r="C49" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="D49" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E49" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F49" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="G49" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="36">
+      <c r="A50" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="B50" s="21"/>
+      <c r="C50" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E50" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="F50" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="G50" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="36">
+      <c r="A51" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B51" s="21"/>
+      <c r="C51" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="D51" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E51" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="F51" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="G51" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="36">
+      <c r="A52" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="B52" s="21"/>
+      <c r="C52" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="D52" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="E52" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F52" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="G52" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="36">
+      <c r="A53" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="B53" s="21"/>
+      <c r="C53" s="22" t="s">
+        <v>339</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E53" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F53" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="G53" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="54" spans="1:7" ht="24">
-      <c r="A54" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="B54" s="14"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
+      <c r="A54" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="B54" s="21"/>
+      <c r="C54" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="D54" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E54" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F54" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="G54" s="22" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="55" spans="1:7" ht="24">
-      <c r="A55" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="B55" s="14"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
+      <c r="A55" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="B55" s="21"/>
+      <c r="C55" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="D55" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E55" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="F55" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="G55" s="22" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="56" spans="1:7" ht="24">
-      <c r="A56" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="B56" s="19"/>
-      <c r="C56" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E56" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="F56" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="G56" s="20"/>
+      <c r="A56" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="B56" s="21"/>
+      <c r="C56" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="D56" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E56" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F56" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="G56" s="22" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="57" spans="1:7" ht="24">
-      <c r="A57" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="B57" s="19"/>
-      <c r="C57" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="D57" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E57" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="F57" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="G57" s="20"/>
+      <c r="A57" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="B57" s="21"/>
+      <c r="C57" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="D57" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E57" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="F57" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="G57" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="58" spans="1:7" ht="24">
-      <c r="A58" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="B58" s="19"/>
-      <c r="C58" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="D58" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E58" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="F58" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="G58" s="20"/>
+      <c r="A58" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="B58" s="21"/>
+      <c r="C58" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="D58" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E58" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="F58" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="G58" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="59" spans="1:7" ht="24">
-      <c r="A59" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="B59" s="19"/>
-      <c r="C59" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="D59" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E59" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="F59" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="G59" s="20"/>
+      <c r="A59" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="B59" s="21"/>
+      <c r="C59" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="D59" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="E59" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F59" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="G59" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="60" spans="1:7" ht="24">
-      <c r="A60" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="D60" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E60" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="F60" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="G60" s="20"/>
+      <c r="A60" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="B60" s="21"/>
+      <c r="C60" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="D60" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E60" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F60" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="G60" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="61" spans="1:7" ht="24">
-      <c r="A61" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="B61" s="19"/>
-      <c r="C61" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="D61" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E61" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="F61" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="G61" s="20"/>
+      <c r="A61" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="B61" s="21"/>
+      <c r="C61" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="D61" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E61" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F61" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="G61" s="22" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="62" spans="1:7" ht="24">
-      <c r="A62" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="B62" s="19"/>
-      <c r="C62" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="D62" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E62" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="F62" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="G62" s="20"/>
+      <c r="A62" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="B62" s="21"/>
+      <c r="C62" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="D62" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E62" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="F62" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="G62" s="22" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="63" spans="1:7" ht="24">
-      <c r="A63" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="B63" s="14"/>
-      <c r="C63" s="16"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="16"/>
+      <c r="A63" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="B63" s="21"/>
+      <c r="C63" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="D63" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E63" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F63" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="G63" s="22" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="64" spans="1:7" ht="24">
-      <c r="A64" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="B64" s="14"/>
-      <c r="C64" s="16"/>
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
-    </row>
-    <row r="65" spans="1:7" ht="24">
+      <c r="A64" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B64" s="21"/>
+      <c r="C64" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="D64" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E64" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="F64" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="G64" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="72">
       <c r="A65" s="21" t="s">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="B65" s="21"/>
-      <c r="C65" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="D65" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E65" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="F65" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="G65" s="16"/>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="16"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="16"/>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="16"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16"/>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="21"/>
+      <c r="C65" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="D65" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E65" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="F65" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="G65" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="24">
+      <c r="A66" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="B66" s="21"/>
+      <c r="C66" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="D66" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="E66" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F66" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="G66" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="24">
+      <c r="A67" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="B67" s="21"/>
+      <c r="C67" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="D67" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E67" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F67" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="G67" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="24">
+      <c r="A68" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="B68" s="21"/>
+      <c r="C68" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="D68" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E68" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="24">
+      <c r="A69" s="21" t="s">
+        <v>229</v>
+      </c>
       <c r="B69" s="21"/>
-      <c r="C69" s="16"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="16"/>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="14"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="16"/>
-      <c r="D70" s="16"/>
-      <c r="E70" s="16"/>
-      <c r="F70" s="16"/>
-      <c r="G70" s="16"/>
+      <c r="C69" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="D69" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E69" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="24">
+      <c r="A70" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B70" s="21"/>
+      <c r="C70" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="D70" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E70" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="71" spans="1:7" ht="24">
       <c r="A71" s="21" t="s">
-        <v>113</v>
+        <v>231</v>
       </c>
       <c r="B71" s="21"/>
-      <c r="C71" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E71" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="F71" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="G71" s="16"/>
+      <c r="C71" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="D71" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E71" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="72" spans="1:7" ht="24">
       <c r="A72" s="21" t="s">
-        <v>117</v>
+        <v>232</v>
       </c>
       <c r="B72" s="21"/>
-      <c r="C72" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="D72" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E72" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="F72" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="G72" s="16"/>
+      <c r="C72" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="D72" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E72" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="73" spans="1:7" ht="24">
       <c r="A73" s="21" t="s">
-        <v>118</v>
+        <v>233</v>
       </c>
       <c r="B73" s="21"/>
-      <c r="C73" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="D73" s="16" t="s">
+      <c r="C73" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="D73" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="E73" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="24">
+      <c r="A74" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="B74" s="21"/>
+      <c r="C74" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="D74" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E74" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="24">
+      <c r="A75" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="B75" s="21"/>
+      <c r="C75" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="D75" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E75" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="24">
+      <c r="A76" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="B76" s="21"/>
+      <c r="C76" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="D76" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E76" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="F76" s="22"/>
+      <c r="G76" s="22" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="24">
+      <c r="A77" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B77" s="21"/>
+      <c r="C77" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="D77" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E77" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F77" s="22"/>
+      <c r="G77" s="22" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="24">
+      <c r="A78" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="B78" s="21"/>
+      <c r="C78" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="D78" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E78" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="F78" s="22"/>
+      <c r="G78" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="24">
+      <c r="A79" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="B79" s="21"/>
+      <c r="C79" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="D79" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E79" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="24">
+      <c r="A80" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="B80" s="21"/>
+      <c r="C80" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="D80" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="E80" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F80" s="22"/>
+      <c r="G80" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="24">
+      <c r="A81" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="B81" s="21"/>
+      <c r="C81" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="D81" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E81" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F81" s="22"/>
+      <c r="G81" s="22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="24">
+      <c r="A82" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B82" s="19"/>
+      <c r="C82" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="D82" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E73" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F73" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="G73" s="16"/>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74" s="14"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="16"/>
-      <c r="D74" s="16"/>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="16"/>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75" s="14"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="16"/>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="16"/>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76" s="14"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="16"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="16"/>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="14"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="16"/>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="16"/>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="14"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="16"/>
-      <c r="D78" s="16"/>
-      <c r="E78" s="16"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="16"/>
-    </row>
-    <row r="79" spans="1:7">
-      <c r="A79" s="14"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="16"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="16"/>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80" s="14"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="16"/>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81" s="14"/>
-      <c r="B81" s="14"/>
-      <c r="C81" s="16"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="16"/>
-      <c r="F81" s="16"/>
-      <c r="G81" s="16"/>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82" s="14"/>
-      <c r="B82" s="14"/>
-      <c r="C82" s="16"/>
-      <c r="D82" s="16"/>
-      <c r="E82" s="16"/>
-      <c r="F82" s="16"/>
-      <c r="G82" s="16"/>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" s="14"/>
-      <c r="B83" s="14"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
-      <c r="E83" s="16"/>
-      <c r="F83" s="16"/>
-      <c r="G83" s="16"/>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="A84" s="14"/>
-      <c r="B84" s="14"/>
-      <c r="C84" s="16"/>
-      <c r="D84" s="16"/>
-      <c r="E84" s="16"/>
-      <c r="F84" s="16"/>
-      <c r="G84" s="16"/>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85" s="14"/>
-      <c r="B85" s="14"/>
-      <c r="C85" s="16"/>
-      <c r="D85" s="16"/>
-      <c r="E85" s="16"/>
-      <c r="F85" s="16"/>
-      <c r="G85" s="16"/>
-    </row>
-    <row r="86" spans="1:7">
-      <c r="A86" s="14"/>
-      <c r="B86" s="14"/>
-      <c r="C86" s="16"/>
-      <c r="D86" s="16"/>
-      <c r="E86" s="16"/>
-      <c r="F86" s="16"/>
-      <c r="G86" s="16"/>
-    </row>
-    <row r="87" spans="1:7">
-      <c r="A87" s="14"/>
-      <c r="B87" s="14"/>
-      <c r="C87" s="16"/>
-      <c r="D87" s="16"/>
-      <c r="E87" s="16"/>
-      <c r="F87" s="16"/>
-      <c r="G87" s="16"/>
-    </row>
-    <row r="88" spans="1:7">
-      <c r="A88" s="14"/>
-      <c r="B88" s="14"/>
-      <c r="C88" s="16"/>
-      <c r="D88" s="16"/>
-      <c r="E88" s="16"/>
-      <c r="F88" s="16"/>
-      <c r="G88" s="16"/>
-    </row>
-    <row r="89" spans="1:7">
-      <c r="A89" s="14"/>
+      <c r="E82" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="F82" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G82" s="20"/>
+    </row>
+    <row r="83" spans="1:7" ht="24">
+      <c r="A83" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="B83" s="19"/>
+      <c r="C83" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="D83" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E83" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="F83" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G83" s="20"/>
+    </row>
+    <row r="84" spans="1:7" ht="24">
+      <c r="A84" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B84" s="19"/>
+      <c r="C84" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="D84" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E84" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="F84" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G84" s="20"/>
+    </row>
+    <row r="85" spans="1:7" ht="24">
+      <c r="A85" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B85" s="19"/>
+      <c r="C85" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="D85" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E85" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="F85" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G85" s="20"/>
+    </row>
+    <row r="86" spans="1:7" ht="24">
+      <c r="A86" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="B86" s="19"/>
+      <c r="C86" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="D86" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="F86" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G86" s="20"/>
+    </row>
+    <row r="87" spans="1:7" ht="24">
+      <c r="A87" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="B87" s="19"/>
+      <c r="C87" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="D87" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E87" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="F87" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G87" s="20"/>
+    </row>
+    <row r="88" spans="1:7" ht="24">
+      <c r="A88" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B88" s="19"/>
+      <c r="C88" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="D88" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E88" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F88" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G88" s="20"/>
+    </row>
+    <row r="89" spans="1:7" ht="24">
+      <c r="A89" s="25" t="s">
+        <v>169</v>
+      </c>
       <c r="B89" s="14"/>
       <c r="C89" s="16"/>
       <c r="D89" s="16"/>
@@ -4493,8 +5107,10 @@
       <c r="F89" s="16"/>
       <c r="G89" s="16"/>
     </row>
-    <row r="90" spans="1:7">
-      <c r="A90" s="14"/>
+    <row r="90" spans="1:7" ht="24">
+      <c r="A90" s="26" t="s">
+        <v>171</v>
+      </c>
       <c r="B90" s="14"/>
       <c r="C90" s="16"/>
       <c r="D90" s="16"/>
@@ -4502,14 +5118,440 @@
       <c r="F90" s="16"/>
       <c r="G90" s="16"/>
     </row>
-    <row r="91" spans="1:7">
-      <c r="A91" s="14"/>
-      <c r="B91" s="14"/>
-      <c r="C91" s="16"/>
-      <c r="D91" s="16"/>
-      <c r="E91" s="16"/>
-      <c r="F91" s="16"/>
-      <c r="G91" s="16"/>
+    <row r="91" spans="1:7" ht="24">
+      <c r="A91" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="B91" s="19"/>
+      <c r="C91" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="D91" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E91" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="F91" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G91" s="20"/>
+    </row>
+    <row r="92" spans="1:7" ht="24">
+      <c r="A92" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="B92" s="19"/>
+      <c r="C92" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="D92" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E92" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="F92" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G92" s="20"/>
+    </row>
+    <row r="93" spans="1:7" ht="24">
+      <c r="A93" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B93" s="19"/>
+      <c r="C93" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="D93" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E93" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="F93" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G93" s="20"/>
+    </row>
+    <row r="94" spans="1:7" ht="24">
+      <c r="A94" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="B94" s="19"/>
+      <c r="C94" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="D94" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E94" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="F94" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="G94" s="20"/>
+    </row>
+    <row r="95" spans="1:7" ht="24">
+      <c r="A95" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B95" s="19"/>
+      <c r="C95" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="D95" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E95" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="F95" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="G95" s="20"/>
+    </row>
+    <row r="96" spans="1:7" ht="24">
+      <c r="A96" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B96" s="19"/>
+      <c r="C96" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D96" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E96" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="F96" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="G96" s="20"/>
+    </row>
+    <row r="97" spans="1:7" ht="24">
+      <c r="A97" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B97" s="19"/>
+      <c r="C97" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="D97" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E97" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F97" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="G97" s="20"/>
+    </row>
+    <row r="98" spans="1:7" ht="24">
+      <c r="A98" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="B98" s="14"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="16"/>
+      <c r="E98" s="16"/>
+      <c r="F98" s="16"/>
+      <c r="G98" s="16"/>
+    </row>
+    <row r="99" spans="1:7" ht="24">
+      <c r="A99" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="B99" s="14"/>
+      <c r="C99" s="16"/>
+      <c r="D99" s="16"/>
+      <c r="E99" s="16"/>
+      <c r="F99" s="16"/>
+      <c r="G99" s="16"/>
+    </row>
+    <row r="100" spans="1:7" ht="24">
+      <c r="A100" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="B100" s="21"/>
+      <c r="C100" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="D100" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E100" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="F100" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G100" s="16"/>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="16"/>
+      <c r="B101" s="14"/>
+      <c r="C101" s="16"/>
+      <c r="D101" s="16"/>
+      <c r="E101" s="16"/>
+      <c r="F101" s="16"/>
+      <c r="G101" s="16"/>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="16"/>
+      <c r="B102" s="14"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="16"/>
+      <c r="F102" s="16"/>
+      <c r="G102" s="16"/>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="C103" s="9"/>
+      <c r="D103" s="9"/>
+      <c r="E103" s="9"/>
+      <c r="F103" s="9"/>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" s="21"/>
+      <c r="B104" s="21"/>
+      <c r="C104" s="16"/>
+      <c r="D104" s="16"/>
+      <c r="E104" s="16"/>
+      <c r="F104" s="16"/>
+      <c r="G104" s="16"/>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" s="14"/>
+      <c r="B105" s="14"/>
+      <c r="C105" s="16"/>
+      <c r="D105" s="16"/>
+      <c r="E105" s="16"/>
+      <c r="F105" s="16"/>
+      <c r="G105" s="16"/>
+    </row>
+    <row r="106" spans="1:7" ht="24">
+      <c r="A106" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B106" s="21"/>
+      <c r="C106" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D106" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E106" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="F106" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="G106" s="16"/>
+    </row>
+    <row r="107" spans="1:7" ht="24">
+      <c r="A107" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B107" s="21"/>
+      <c r="C107" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D107" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E107" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F107" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="G107" s="16"/>
+    </row>
+    <row r="108" spans="1:7" ht="24">
+      <c r="A108" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B108" s="21"/>
+      <c r="C108" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D108" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E108" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F108" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="G108" s="16"/>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" s="14"/>
+      <c r="B109" s="14"/>
+      <c r="C109" s="16"/>
+      <c r="D109" s="16"/>
+      <c r="E109" s="16"/>
+      <c r="F109" s="16"/>
+      <c r="G109" s="16"/>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" s="14"/>
+      <c r="B110" s="14"/>
+      <c r="C110" s="16"/>
+      <c r="D110" s="16"/>
+      <c r="E110" s="16"/>
+      <c r="F110" s="16"/>
+      <c r="G110" s="16"/>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" s="14"/>
+      <c r="B111" s="14"/>
+      <c r="C111" s="16"/>
+      <c r="D111" s="16"/>
+      <c r="E111" s="16"/>
+      <c r="F111" s="16"/>
+      <c r="G111" s="16"/>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" s="14"/>
+      <c r="B112" s="14"/>
+      <c r="C112" s="16"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="16"/>
+      <c r="F112" s="16"/>
+      <c r="G112" s="16"/>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" s="14"/>
+      <c r="B113" s="14"/>
+      <c r="C113" s="16"/>
+      <c r="D113" s="16"/>
+      <c r="E113" s="16"/>
+      <c r="F113" s="16"/>
+      <c r="G113" s="16"/>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" s="14"/>
+      <c r="B114" s="14"/>
+      <c r="C114" s="16"/>
+      <c r="D114" s="16"/>
+      <c r="E114" s="16"/>
+      <c r="F114" s="16"/>
+      <c r="G114" s="16"/>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="14"/>
+      <c r="B115" s="14"/>
+      <c r="C115" s="16"/>
+      <c r="D115" s="16"/>
+      <c r="E115" s="16"/>
+      <c r="F115" s="16"/>
+      <c r="G115" s="16"/>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="14"/>
+      <c r="B116" s="14"/>
+      <c r="C116" s="16"/>
+      <c r="D116" s="16"/>
+      <c r="E116" s="16"/>
+      <c r="F116" s="16"/>
+      <c r="G116" s="16"/>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" s="14"/>
+      <c r="B117" s="14"/>
+      <c r="C117" s="16"/>
+      <c r="D117" s="16"/>
+      <c r="E117" s="16"/>
+      <c r="F117" s="16"/>
+      <c r="G117" s="16"/>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" s="14"/>
+      <c r="B118" s="14"/>
+      <c r="C118" s="16"/>
+      <c r="D118" s="16"/>
+      <c r="E118" s="16"/>
+      <c r="F118" s="16"/>
+      <c r="G118" s="16"/>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="14"/>
+      <c r="B119" s="14"/>
+      <c r="C119" s="16"/>
+      <c r="D119" s="16"/>
+      <c r="E119" s="16"/>
+      <c r="F119" s="16"/>
+      <c r="G119" s="16"/>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" s="14"/>
+      <c r="B120" s="14"/>
+      <c r="C120" s="16"/>
+      <c r="D120" s="16"/>
+      <c r="E120" s="16"/>
+      <c r="F120" s="16"/>
+      <c r="G120" s="16"/>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" s="14"/>
+      <c r="B121" s="14"/>
+      <c r="C121" s="16"/>
+      <c r="D121" s="16"/>
+      <c r="E121" s="16"/>
+      <c r="F121" s="16"/>
+      <c r="G121" s="16"/>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" s="14"/>
+      <c r="B122" s="14"/>
+      <c r="C122" s="16"/>
+      <c r="D122" s="16"/>
+      <c r="E122" s="16"/>
+      <c r="F122" s="16"/>
+      <c r="G122" s="16"/>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" s="14"/>
+      <c r="B123" s="14"/>
+      <c r="C123" s="16"/>
+      <c r="D123" s="16"/>
+      <c r="E123" s="16"/>
+      <c r="F123" s="16"/>
+      <c r="G123" s="16"/>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" s="14"/>
+      <c r="B124" s="14"/>
+      <c r="C124" s="16"/>
+      <c r="D124" s="16"/>
+      <c r="E124" s="16"/>
+      <c r="F124" s="16"/>
+      <c r="G124" s="16"/>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" s="14"/>
+      <c r="B125" s="14"/>
+      <c r="C125" s="16"/>
+      <c r="D125" s="16"/>
+      <c r="E125" s="16"/>
+      <c r="F125" s="16"/>
+      <c r="G125" s="16"/>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" s="14"/>
+      <c r="B126" s="14"/>
+      <c r="C126" s="16"/>
+      <c r="D126" s="16"/>
+      <c r="E126" s="16"/>
+      <c r="F126" s="16"/>
+      <c r="G126" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:G3"/>

--- a/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
+++ b/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
@@ -1010,62 +1010,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sequoiadb_fault_001_003_001_007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_002_007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_003_007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_004_007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_005_007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_006_007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_007_007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_001_008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_002_008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_003_008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_004_008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_005_008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_006_008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_007_008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>sequoiadb_fault_001_003_001_00X</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1138,62 +1082,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sequoiadb_fault_001_003_001_002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_002_002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_003_002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_004_002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_005_002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_006_002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_007_002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_001_003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_002_003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_003_003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_004_003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_005_003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_006_003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_007_003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>操作会报失败，自动恢复</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1202,90 +1090,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sequoiadb_fault_001_003_001_004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_002_004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_003_004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_004_004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_005_004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_006_004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_007_004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_001_005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_002_005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_003_005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_004_005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_005_005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_006_005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_007_005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_001_006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_002_006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_003_006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_004_006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_005_006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_006_006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_fault_001_003_007_006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10个线程并发做插入、更新（3.3:6.7）过程中，强杀一个主节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1439,6 +1243,202 @@
   </si>
   <si>
     <t>当查询发生在这些备上时，操作会失败。失败后，节点自动恢复。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_002_003_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_002_003_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_002_003_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_002_003_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_002_003_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_002_003_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_002_003_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_008_003_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_008_003_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_008_003_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_008_003_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_008_003_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_008_003_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_008_003_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_007_003_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_007_003_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_007_003_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_007_003_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_007_003_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_007_003_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_007_003_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_006_003_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_006_003_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_006_003_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_006_003_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_006_003_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_006_003_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_006_003_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_005_003_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_005_003_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_005_003_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_005_003_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_005_003_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_005_003_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_005_003_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_004_003_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_004_003_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_004_003_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_004_003_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_004_003_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_004_003_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_004_003_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_003_003_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_003_003_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_003_003_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_003_003_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_003_003_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_003_003_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_003_003_001_001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1723,6 +1723,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1740,9 +1743,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2436,10 +2436,10 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="33" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -2453,8 +2453,8 @@
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="33"/>
-      <c r="B3" s="33"/>
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
@@ -2462,8 +2462,8 @@
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="33"/>
-      <c r="B4" s="34"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="35"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
@@ -2471,8 +2471,8 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="33"/>
-      <c r="B5" s="32" t="s">
+      <c r="A5" s="34"/>
+      <c r="B5" s="33" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -2486,8 +2486,8 @@
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="33"/>
-      <c r="B6" s="33"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="5" t="s">
         <v>32</v>
       </c>
@@ -2499,8 +2499,8 @@
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="33"/>
-      <c r="B7" s="34"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -2508,7 +2508,7 @@
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="33"/>
+      <c r="A8" s="34"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -2517,7 +2517,7 @@
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="34"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -2526,10 +2526,10 @@
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="33" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -2543,8 +2543,8 @@
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -2552,8 +2552,8 @@
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="33"/>
-      <c r="B12" s="34"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -2561,8 +2561,8 @@
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="33"/>
-      <c r="B13" s="32" t="s">
+      <c r="A13" s="34"/>
+      <c r="B13" s="33" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -2576,8 +2576,8 @@
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="33"/>
-      <c r="B14" s="33"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
       <c r="C14" s="5" t="s">
         <v>34</v>
       </c>
@@ -2589,8 +2589,8 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="33"/>
-      <c r="B15" s="33"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -2598,8 +2598,8 @@
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="33"/>
-      <c r="B16" s="34"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="35"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -2607,8 +2607,8 @@
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="33"/>
-      <c r="B17" s="32" t="s">
+      <c r="A17" s="34"/>
+      <c r="B17" s="33" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -2622,8 +2622,8 @@
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="33"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="34"/>
       <c r="C18" s="5" t="s">
         <v>14</v>
       </c>
@@ -2635,8 +2635,8 @@
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="33"/>
-      <c r="B19" s="33"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -2644,8 +2644,8 @@
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="34"/>
-      <c r="B20" s="34"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="35"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -2653,10 +2653,10 @@
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="33" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="5" t="s">
@@ -2670,8 +2670,8 @@
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="33"/>
-      <c r="B22" s="33"/>
+      <c r="A22" s="34"/>
+      <c r="B22" s="34"/>
       <c r="C22" s="5" t="s">
         <v>37</v>
       </c>
@@ -2683,8 +2683,8 @@
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="33"/>
-      <c r="B23" s="33"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="34"/>
       <c r="C23" s="5" t="s">
         <v>38</v>
       </c>
@@ -2696,8 +2696,8 @@
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="33"/>
-      <c r="B24" s="33"/>
+      <c r="A24" s="34"/>
+      <c r="B24" s="34"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -2705,8 +2705,8 @@
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="33"/>
-      <c r="B25" s="34"/>
+      <c r="A25" s="34"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -2714,8 +2714,8 @@
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="33"/>
-      <c r="B26" s="32" t="s">
+      <c r="A26" s="34"/>
+      <c r="B26" s="33" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="5" t="s">
@@ -2729,8 +2729,8 @@
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="33"/>
-      <c r="B27" s="33"/>
+      <c r="A27" s="34"/>
+      <c r="B27" s="34"/>
       <c r="C27" s="5" t="s">
         <v>40</v>
       </c>
@@ -2742,8 +2742,8 @@
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="34"/>
-      <c r="B28" s="34"/>
+      <c r="A28" s="35"/>
+      <c r="B28" s="35"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -2751,7 +2751,7 @@
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="32" t="s">
+      <c r="A29" s="33" t="s">
         <v>19</v>
       </c>
       <c r="B29" s="5"/>
@@ -2766,7 +2766,7 @@
       <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="33"/>
+      <c r="A30" s="34"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
         <v>41</v>
@@ -2779,7 +2779,7 @@
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="33"/>
+      <c r="A31" s="34"/>
       <c r="B31" s="3"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -2788,7 +2788,7 @@
       <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="34"/>
+      <c r="A32" s="35"/>
       <c r="B32" s="3"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -2843,11 +2843,11 @@
       <c r="A3" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="36"/>
-      <c r="D3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="38"/>
       <c r="E3" s="11" t="s">
         <v>222</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>139</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="G13" s="22" t="s">
         <v>225</v>
@@ -3670,11 +3670,11 @@
     </row>
     <row r="19" spans="1:7" ht="36">
       <c r="A19" s="21" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="22" t="s">
-        <v>340</v>
+        <v>291</v>
       </c>
       <c r="D19" s="22" t="s">
         <v>235</v>
@@ -3683,7 +3683,7 @@
         <v>138</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="G19" s="22" t="s">
         <v>227</v>
@@ -3691,11 +3691,11 @@
     </row>
     <row r="20" spans="1:7" ht="36">
       <c r="A20" s="21" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="B20" s="21"/>
       <c r="C20" s="22" t="s">
-        <v>341</v>
+        <v>292</v>
       </c>
       <c r="D20" s="22" t="s">
         <v>235</v>
@@ -3704,7 +3704,7 @@
         <v>139</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="G20" s="22" t="s">
         <v>227</v>
@@ -3712,11 +3712,11 @@
     </row>
     <row r="21" spans="1:7" ht="36">
       <c r="A21" s="21" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="22" t="s">
-        <v>342</v>
+        <v>293</v>
       </c>
       <c r="D21" s="22" t="s">
         <v>235</v>
@@ -3725,7 +3725,7 @@
         <v>140</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="G21" s="22" t="s">
         <v>227</v>
@@ -3733,11 +3733,11 @@
     </row>
     <row r="22" spans="1:7" ht="36">
       <c r="A22" s="21" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="B22" s="21"/>
       <c r="C22" s="22" t="s">
-        <v>343</v>
+        <v>294</v>
       </c>
       <c r="D22" s="22" t="s">
         <v>235</v>
@@ -3746,7 +3746,7 @@
         <v>141</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="G22" s="22" t="s">
         <v>227</v>
@@ -3754,11 +3754,11 @@
     </row>
     <row r="23" spans="1:7" ht="72">
       <c r="A23" s="21" t="s">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="B23" s="21"/>
       <c r="C23" s="22" t="s">
-        <v>344</v>
+        <v>295</v>
       </c>
       <c r="D23" s="22" t="s">
         <v>235</v>
@@ -3767,7 +3767,7 @@
         <v>142</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>318</v>
+        <v>269</v>
       </c>
       <c r="G23" s="22" t="s">
         <v>227</v>
@@ -3775,11 +3775,11 @@
     </row>
     <row r="24" spans="1:7" ht="36">
       <c r="A24" s="21" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="22" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="D24" s="22" t="s">
         <v>236</v>
@@ -3788,7 +3788,7 @@
         <v>143</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="G24" s="22" t="s">
         <v>227</v>
@@ -3796,11 +3796,11 @@
     </row>
     <row r="25" spans="1:7" ht="36">
       <c r="A25" s="21" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="22" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="D25" s="22" t="s">
         <v>235</v>
@@ -3809,7 +3809,7 @@
         <v>144</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="G25" s="22" t="s">
         <v>227</v>
@@ -3817,11 +3817,11 @@
     </row>
     <row r="26" spans="1:7" ht="36">
       <c r="A26" s="21" t="s">
-        <v>280</v>
+        <v>348</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="22" t="s">
-        <v>310</v>
+        <v>261</v>
       </c>
       <c r="D26" s="22" t="s">
         <v>235</v>
@@ -3830,7 +3830,7 @@
         <v>138</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="G26" s="22" t="s">
         <v>227</v>
@@ -3838,11 +3838,11 @@
     </row>
     <row r="27" spans="1:7" ht="36">
       <c r="A27" s="21" t="s">
-        <v>281</v>
+        <v>347</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="22" t="s">
-        <v>311</v>
+        <v>262</v>
       </c>
       <c r="D27" s="22" t="s">
         <v>235</v>
@@ -3851,7 +3851,7 @@
         <v>139</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="G27" s="22" t="s">
         <v>227</v>
@@ -3859,11 +3859,11 @@
     </row>
     <row r="28" spans="1:7" ht="36">
       <c r="A28" s="21" t="s">
-        <v>282</v>
+        <v>346</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="22" t="s">
-        <v>312</v>
+        <v>263</v>
       </c>
       <c r="D28" s="22" t="s">
         <v>235</v>
@@ -3872,7 +3872,7 @@
         <v>140</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="G28" s="22" t="s">
         <v>227</v>
@@ -3880,11 +3880,11 @@
     </row>
     <row r="29" spans="1:7" ht="36">
       <c r="A29" s="21" t="s">
-        <v>283</v>
+        <v>345</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="22" t="s">
-        <v>313</v>
+        <v>264</v>
       </c>
       <c r="D29" s="22" t="s">
         <v>235</v>
@@ -3893,7 +3893,7 @@
         <v>141</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="G29" s="22" t="s">
         <v>227</v>
@@ -3901,11 +3901,11 @@
     </row>
     <row r="30" spans="1:7" ht="72">
       <c r="A30" s="21" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="B30" s="21"/>
       <c r="C30" s="22" t="s">
-        <v>314</v>
+        <v>265</v>
       </c>
       <c r="D30" s="22" t="s">
         <v>235</v>
@@ -3914,7 +3914,7 @@
         <v>142</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>318</v>
+        <v>269</v>
       </c>
       <c r="G30" s="22" t="s">
         <v>227</v>
@@ -3922,11 +3922,11 @@
     </row>
     <row r="31" spans="1:7" ht="36">
       <c r="A31" s="21" t="s">
-        <v>285</v>
+        <v>343</v>
       </c>
       <c r="B31" s="21"/>
       <c r="C31" s="22" t="s">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="D31" s="22" t="s">
         <v>236</v>
@@ -3935,7 +3935,7 @@
         <v>143</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="G31" s="22" t="s">
         <v>227</v>
@@ -3943,11 +3943,11 @@
     </row>
     <row r="32" spans="1:7" ht="36">
       <c r="A32" s="21" t="s">
-        <v>286</v>
+        <v>342</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="22" t="s">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="D32" s="22" t="s">
         <v>235</v>
@@ -3956,7 +3956,7 @@
         <v>144</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="G32" s="22" t="s">
         <v>227</v>
@@ -3964,11 +3964,11 @@
     </row>
     <row r="33" spans="1:7" ht="36">
       <c r="A33" s="21" t="s">
-        <v>289</v>
+        <v>341</v>
       </c>
       <c r="B33" s="21"/>
       <c r="C33" s="22" t="s">
-        <v>319</v>
+        <v>270</v>
       </c>
       <c r="D33" s="22" t="s">
         <v>235</v>
@@ -3977,7 +3977,7 @@
         <v>138</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="G33" s="22" t="s">
         <v>227</v>
@@ -3985,11 +3985,11 @@
     </row>
     <row r="34" spans="1:7" ht="36">
       <c r="A34" s="21" t="s">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="B34" s="21"/>
       <c r="C34" s="22" t="s">
-        <v>320</v>
+        <v>271</v>
       </c>
       <c r="D34" s="22" t="s">
         <v>235</v>
@@ -3998,7 +3998,7 @@
         <v>139</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="G34" s="22" t="s">
         <v>227</v>
@@ -4006,11 +4006,11 @@
     </row>
     <row r="35" spans="1:7" ht="36">
       <c r="A35" s="21" t="s">
-        <v>291</v>
+        <v>339</v>
       </c>
       <c r="B35" s="21"/>
       <c r="C35" s="22" t="s">
-        <v>321</v>
+        <v>272</v>
       </c>
       <c r="D35" s="22" t="s">
         <v>235</v>
@@ -4019,7 +4019,7 @@
         <v>140</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="G35" s="22" t="s">
         <v>227</v>
@@ -4027,11 +4027,11 @@
     </row>
     <row r="36" spans="1:7" ht="36">
       <c r="A36" s="21" t="s">
-        <v>292</v>
+        <v>338</v>
       </c>
       <c r="B36" s="21"/>
       <c r="C36" s="22" t="s">
-        <v>322</v>
+        <v>273</v>
       </c>
       <c r="D36" s="22" t="s">
         <v>235</v>
@@ -4040,7 +4040,7 @@
         <v>141</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="G36" s="22" t="s">
         <v>227</v>
@@ -4048,11 +4048,11 @@
     </row>
     <row r="37" spans="1:7" ht="72">
       <c r="A37" s="21" t="s">
-        <v>293</v>
+        <v>337</v>
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="22" t="s">
-        <v>323</v>
+        <v>274</v>
       </c>
       <c r="D37" s="22" t="s">
         <v>235</v>
@@ -4061,7 +4061,7 @@
         <v>142</v>
       </c>
       <c r="F37" s="22" t="s">
-        <v>318</v>
+        <v>269</v>
       </c>
       <c r="G37" s="22" t="s">
         <v>227</v>
@@ -4069,11 +4069,11 @@
     </row>
     <row r="38" spans="1:7" ht="36">
       <c r="A38" s="21" t="s">
-        <v>294</v>
+        <v>336</v>
       </c>
       <c r="B38" s="21"/>
       <c r="C38" s="22" t="s">
-        <v>324</v>
+        <v>275</v>
       </c>
       <c r="D38" s="22" t="s">
         <v>236</v>
@@ -4082,7 +4082,7 @@
         <v>143</v>
       </c>
       <c r="F38" s="22" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="G38" s="22" t="s">
         <v>227</v>
@@ -4090,11 +4090,11 @@
     </row>
     <row r="39" spans="1:7" ht="36">
       <c r="A39" s="21" t="s">
-        <v>295</v>
+        <v>335</v>
       </c>
       <c r="B39" s="21"/>
       <c r="C39" s="22" t="s">
-        <v>325</v>
+        <v>276</v>
       </c>
       <c r="D39" s="22" t="s">
         <v>235</v>
@@ -4103,7 +4103,7 @@
         <v>144</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="G39" s="22" t="s">
         <v>227</v>
@@ -4111,11 +4111,11 @@
     </row>
     <row r="40" spans="1:7" ht="36">
       <c r="A40" s="21" t="s">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="B40" s="21"/>
       <c r="C40" s="22" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
       <c r="D40" s="22" t="s">
         <v>235</v>
@@ -4124,7 +4124,7 @@
         <v>138</v>
       </c>
       <c r="F40" s="22" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="G40" s="22" t="s">
         <v>227</v>
@@ -4132,11 +4132,11 @@
     </row>
     <row r="41" spans="1:7" ht="36">
       <c r="A41" s="21" t="s">
-        <v>297</v>
+        <v>333</v>
       </c>
       <c r="B41" s="21"/>
       <c r="C41" s="22" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="D41" s="22" t="s">
         <v>235</v>
@@ -4144,8 +4144,8 @@
       <c r="E41" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="F41" s="38" t="s">
-        <v>288</v>
+      <c r="F41" s="32" t="s">
+        <v>260</v>
       </c>
       <c r="G41" s="22" t="s">
         <v>227</v>
@@ -4153,11 +4153,11 @@
     </row>
     <row r="42" spans="1:7" ht="36">
       <c r="A42" s="21" t="s">
-        <v>298</v>
+        <v>332</v>
       </c>
       <c r="B42" s="21"/>
       <c r="C42" s="22" t="s">
-        <v>328</v>
+        <v>279</v>
       </c>
       <c r="D42" s="22" t="s">
         <v>235</v>
@@ -4166,7 +4166,7 @@
         <v>140</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="G42" s="22" t="s">
         <v>227</v>
@@ -4174,11 +4174,11 @@
     </row>
     <row r="43" spans="1:7" ht="36">
       <c r="A43" s="21" t="s">
-        <v>299</v>
+        <v>331</v>
       </c>
       <c r="B43" s="21"/>
       <c r="C43" s="22" t="s">
-        <v>329</v>
+        <v>280</v>
       </c>
       <c r="D43" s="22" t="s">
         <v>235</v>
@@ -4187,7 +4187,7 @@
         <v>141</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>347</v>
+        <v>298</v>
       </c>
       <c r="G43" s="22" t="s">
         <v>227</v>
@@ -4195,11 +4195,11 @@
     </row>
     <row r="44" spans="1:7" ht="36">
       <c r="A44" s="21" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="22" t="s">
-        <v>330</v>
+        <v>281</v>
       </c>
       <c r="D44" s="22" t="s">
         <v>235</v>
@@ -4208,7 +4208,7 @@
         <v>142</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="G44" s="22" t="s">
         <v>227</v>
@@ -4216,11 +4216,11 @@
     </row>
     <row r="45" spans="1:7" ht="36">
       <c r="A45" s="21" t="s">
-        <v>301</v>
+        <v>329</v>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="22" t="s">
-        <v>331</v>
+        <v>282</v>
       </c>
       <c r="D45" s="22" t="s">
         <v>236</v>
@@ -4229,7 +4229,7 @@
         <v>143</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="G45" s="22" t="s">
         <v>227</v>
@@ -4237,11 +4237,11 @@
     </row>
     <row r="46" spans="1:7" ht="36">
       <c r="A46" s="21" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="B46" s="21"/>
       <c r="C46" s="22" t="s">
-        <v>332</v>
+        <v>283</v>
       </c>
       <c r="D46" s="22" t="s">
         <v>235</v>
@@ -4250,7 +4250,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="G46" s="22" t="s">
         <v>227</v>
@@ -4258,11 +4258,11 @@
     </row>
     <row r="47" spans="1:7" ht="36">
       <c r="A47" s="21" t="s">
-        <v>303</v>
+        <v>327</v>
       </c>
       <c r="B47" s="21"/>
       <c r="C47" s="22" t="s">
-        <v>333</v>
+        <v>284</v>
       </c>
       <c r="D47" s="22" t="s">
         <v>235</v>
@@ -4271,7 +4271,7 @@
         <v>138</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="G47" s="22" t="s">
         <v>227</v>
@@ -4279,11 +4279,11 @@
     </row>
     <row r="48" spans="1:7" ht="36">
       <c r="A48" s="21" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="B48" s="21"/>
       <c r="C48" s="22" t="s">
-        <v>334</v>
+        <v>285</v>
       </c>
       <c r="D48" s="22" t="s">
         <v>235</v>
@@ -4292,7 +4292,7 @@
         <v>139</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="G48" s="22" t="s">
         <v>227</v>
@@ -4300,11 +4300,11 @@
     </row>
     <row r="49" spans="1:7" ht="36">
       <c r="A49" s="21" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="B49" s="21"/>
       <c r="C49" s="22" t="s">
-        <v>335</v>
+        <v>286</v>
       </c>
       <c r="D49" s="22" t="s">
         <v>235</v>
@@ -4313,7 +4313,7 @@
         <v>140</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="G49" s="22" t="s">
         <v>227</v>
@@ -4321,11 +4321,11 @@
     </row>
     <row r="50" spans="1:7" ht="36">
       <c r="A50" s="21" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="B50" s="21"/>
       <c r="C50" s="22" t="s">
-        <v>336</v>
+        <v>287</v>
       </c>
       <c r="D50" s="22" t="s">
         <v>235</v>
@@ -4334,7 +4334,7 @@
         <v>141</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="G50" s="22" t="s">
         <v>227</v>
@@ -4342,11 +4342,11 @@
     </row>
     <row r="51" spans="1:7" ht="36">
       <c r="A51" s="21" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="B51" s="21"/>
       <c r="C51" s="22" t="s">
-        <v>337</v>
+        <v>288</v>
       </c>
       <c r="D51" s="22" t="s">
         <v>235</v>
@@ -4355,7 +4355,7 @@
         <v>142</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="G51" s="22" t="s">
         <v>227</v>
@@ -4363,11 +4363,11 @@
     </row>
     <row r="52" spans="1:7" ht="36">
       <c r="A52" s="21" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="B52" s="21"/>
       <c r="C52" s="22" t="s">
-        <v>338</v>
+        <v>289</v>
       </c>
       <c r="D52" s="22" t="s">
         <v>236</v>
@@ -4376,7 +4376,7 @@
         <v>143</v>
       </c>
       <c r="F52" s="22" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="G52" s="22" t="s">
         <v>227</v>
@@ -4384,11 +4384,11 @@
     </row>
     <row r="53" spans="1:7" ht="36">
       <c r="A53" s="21" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B53" s="21"/>
       <c r="C53" s="22" t="s">
-        <v>339</v>
+        <v>290</v>
       </c>
       <c r="D53" s="22" t="s">
         <v>235</v>
@@ -4397,7 +4397,7 @@
         <v>144</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="G53" s="22" t="s">
         <v>227</v>
@@ -4405,11 +4405,11 @@
     </row>
     <row r="54" spans="1:7" ht="24">
       <c r="A54" s="21" t="s">
-        <v>241</v>
+        <v>320</v>
       </c>
       <c r="B54" s="21"/>
       <c r="C54" s="22" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="D54" s="22" t="s">
         <v>235</v>
@@ -4426,11 +4426,11 @@
     </row>
     <row r="55" spans="1:7" ht="24">
       <c r="A55" s="21" t="s">
-        <v>242</v>
+        <v>319</v>
       </c>
       <c r="B55" s="21"/>
       <c r="C55" s="22" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="D55" s="22" t="s">
         <v>235</v>
@@ -4447,11 +4447,11 @@
     </row>
     <row r="56" spans="1:7" ht="24">
       <c r="A56" s="21" t="s">
-        <v>243</v>
+        <v>318</v>
       </c>
       <c r="B56" s="21"/>
       <c r="C56" s="22" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="D56" s="22" t="s">
         <v>235</v>
@@ -4468,11 +4468,11 @@
     </row>
     <row r="57" spans="1:7" ht="24">
       <c r="A57" s="21" t="s">
-        <v>244</v>
+        <v>317</v>
       </c>
       <c r="B57" s="21"/>
       <c r="C57" s="22" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="D57" s="22" t="s">
         <v>235</v>
@@ -4489,11 +4489,11 @@
     </row>
     <row r="58" spans="1:7" ht="24">
       <c r="A58" s="21" t="s">
-        <v>245</v>
+        <v>316</v>
       </c>
       <c r="B58" s="21"/>
       <c r="C58" s="22" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="D58" s="22" t="s">
         <v>235</v>
@@ -4510,11 +4510,11 @@
     </row>
     <row r="59" spans="1:7" ht="24">
       <c r="A59" s="21" t="s">
-        <v>246</v>
+        <v>315</v>
       </c>
       <c r="B59" s="21"/>
       <c r="C59" s="22" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="D59" s="22" t="s">
         <v>236</v>
@@ -4531,11 +4531,11 @@
     </row>
     <row r="60" spans="1:7" ht="24">
       <c r="A60" s="21" t="s">
-        <v>247</v>
+        <v>314</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="22" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="D60" s="22" t="s">
         <v>235</v>
@@ -4552,11 +4552,11 @@
     </row>
     <row r="61" spans="1:7" ht="24">
       <c r="A61" s="21" t="s">
-        <v>248</v>
+        <v>313</v>
       </c>
       <c r="B61" s="21"/>
       <c r="C61" s="22" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="D61" s="22" t="s">
         <v>235</v>
@@ -4565,7 +4565,7 @@
         <v>138</v>
       </c>
       <c r="F61" s="22" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="G61" s="22" t="s">
         <v>239</v>
@@ -4573,11 +4573,11 @@
     </row>
     <row r="62" spans="1:7" ht="24">
       <c r="A62" s="21" t="s">
-        <v>249</v>
+        <v>312</v>
       </c>
       <c r="B62" s="21"/>
       <c r="C62" s="22" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="D62" s="22" t="s">
         <v>235</v>
@@ -4586,7 +4586,7 @@
         <v>139</v>
       </c>
       <c r="F62" s="22" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="G62" s="22" t="s">
         <v>239</v>
@@ -4594,11 +4594,11 @@
     </row>
     <row r="63" spans="1:7" ht="24">
       <c r="A63" s="21" t="s">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="B63" s="21"/>
       <c r="C63" s="22" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="D63" s="22" t="s">
         <v>235</v>
@@ -4607,7 +4607,7 @@
         <v>140</v>
       </c>
       <c r="F63" s="22" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="G63" s="22" t="s">
         <v>239</v>
@@ -4615,11 +4615,11 @@
     </row>
     <row r="64" spans="1:7" ht="24">
       <c r="A64" s="21" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="B64" s="21"/>
       <c r="C64" s="22" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="D64" s="22" t="s">
         <v>235</v>
@@ -4628,7 +4628,7 @@
         <v>141</v>
       </c>
       <c r="F64" s="22" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="G64" s="22" t="s">
         <v>227</v>
@@ -4636,11 +4636,11 @@
     </row>
     <row r="65" spans="1:7" ht="72">
       <c r="A65" s="21" t="s">
-        <v>252</v>
+        <v>309</v>
       </c>
       <c r="B65" s="21"/>
       <c r="C65" s="22" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="D65" s="22" t="s">
         <v>235</v>
@@ -4649,7 +4649,7 @@
         <v>142</v>
       </c>
       <c r="F65" s="22" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="G65" s="22" t="s">
         <v>227</v>
@@ -4657,11 +4657,11 @@
     </row>
     <row r="66" spans="1:7" ht="24">
       <c r="A66" s="21" t="s">
-        <v>253</v>
+        <v>308</v>
       </c>
       <c r="B66" s="21"/>
       <c r="C66" s="22" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="D66" s="22" t="s">
         <v>236</v>
@@ -4670,7 +4670,7 @@
         <v>143</v>
       </c>
       <c r="F66" s="22" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="G66" s="22" t="s">
         <v>227</v>
@@ -4678,11 +4678,11 @@
     </row>
     <row r="67" spans="1:7" ht="24">
       <c r="A67" s="21" t="s">
-        <v>254</v>
+        <v>307</v>
       </c>
       <c r="B67" s="21"/>
       <c r="C67" s="22" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="D67" s="22" t="s">
         <v>235</v>
@@ -4691,7 +4691,7 @@
         <v>144</v>
       </c>
       <c r="F67" s="22" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="G67" s="22" t="s">
         <v>227</v>
@@ -4832,7 +4832,7 @@
     </row>
     <row r="75" spans="1:7" ht="24">
       <c r="A75" s="21" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B75" s="21"/>
       <c r="C75" s="22" t="s">

--- a/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
+++ b/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="375">
   <si>
     <t>测试功能点：查询、插入、更新、分区</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1439,6 +1439,103 @@
   </si>
   <si>
     <t>sequoiadb_fault_003_003_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与预期一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群正常，已经split完成，插入/查询/update</t>
+  </si>
+  <si>
+    <t>插入/查询/update过程中，kill两个主节点</t>
+  </si>
+  <si>
+    <t>插入/查询/update过程中，kill三个主节点</t>
+  </si>
+  <si>
+    <t>插入/查询/update过程中，kill一个备节点</t>
+  </si>
+  <si>
+    <t>插入/查询/update过程中，kill两个备节点（同一组）</t>
+  </si>
+  <si>
+    <t>插入/查询/update过程中，kill两个备节点（不同组）</t>
+  </si>
+  <si>
+    <t>插入/查询/update过程中，kill三个备节点（不同组）</t>
+  </si>
+  <si>
+    <t>sequoiadb_fault_002_001_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入/查询/update过程中，kill一个主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 主节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行1之后操作会报失败，并且在执行步骤2之前会恢复正常，之后一直正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_002_001_002_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 两个主节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_002_001_003_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 三个主节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_002_001_004_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 一个备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一直正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_002_001_005_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 同一组内的两个备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有步骤2之后才能恢复正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_002_001_006_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 两个不同组的备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_002_001_007_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.kill -15 三个不同组的备节点; 2.过一定时间恢复故障</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1723,9 +1820,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1744,6 +1838,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1752,6 +1849,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -2097,7 +2262,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2436,10 +2601,10 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="32" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -2453,8 +2618,8 @@
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="34"/>
-      <c r="B3" s="34"/>
+      <c r="A3" s="33"/>
+      <c r="B3" s="33"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
@@ -2462,8 +2627,8 @@
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="34"/>
-      <c r="B4" s="35"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="34"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
@@ -2471,8 +2636,8 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="34"/>
-      <c r="B5" s="33" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="32" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -2486,8 +2651,8 @@
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="34"/>
-      <c r="B6" s="34"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="5" t="s">
         <v>32</v>
       </c>
@@ -2499,8 +2664,8 @@
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="34"/>
-      <c r="B7" s="35"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -2508,7 +2673,7 @@
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="34"/>
+      <c r="A8" s="33"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -2517,7 +2682,7 @@
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="35"/>
+      <c r="A9" s="34"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -2526,10 +2691,10 @@
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="32" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -2543,8 +2708,8 @@
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="34"/>
-      <c r="B11" s="34"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="33"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -2552,8 +2717,8 @@
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="34"/>
-      <c r="B12" s="35"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="34"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -2561,8 +2726,8 @@
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="34"/>
-      <c r="B13" s="33" t="s">
+      <c r="A13" s="33"/>
+      <c r="B13" s="32" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -2576,8 +2741,8 @@
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="34"/>
-      <c r="B14" s="34"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="33"/>
       <c r="C14" s="5" t="s">
         <v>34</v>
       </c>
@@ -2589,8 +2754,8 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="34"/>
-      <c r="B15" s="34"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="33"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -2598,8 +2763,8 @@
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="34"/>
-      <c r="B16" s="35"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="34"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -2607,8 +2772,8 @@
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="34"/>
-      <c r="B17" s="33" t="s">
+      <c r="A17" s="33"/>
+      <c r="B17" s="32" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -2622,8 +2787,8 @@
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="34"/>
-      <c r="B18" s="34"/>
+      <c r="A18" s="33"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="5" t="s">
         <v>14</v>
       </c>
@@ -2635,8 +2800,8 @@
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="34"/>
-      <c r="B19" s="34"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -2644,8 +2809,8 @@
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="35"/>
-      <c r="B20" s="35"/>
+      <c r="A20" s="34"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -2653,10 +2818,10 @@
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="32" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="5" t="s">
@@ -2670,8 +2835,8 @@
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="34"/>
-      <c r="B22" s="34"/>
+      <c r="A22" s="33"/>
+      <c r="B22" s="33"/>
       <c r="C22" s="5" t="s">
         <v>37</v>
       </c>
@@ -2683,8 +2848,8 @@
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="34"/>
-      <c r="B23" s="34"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="33"/>
       <c r="C23" s="5" t="s">
         <v>38</v>
       </c>
@@ -2696,8 +2861,8 @@
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="34"/>
-      <c r="B24" s="34"/>
+      <c r="A24" s="33"/>
+      <c r="B24" s="33"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -2705,8 +2870,8 @@
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="34"/>
-      <c r="B25" s="35"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="34"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -2714,8 +2879,8 @@
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="34"/>
-      <c r="B26" s="33" t="s">
+      <c r="A26" s="33"/>
+      <c r="B26" s="32" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="5" t="s">
@@ -2729,8 +2894,8 @@
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="34"/>
-      <c r="B27" s="34"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="33"/>
       <c r="C27" s="5" t="s">
         <v>40</v>
       </c>
@@ -2742,8 +2907,8 @@
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="35"/>
-      <c r="B28" s="35"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="34"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -2751,7 +2916,7 @@
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="33" t="s">
+      <c r="A29" s="32" t="s">
         <v>19</v>
       </c>
       <c r="B29" s="5"/>
@@ -2766,7 +2931,7 @@
       <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="34"/>
+      <c r="A30" s="33"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
         <v>41</v>
@@ -2779,7 +2944,7 @@
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="34"/>
+      <c r="A31" s="33"/>
       <c r="B31" s="3"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -2788,7 +2953,7 @@
       <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="35"/>
+      <c r="A32" s="34"/>
       <c r="B32" s="3"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -2843,11 +3008,11 @@
       <c r="A3" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="38"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="37"/>
       <c r="E3" s="11" t="s">
         <v>222</v>
       </c>
@@ -3336,12 +3501,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="27.875" style="9" customWidth="1"/>
     <col min="2" max="2" width="6.125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="25.75" style="17" customWidth="1"/>
+    <col min="3" max="3" width="29.25" style="17" customWidth="1"/>
     <col min="4" max="4" width="26" style="17" customWidth="1"/>
     <col min="5" max="5" width="40.625" style="17" customWidth="1"/>
     <col min="6" max="6" width="30" style="17" customWidth="1"/>
@@ -3394,7 +3559,9 @@
       <c r="F4" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="G4" s="22"/>
+      <c r="G4" s="21" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="5" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A5" s="21" t="s">
@@ -3413,7 +3580,9 @@
       <c r="F5" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="G5" s="22"/>
+      <c r="G5" s="21" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="6" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A6" s="21" t="s">
@@ -3432,7 +3601,9 @@
       <c r="F6" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="22"/>
+      <c r="G6" s="21" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="7" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A7" s="21" t="s">
@@ -3451,7 +3622,9 @@
       <c r="F7" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="G7" s="22"/>
+      <c r="G7" s="21" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="24">
       <c r="A8" s="21" t="s">
@@ -3470,7 +3643,9 @@
       <c r="F8" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="G8" s="16"/>
+      <c r="G8" s="21" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="24">
       <c r="A9" s="21" t="s">
@@ -3489,7 +3664,9 @@
       <c r="F9" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="G9" s="16"/>
+      <c r="G9" s="21" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="24">
       <c r="A10" s="21" t="s">
@@ -3508,7 +3685,9 @@
       <c r="F10" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="G10" s="16"/>
+      <c r="G10" s="21" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="24">
       <c r="A11" s="24" t="s">
@@ -3668,160 +3847,160 @@
         <v>227</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="36">
-      <c r="A19" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="22" t="s">
-        <v>291</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="F19" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="G19" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="36">
-      <c r="A20" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="B20" s="21"/>
-      <c r="C20" s="22" t="s">
-        <v>292</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="F20" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="G20" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="36">
-      <c r="A21" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="22" t="s">
-        <v>293</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="G21" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="36">
-      <c r="A22" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="22" t="s">
-        <v>294</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="F22" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="G22" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="72">
-      <c r="A23" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="22" t="s">
-        <v>295</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="F23" s="22" t="s">
-        <v>269</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="36">
-      <c r="A24" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="22" t="s">
-        <v>296</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="G24" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="36">
-      <c r="A25" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="22" t="s">
-        <v>297</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="F25" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="G25" s="22" t="s">
-        <v>227</v>
+    <row r="19" spans="1:7" ht="24">
+      <c r="A19" s="19" t="s">
+        <v>357</v>
+      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="24">
+      <c r="A20" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="24">
+      <c r="A21" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="24">
+      <c r="A22" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>366</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="24">
+      <c r="A23" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="20" t="s">
+        <v>354</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="24">
+      <c r="A24" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="24">
+      <c r="A25" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>374</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="36">
       <c r="A26" s="21" t="s">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="22" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="D26" s="22" t="s">
         <v>235</v>
@@ -3838,11 +4017,11 @@
     </row>
     <row r="27" spans="1:7" ht="36">
       <c r="A27" s="21" t="s">
-        <v>347</v>
+        <v>301</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="22" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="D27" s="22" t="s">
         <v>235</v>
@@ -3859,11 +4038,11 @@
     </row>
     <row r="28" spans="1:7" ht="36">
       <c r="A28" s="21" t="s">
-        <v>346</v>
+        <v>302</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="22" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="D28" s="22" t="s">
         <v>235</v>
@@ -3880,11 +4059,11 @@
     </row>
     <row r="29" spans="1:7" ht="36">
       <c r="A29" s="21" t="s">
-        <v>345</v>
+        <v>303</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="22" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="D29" s="22" t="s">
         <v>235</v>
@@ -3901,11 +4080,11 @@
     </row>
     <row r="30" spans="1:7" ht="72">
       <c r="A30" s="21" t="s">
-        <v>344</v>
+        <v>306</v>
       </c>
       <c r="B30" s="21"/>
       <c r="C30" s="22" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="D30" s="22" t="s">
         <v>235</v>
@@ -3922,11 +4101,11 @@
     </row>
     <row r="31" spans="1:7" ht="36">
       <c r="A31" s="21" t="s">
-        <v>343</v>
+        <v>305</v>
       </c>
       <c r="B31" s="21"/>
       <c r="C31" s="22" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="D31" s="22" t="s">
         <v>236</v>
@@ -3943,11 +4122,11 @@
     </row>
     <row r="32" spans="1:7" ht="36">
       <c r="A32" s="21" t="s">
-        <v>342</v>
+        <v>304</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="22" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="D32" s="22" t="s">
         <v>235</v>
@@ -3963,159 +4142,159 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="36">
-      <c r="A33" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="D33" s="22" t="s">
+      <c r="A33" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="D33" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="F33" s="22" t="s">
+      <c r="F33" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="G33" s="22" t="s">
+      <c r="G33" s="20" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="36">
-      <c r="A34" s="21" t="s">
-        <v>340</v>
-      </c>
-      <c r="B34" s="21"/>
-      <c r="C34" s="22" t="s">
-        <v>271</v>
-      </c>
-      <c r="D34" s="22" t="s">
+      <c r="A34" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="D34" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="E34" s="22" t="s">
+      <c r="E34" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="F34" s="22" t="s">
+      <c r="F34" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="G34" s="22" t="s">
+      <c r="G34" s="20" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="36">
-      <c r="A35" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="B35" s="21"/>
-      <c r="C35" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="D35" s="22" t="s">
+      <c r="A35" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="D35" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="E35" s="22" t="s">
+      <c r="E35" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="F35" s="22" t="s">
+      <c r="F35" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="G35" s="22" t="s">
+      <c r="G35" s="20" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="36">
-      <c r="A36" s="21" t="s">
-        <v>338</v>
-      </c>
-      <c r="B36" s="21"/>
-      <c r="C36" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="D36" s="22" t="s">
+      <c r="A36" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="D36" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="E36" s="22" t="s">
+      <c r="E36" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="F36" s="22" t="s">
+      <c r="F36" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="G36" s="22" t="s">
+      <c r="G36" s="20" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="72">
-      <c r="A37" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="B37" s="21"/>
-      <c r="C37" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="D37" s="22" t="s">
+      <c r="A37" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="D37" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="E37" s="22" t="s">
+      <c r="E37" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="F37" s="22" t="s">
+      <c r="F37" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="G37" s="22" t="s">
+      <c r="G37" s="20" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="36">
-      <c r="A38" s="21" t="s">
-        <v>336</v>
-      </c>
-      <c r="B38" s="21"/>
-      <c r="C38" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="D38" s="22" t="s">
+      <c r="A38" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="D38" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="E38" s="22" t="s">
+      <c r="E38" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="F38" s="22" t="s">
+      <c r="F38" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="20" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="36">
-      <c r="A39" s="21" t="s">
-        <v>335</v>
-      </c>
-      <c r="B39" s="21"/>
-      <c r="C39" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="D39" s="22" t="s">
+      <c r="A39" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="D39" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="E39" s="22" t="s">
+      <c r="E39" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="F39" s="22" t="s">
+      <c r="F39" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="G39" s="22" t="s">
+      <c r="G39" s="20" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="36">
       <c r="A40" s="21" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="B40" s="21"/>
       <c r="C40" s="22" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="D40" s="22" t="s">
         <v>235</v>
@@ -4132,11 +4311,11 @@
     </row>
     <row r="41" spans="1:7" ht="36">
       <c r="A41" s="21" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B41" s="21"/>
       <c r="C41" s="22" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="D41" s="22" t="s">
         <v>235</v>
@@ -4144,7 +4323,7 @@
       <c r="E41" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="F41" s="32" t="s">
+      <c r="F41" s="22" t="s">
         <v>260</v>
       </c>
       <c r="G41" s="22" t="s">
@@ -4153,11 +4332,11 @@
     </row>
     <row r="42" spans="1:7" ht="36">
       <c r="A42" s="21" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B42" s="21"/>
       <c r="C42" s="22" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="D42" s="22" t="s">
         <v>235</v>
@@ -4174,11 +4353,11 @@
     </row>
     <row r="43" spans="1:7" ht="36">
       <c r="A43" s="21" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="B43" s="21"/>
       <c r="C43" s="22" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="D43" s="22" t="s">
         <v>235</v>
@@ -4187,19 +4366,19 @@
         <v>141</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>298</v>
+        <v>268</v>
       </c>
       <c r="G43" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="36">
+    <row r="44" spans="1:7" ht="72">
       <c r="A44" s="21" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="22" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D44" s="22" t="s">
         <v>235</v>
@@ -4208,7 +4387,7 @@
         <v>142</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="G44" s="22" t="s">
         <v>227</v>
@@ -4216,11 +4395,11 @@
     </row>
     <row r="45" spans="1:7" ht="36">
       <c r="A45" s="21" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="22" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="D45" s="22" t="s">
         <v>236</v>
@@ -4229,7 +4408,7 @@
         <v>143</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="G45" s="22" t="s">
         <v>227</v>
@@ -4237,11 +4416,11 @@
     </row>
     <row r="46" spans="1:7" ht="36">
       <c r="A46" s="21" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B46" s="21"/>
       <c r="C46" s="22" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="D46" s="22" t="s">
         <v>235</v>
@@ -4250,166 +4429,166 @@
         <v>144</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="G46" s="22" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="36">
-      <c r="A47" s="21" t="s">
+      <c r="A47" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="B47" s="19"/>
+      <c r="C47" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="D47" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="G47" s="20" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="36">
+      <c r="A48" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="B48" s="19"/>
+      <c r="C48" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F48" s="38" t="s">
+        <v>260</v>
+      </c>
+      <c r="G48" s="20" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="36">
+      <c r="A49" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="B49" s="19"/>
+      <c r="C49" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="D49" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="G49" s="20" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="36">
+      <c r="A50" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="B50" s="19"/>
+      <c r="C50" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="G50" s="20" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="36">
+      <c r="A51" s="19" t="s">
+        <v>330</v>
+      </c>
+      <c r="B51" s="19"/>
+      <c r="C51" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="D51" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="F51" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="G51" s="20" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="36">
+      <c r="A52" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="B52" s="19"/>
+      <c r="C52" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="D52" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="F52" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="G52" s="20" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="36">
+      <c r="A53" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="B53" s="19"/>
+      <c r="C53" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="D53" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="F53" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="G53" s="20" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="36">
+      <c r="A54" s="21" t="s">
         <v>327</v>
-      </c>
-      <c r="B47" s="21"/>
-      <c r="C47" s="22" t="s">
-        <v>284</v>
-      </c>
-      <c r="D47" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="E47" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="F47" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="G47" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="36">
-      <c r="A48" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="B48" s="21"/>
-      <c r="C48" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="D48" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="F48" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="G48" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="36">
-      <c r="A49" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="B49" s="21"/>
-      <c r="C49" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="D49" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="E49" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="F49" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="G49" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="36">
-      <c r="A50" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="B50" s="21"/>
-      <c r="C50" s="22" t="s">
-        <v>287</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="E50" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="F50" s="22" t="s">
-        <v>299</v>
-      </c>
-      <c r="G50" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="36">
-      <c r="A51" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="B51" s="21"/>
-      <c r="C51" s="22" t="s">
-        <v>288</v>
-      </c>
-      <c r="D51" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="E51" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="F51" s="22" t="s">
-        <v>299</v>
-      </c>
-      <c r="G51" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="36">
-      <c r="A52" s="21" t="s">
-        <v>322</v>
-      </c>
-      <c r="B52" s="21"/>
-      <c r="C52" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="E52" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="F52" s="22" t="s">
-        <v>299</v>
-      </c>
-      <c r="G52" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="36">
-      <c r="A53" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="B53" s="21"/>
-      <c r="C53" s="22" t="s">
-        <v>290</v>
-      </c>
-      <c r="D53" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="E53" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="F53" s="22" t="s">
-        <v>299</v>
-      </c>
-      <c r="G53" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="24">
-      <c r="A54" s="21" t="s">
-        <v>320</v>
       </c>
       <c r="B54" s="21"/>
       <c r="C54" s="22" t="s">
-        <v>242</v>
+        <v>284</v>
       </c>
       <c r="D54" s="22" t="s">
         <v>235</v>
@@ -4418,19 +4597,19 @@
         <v>138</v>
       </c>
       <c r="F54" s="22" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="G54" s="22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="24">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="36">
       <c r="A55" s="21" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B55" s="21"/>
       <c r="C55" s="22" t="s">
-        <v>243</v>
+        <v>285</v>
       </c>
       <c r="D55" s="22" t="s">
         <v>235</v>
@@ -4439,19 +4618,19 @@
         <v>139</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="G55" s="22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="24">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="36">
       <c r="A56" s="21" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B56" s="21"/>
       <c r="C56" s="22" t="s">
-        <v>244</v>
+        <v>286</v>
       </c>
       <c r="D56" s="22" t="s">
         <v>235</v>
@@ -4460,19 +4639,19 @@
         <v>140</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="G56" s="22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="24">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="36">
       <c r="A57" s="21" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B57" s="21"/>
       <c r="C57" s="22" t="s">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="D57" s="22" t="s">
         <v>235</v>
@@ -4481,19 +4660,19 @@
         <v>141</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="G57" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="24">
+    <row r="58" spans="1:7" ht="36">
       <c r="A58" s="21" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B58" s="21"/>
       <c r="C58" s="22" t="s">
-        <v>246</v>
+        <v>288</v>
       </c>
       <c r="D58" s="22" t="s">
         <v>235</v>
@@ -4502,19 +4681,19 @@
         <v>142</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="G58" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="24">
+    <row r="59" spans="1:7" ht="36">
       <c r="A59" s="21" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B59" s="21"/>
       <c r="C59" s="22" t="s">
-        <v>247</v>
+        <v>289</v>
       </c>
       <c r="D59" s="22" t="s">
         <v>236</v>
@@ -4523,19 +4702,19 @@
         <v>143</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="G59" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="24">
+    <row r="60" spans="1:7" ht="36">
       <c r="A60" s="21" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="22" t="s">
-        <v>248</v>
+        <v>290</v>
       </c>
       <c r="D60" s="22" t="s">
         <v>235</v>
@@ -4544,166 +4723,166 @@
         <v>144</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="G60" s="22" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="24">
-      <c r="A61" s="21" t="s">
-        <v>313</v>
-      </c>
-      <c r="B61" s="21"/>
-      <c r="C61" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="D61" s="22" t="s">
+      <c r="A61" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="B61" s="19"/>
+      <c r="C61" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="D61" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="E61" s="22" t="s">
+      <c r="E61" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="F61" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="G61" s="22" t="s">
+      <c r="F61" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="G61" s="20" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="24">
-      <c r="A62" s="21" t="s">
-        <v>312</v>
-      </c>
-      <c r="B62" s="21"/>
-      <c r="C62" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="D62" s="22" t="s">
+      <c r="A62" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="B62" s="19"/>
+      <c r="C62" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="D62" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="E62" s="22" t="s">
+      <c r="E62" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="F62" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="G62" s="22" t="s">
+      <c r="F62" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="G62" s="20" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="24">
-      <c r="A63" s="21" t="s">
-        <v>311</v>
-      </c>
-      <c r="B63" s="21"/>
-      <c r="C63" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="D63" s="22" t="s">
+      <c r="A63" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B63" s="19"/>
+      <c r="C63" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="D63" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="E63" s="22" t="s">
+      <c r="E63" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="F63" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="G63" s="22" t="s">
+      <c r="F63" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="G63" s="20" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="24">
-      <c r="A64" s="21" t="s">
-        <v>310</v>
-      </c>
-      <c r="B64" s="21"/>
-      <c r="C64" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="D64" s="22" t="s">
+      <c r="A64" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="B64" s="19"/>
+      <c r="C64" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="D64" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="E64" s="22" t="s">
+      <c r="E64" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="F64" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="G64" s="22" t="s">
+      <c r="F64" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="G64" s="20" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="72">
-      <c r="A65" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="B65" s="21"/>
-      <c r="C65" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="D65" s="22" t="s">
+    <row r="65" spans="1:7" ht="24">
+      <c r="A65" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="B65" s="19"/>
+      <c r="C65" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="D65" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="E65" s="22" t="s">
+      <c r="E65" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="F65" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="G65" s="22" t="s">
+      <c r="F65" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="G65" s="20" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="24">
-      <c r="A66" s="21" t="s">
-        <v>308</v>
-      </c>
-      <c r="B66" s="21"/>
-      <c r="C66" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="D66" s="22" t="s">
+      <c r="A66" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="B66" s="19"/>
+      <c r="C66" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="D66" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="E66" s="22" t="s">
+      <c r="E66" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="F66" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="G66" s="22" t="s">
+      <c r="F66" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="G66" s="20" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="24">
-      <c r="A67" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="B67" s="21"/>
-      <c r="C67" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="D67" s="22" t="s">
+      <c r="A67" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="B67" s="19"/>
+      <c r="C67" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="D67" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="E67" s="22" t="s">
+      <c r="E67" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="F67" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="G67" s="22" t="s">
+      <c r="F67" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="G67" s="20" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="24">
       <c r="A68" s="21" t="s">
-        <v>228</v>
+        <v>313</v>
       </c>
       <c r="B68" s="21"/>
       <c r="C68" s="22" t="s">
-        <v>131</v>
+        <v>249</v>
       </c>
       <c r="D68" s="22" t="s">
         <v>235</v>
@@ -4711,18 +4890,20 @@
       <c r="E68" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="F68" s="22"/>
+      <c r="F68" s="22" t="s">
+        <v>256</v>
+      </c>
       <c r="G68" s="22" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="24">
       <c r="A69" s="21" t="s">
-        <v>229</v>
+        <v>312</v>
       </c>
       <c r="B69" s="21"/>
       <c r="C69" s="22" t="s">
-        <v>132</v>
+        <v>250</v>
       </c>
       <c r="D69" s="22" t="s">
         <v>235</v>
@@ -4730,18 +4911,20 @@
       <c r="E69" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="F69" s="22"/>
+      <c r="F69" s="22" t="s">
+        <v>256</v>
+      </c>
       <c r="G69" s="22" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="24">
       <c r="A70" s="21" t="s">
-        <v>230</v>
+        <v>311</v>
       </c>
       <c r="B70" s="21"/>
       <c r="C70" s="22" t="s">
-        <v>133</v>
+        <v>251</v>
       </c>
       <c r="D70" s="22" t="s">
         <v>235</v>
@@ -4749,18 +4932,20 @@
       <c r="E70" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="F70" s="22"/>
+      <c r="F70" s="22" t="s">
+        <v>256</v>
+      </c>
       <c r="G70" s="22" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="24">
       <c r="A71" s="21" t="s">
-        <v>231</v>
+        <v>310</v>
       </c>
       <c r="B71" s="21"/>
       <c r="C71" s="22" t="s">
-        <v>134</v>
+        <v>252</v>
       </c>
       <c r="D71" s="22" t="s">
         <v>235</v>
@@ -4768,18 +4953,20 @@
       <c r="E71" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="F71" s="22"/>
+      <c r="F71" s="22" t="s">
+        <v>257</v>
+      </c>
       <c r="G71" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="24">
+    <row r="72" spans="1:7" ht="72">
       <c r="A72" s="21" t="s">
-        <v>232</v>
+        <v>309</v>
       </c>
       <c r="B72" s="21"/>
       <c r="C72" s="22" t="s">
-        <v>135</v>
+        <v>253</v>
       </c>
       <c r="D72" s="22" t="s">
         <v>235</v>
@@ -4787,18 +4974,20 @@
       <c r="E72" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="F72" s="22"/>
+      <c r="F72" s="22" t="s">
+        <v>258</v>
+      </c>
       <c r="G72" s="22" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="24">
       <c r="A73" s="21" t="s">
-        <v>233</v>
+        <v>308</v>
       </c>
       <c r="B73" s="21"/>
       <c r="C73" s="22" t="s">
-        <v>136</v>
+        <v>254</v>
       </c>
       <c r="D73" s="22" t="s">
         <v>236</v>
@@ -4806,18 +4995,20 @@
       <c r="E73" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="F73" s="22"/>
+      <c r="F73" s="22" t="s">
+        <v>257</v>
+      </c>
       <c r="G73" s="22" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="24">
       <c r="A74" s="21" t="s">
-        <v>234</v>
+        <v>307</v>
       </c>
       <c r="B74" s="21"/>
       <c r="C74" s="22" t="s">
-        <v>137</v>
+        <v>255</v>
       </c>
       <c r="D74" s="22" t="s">
         <v>235</v>
@@ -4825,508 +5016,571 @@
       <c r="E74" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="F74" s="22"/>
+      <c r="F74" s="22" t="s">
+        <v>257</v>
+      </c>
       <c r="G74" s="22" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="24">
-      <c r="A75" s="21" t="s">
+      <c r="A75" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="B75" s="19"/>
+      <c r="C75" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="D75" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="E75" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="24">
+      <c r="A76" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B76" s="19"/>
+      <c r="C76" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="D76" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="24">
+      <c r="A77" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B77" s="19"/>
+      <c r="C77" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="D77" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="E77" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F77" s="20"/>
+      <c r="G77" s="20" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="24">
+      <c r="A78" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="B78" s="19"/>
+      <c r="C78" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="D78" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="E78" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F78" s="20"/>
+      <c r="G78" s="20" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="24">
+      <c r="A79" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="B79" s="19"/>
+      <c r="C79" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="D79" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="E79" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="F79" s="20"/>
+      <c r="G79" s="20" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="24">
+      <c r="A80" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="B80" s="19"/>
+      <c r="C80" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="D80" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="E80" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="F80" s="20"/>
+      <c r="G80" s="20" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="24">
+      <c r="A81" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="B81" s="19"/>
+      <c r="C81" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D81" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="E81" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="F81" s="20"/>
+      <c r="G81" s="20" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="24">
+      <c r="A82" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="B75" s="21"/>
-      <c r="C75" s="22" t="s">
+      <c r="B82" s="21"/>
+      <c r="C82" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="D75" s="22" t="s">
+      <c r="D82" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="E75" s="22" t="s">
+      <c r="E82" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="F75" s="22"/>
-      <c r="G75" s="22" t="s">
+      <c r="F82" s="22"/>
+      <c r="G82" s="22" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="24">
-      <c r="A76" s="21" t="s">
+    <row r="83" spans="1:7" ht="24">
+      <c r="A83" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="B76" s="21"/>
-      <c r="C76" s="22" t="s">
+      <c r="B83" s="21"/>
+      <c r="C83" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="D76" s="22" t="s">
+      <c r="D83" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="E76" s="22" t="s">
+      <c r="E83" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="F76" s="22"/>
-      <c r="G76" s="22" t="s">
+      <c r="F83" s="22"/>
+      <c r="G83" s="22" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="24">
-      <c r="A77" s="21" t="s">
+    <row r="84" spans="1:7" ht="24">
+      <c r="A84" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="B77" s="21"/>
-      <c r="C77" s="22" t="s">
+      <c r="B84" s="21"/>
+      <c r="C84" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="D77" s="22" t="s">
+      <c r="D84" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="E77" s="22" t="s">
+      <c r="E84" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="F77" s="22"/>
-      <c r="G77" s="22" t="s">
+      <c r="F84" s="22"/>
+      <c r="G84" s="22" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="24">
-      <c r="A78" s="21" t="s">
+    <row r="85" spans="1:7" ht="24">
+      <c r="A85" s="21" t="s">
         <v>231</v>
       </c>
-      <c r="B78" s="21"/>
-      <c r="C78" s="22" t="s">
+      <c r="B85" s="21"/>
+      <c r="C85" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="D78" s="22" t="s">
+      <c r="D85" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="E78" s="22" t="s">
+      <c r="E85" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="F78" s="22"/>
-      <c r="G78" s="22" t="s">
+      <c r="F85" s="22"/>
+      <c r="G85" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="24">
-      <c r="A79" s="21" t="s">
+    <row r="86" spans="1:7" ht="24">
+      <c r="A86" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="B79" s="21"/>
-      <c r="C79" s="22" t="s">
+      <c r="B86" s="21"/>
+      <c r="C86" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="D79" s="22" t="s">
+      <c r="D86" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="E79" s="22" t="s">
+      <c r="E86" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="F79" s="22"/>
-      <c r="G79" s="22" t="s">
+      <c r="F86" s="22"/>
+      <c r="G86" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="24">
-      <c r="A80" s="21" t="s">
+    <row r="87" spans="1:7" ht="24">
+      <c r="A87" s="21" t="s">
         <v>233</v>
       </c>
-      <c r="B80" s="21"/>
-      <c r="C80" s="22" t="s">
+      <c r="B87" s="21"/>
+      <c r="C87" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="D80" s="22" t="s">
+      <c r="D87" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="E80" s="22" t="s">
+      <c r="E87" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="F80" s="22"/>
-      <c r="G80" s="22" t="s">
+      <c r="F87" s="22"/>
+      <c r="G87" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="24">
-      <c r="A81" s="21" t="s">
+    <row r="88" spans="1:7" ht="24">
+      <c r="A88" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="B81" s="21"/>
-      <c r="C81" s="22" t="s">
+      <c r="B88" s="21"/>
+      <c r="C88" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="D81" s="22" t="s">
+      <c r="D88" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="E81" s="22" t="s">
+      <c r="E88" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="F81" s="22"/>
-      <c r="G81" s="22" t="s">
+      <c r="F88" s="22"/>
+      <c r="G88" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="24">
-      <c r="A82" s="19" t="s">
+    <row r="89" spans="1:7" ht="24">
+      <c r="A89" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="B82" s="19"/>
-      <c r="C82" s="20" t="s">
+      <c r="B89" s="19"/>
+      <c r="C89" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="D82" s="20" t="s">
+      <c r="D89" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E82" s="20" t="s">
+      <c r="E89" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="F82" s="20" t="s">
+      <c r="F89" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G82" s="20"/>
-    </row>
-    <row r="83" spans="1:7" ht="24">
-      <c r="A83" s="19" t="s">
+      <c r="G89" s="20"/>
+    </row>
+    <row r="90" spans="1:7" ht="24">
+      <c r="A90" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="B83" s="19"/>
-      <c r="C83" s="20" t="s">
+      <c r="B90" s="19"/>
+      <c r="C90" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="D83" s="20" t="s">
+      <c r="D90" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E83" s="20" t="s">
+      <c r="E90" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="F83" s="20" t="s">
+      <c r="F90" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G83" s="20"/>
-    </row>
-    <row r="84" spans="1:7" ht="24">
-      <c r="A84" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="B84" s="19"/>
-      <c r="C84" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="D84" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E84" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="F84" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G84" s="20"/>
-    </row>
-    <row r="85" spans="1:7" ht="24">
-      <c r="A85" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="B85" s="19"/>
-      <c r="C85" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="D85" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E85" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="F85" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G85" s="20"/>
-    </row>
-    <row r="86" spans="1:7" ht="24">
-      <c r="A86" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="B86" s="19"/>
-      <c r="C86" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="D86" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E86" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="F86" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G86" s="20"/>
-    </row>
-    <row r="87" spans="1:7" ht="24">
-      <c r="A87" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="B87" s="19"/>
-      <c r="C87" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="D87" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E87" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="F87" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G87" s="20"/>
-    </row>
-    <row r="88" spans="1:7" ht="24">
-      <c r="A88" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="B88" s="19"/>
-      <c r="C88" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="D88" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E88" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="F88" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G88" s="20"/>
-    </row>
-    <row r="89" spans="1:7" ht="24">
-      <c r="A89" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="B89" s="14"/>
-      <c r="C89" s="16"/>
-      <c r="D89" s="16"/>
-      <c r="E89" s="16"/>
-      <c r="F89" s="16"/>
-      <c r="G89" s="16"/>
-    </row>
-    <row r="90" spans="1:7" ht="24">
-      <c r="A90" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="B90" s="14"/>
-      <c r="C90" s="16"/>
-      <c r="D90" s="16"/>
-      <c r="E90" s="16"/>
-      <c r="F90" s="16"/>
-      <c r="G90" s="16"/>
+      <c r="G90" s="20"/>
     </row>
     <row r="91" spans="1:7" ht="24">
       <c r="A91" s="19" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="B91" s="19"/>
       <c r="C91" s="20" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="D91" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="F91" s="20" t="s">
-        <v>194</v>
+        <v>29</v>
       </c>
       <c r="G91" s="20"/>
     </row>
     <row r="92" spans="1:7" ht="24">
       <c r="A92" s="19" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="B92" s="19"/>
       <c r="C92" s="20" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="D92" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="F92" s="20" t="s">
-        <v>194</v>
+        <v>102</v>
       </c>
       <c r="G92" s="20"/>
     </row>
     <row r="93" spans="1:7" ht="24">
       <c r="A93" s="19" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="B93" s="19"/>
       <c r="C93" s="20" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="D93" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E93" s="20" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="F93" s="20" t="s">
-        <v>194</v>
+        <v>102</v>
       </c>
       <c r="G93" s="20"/>
     </row>
     <row r="94" spans="1:7" ht="24">
       <c r="A94" s="19" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="B94" s="19"/>
       <c r="C94" s="20" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="D94" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E94" s="20" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="F94" s="20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G94" s="20"/>
     </row>
     <row r="95" spans="1:7" ht="24">
       <c r="A95" s="19" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="B95" s="19"/>
       <c r="C95" s="20" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="D95" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E95" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F95" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G95" s="20"/>
+    </row>
+    <row r="96" spans="1:7" ht="24">
+      <c r="A96" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="B96" s="14"/>
+      <c r="C96" s="16"/>
+      <c r="D96" s="16"/>
+      <c r="E96" s="16"/>
+      <c r="F96" s="16"/>
+      <c r="G96" s="16"/>
+    </row>
+    <row r="97" spans="1:7" ht="24">
+      <c r="A97" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="B97" s="14"/>
+      <c r="C97" s="16"/>
+      <c r="D97" s="16"/>
+      <c r="E97" s="16"/>
+      <c r="F97" s="16"/>
+      <c r="G97" s="16"/>
+    </row>
+    <row r="98" spans="1:7" ht="24">
+      <c r="A98" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="B98" s="19"/>
+      <c r="C98" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="D98" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E98" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="F98" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G98" s="20"/>
+    </row>
+    <row r="99" spans="1:7" ht="24">
+      <c r="A99" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="B99" s="19"/>
+      <c r="C99" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="D99" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E99" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="F99" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G99" s="20"/>
+    </row>
+    <row r="100" spans="1:7" ht="24">
+      <c r="A100" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B100" s="19"/>
+      <c r="C100" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="D100" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E100" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="F100" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G100" s="20"/>
+    </row>
+    <row r="101" spans="1:7" ht="24">
+      <c r="A101" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="B101" s="19"/>
+      <c r="C101" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="D101" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E101" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="F101" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="G101" s="20"/>
+    </row>
+    <row r="102" spans="1:7" ht="24">
+      <c r="A102" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B102" s="19"/>
+      <c r="C102" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="D102" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E102" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="F95" s="20" t="s">
+      <c r="F102" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="G95" s="20"/>
-    </row>
-    <row r="96" spans="1:7" ht="24">
-      <c r="A96" s="19" t="s">
+      <c r="G102" s="20"/>
+    </row>
+    <row r="103" spans="1:7" ht="24">
+      <c r="A103" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="B96" s="19"/>
-      <c r="C96" s="20" t="s">
+      <c r="B103" s="19"/>
+      <c r="C103" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="D96" s="20" t="s">
+      <c r="D103" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E96" s="20" t="s">
+      <c r="E103" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="F96" s="20" t="s">
+      <c r="F103" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="G96" s="20"/>
-    </row>
-    <row r="97" spans="1:7" ht="24">
-      <c r="A97" s="19" t="s">
+      <c r="G103" s="20"/>
+    </row>
+    <row r="104" spans="1:7" ht="24">
+      <c r="A104" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="B97" s="19"/>
-      <c r="C97" s="20" t="s">
+      <c r="B104" s="19"/>
+      <c r="C104" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="D97" s="20" t="s">
+      <c r="D104" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E97" s="20" t="s">
+      <c r="E104" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="F97" s="20" t="s">
+      <c r="F104" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="G97" s="20"/>
-    </row>
-    <row r="98" spans="1:7" ht="24">
-      <c r="A98" s="25" t="s">
+      <c r="G104" s="20"/>
+    </row>
+    <row r="105" spans="1:7" ht="24">
+      <c r="A105" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="B98" s="14"/>
-      <c r="C98" s="16"/>
-      <c r="D98" s="16"/>
-      <c r="E98" s="16"/>
-      <c r="F98" s="16"/>
-      <c r="G98" s="16"/>
-    </row>
-    <row r="99" spans="1:7" ht="24">
-      <c r="A99" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="B99" s="14"/>
-      <c r="C99" s="16"/>
-      <c r="D99" s="16"/>
-      <c r="E99" s="16"/>
-      <c r="F99" s="16"/>
-      <c r="G99" s="16"/>
-    </row>
-    <row r="100" spans="1:7" ht="24">
-      <c r="A100" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="B100" s="21"/>
-      <c r="C100" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="D100" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E100" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="F100" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="G100" s="16"/>
-    </row>
-    <row r="101" spans="1:7">
-      <c r="A101" s="16"/>
-      <c r="B101" s="14"/>
-      <c r="C101" s="16"/>
-      <c r="D101" s="16"/>
-      <c r="E101" s="16"/>
-      <c r="F101" s="16"/>
-      <c r="G101" s="16"/>
-    </row>
-    <row r="102" spans="1:7">
-      <c r="A102" s="16"/>
-      <c r="B102" s="14"/>
-      <c r="C102" s="16"/>
-      <c r="D102" s="16"/>
-      <c r="E102" s="16"/>
-      <c r="F102" s="16"/>
-      <c r="G102" s="16"/>
-    </row>
-    <row r="103" spans="1:7">
-      <c r="C103" s="9"/>
-      <c r="D103" s="9"/>
-      <c r="E103" s="9"/>
-      <c r="F103" s="9"/>
-    </row>
-    <row r="104" spans="1:7">
-      <c r="A104" s="21"/>
-      <c r="B104" s="21"/>
-      <c r="C104" s="16"/>
-      <c r="D104" s="16"/>
-      <c r="E104" s="16"/>
-      <c r="F104" s="16"/>
-      <c r="G104" s="16"/>
-    </row>
-    <row r="105" spans="1:7">
-      <c r="A105" s="14"/>
       <c r="B105" s="14"/>
       <c r="C105" s="16"/>
       <c r="D105" s="16"/>
@@ -5335,64 +5589,46 @@
       <c r="G105" s="16"/>
     </row>
     <row r="106" spans="1:7" ht="24">
-      <c r="A106" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="B106" s="21"/>
-      <c r="C106" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D106" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E106" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="F106" s="16" t="s">
-        <v>116</v>
-      </c>
+      <c r="A106" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="B106" s="14"/>
+      <c r="C106" s="16"/>
+      <c r="D106" s="16"/>
+      <c r="E106" s="16"/>
+      <c r="F106" s="16"/>
       <c r="G106" s="16"/>
     </row>
     <row r="107" spans="1:7" ht="24">
       <c r="A107" s="21" t="s">
-        <v>117</v>
+        <v>198</v>
       </c>
       <c r="B107" s="21"/>
       <c r="C107" s="16" t="s">
-        <v>119</v>
+        <v>199</v>
       </c>
       <c r="D107" s="16" t="s">
         <v>98</v>
       </c>
       <c r="E107" s="16" t="s">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="F107" s="16" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G107" s="16"/>
     </row>
-    <row r="108" spans="1:7" ht="24">
-      <c r="A108" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="B108" s="21"/>
-      <c r="C108" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="D108" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E108" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F108" s="16" t="s">
-        <v>116</v>
-      </c>
+    <row r="108" spans="1:7">
+      <c r="A108" s="16"/>
+      <c r="B108" s="14"/>
+      <c r="C108" s="16"/>
+      <c r="D108" s="16"/>
+      <c r="E108" s="16"/>
+      <c r="F108" s="16"/>
       <c r="G108" s="16"/>
     </row>
     <row r="109" spans="1:7">
-      <c r="A109" s="14"/>
+      <c r="A109" s="16"/>
       <c r="B109" s="14"/>
       <c r="C109" s="16"/>
       <c r="D109" s="16"/>
@@ -5401,17 +5637,14 @@
       <c r="G109" s="16"/>
     </row>
     <row r="110" spans="1:7">
-      <c r="A110" s="14"/>
-      <c r="B110" s="14"/>
-      <c r="C110" s="16"/>
-      <c r="D110" s="16"/>
-      <c r="E110" s="16"/>
-      <c r="F110" s="16"/>
-      <c r="G110" s="16"/>
+      <c r="C110" s="9"/>
+      <c r="D110" s="9"/>
+      <c r="E110" s="9"/>
+      <c r="F110" s="9"/>
     </row>
     <row r="111" spans="1:7">
-      <c r="A111" s="14"/>
-      <c r="B111" s="14"/>
+      <c r="A111" s="21"/>
+      <c r="B111" s="21"/>
       <c r="C111" s="16"/>
       <c r="D111" s="16"/>
       <c r="E111" s="16"/>
@@ -5427,31 +5660,61 @@
       <c r="F112" s="16"/>
       <c r="G112" s="16"/>
     </row>
-    <row r="113" spans="1:7">
-      <c r="A113" s="14"/>
-      <c r="B113" s="14"/>
-      <c r="C113" s="16"/>
-      <c r="D113" s="16"/>
-      <c r="E113" s="16"/>
-      <c r="F113" s="16"/>
+    <row r="113" spans="1:7" ht="24">
+      <c r="A113" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B113" s="21"/>
+      <c r="C113" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D113" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E113" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="F113" s="16" t="s">
+        <v>116</v>
+      </c>
       <c r="G113" s="16"/>
     </row>
-    <row r="114" spans="1:7">
-      <c r="A114" s="14"/>
-      <c r="B114" s="14"/>
-      <c r="C114" s="16"/>
-      <c r="D114" s="16"/>
-      <c r="E114" s="16"/>
-      <c r="F114" s="16"/>
+    <row r="114" spans="1:7" ht="24">
+      <c r="A114" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B114" s="21"/>
+      <c r="C114" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D114" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E114" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F114" s="16" t="s">
+        <v>116</v>
+      </c>
       <c r="G114" s="16"/>
     </row>
-    <row r="115" spans="1:7">
-      <c r="A115" s="14"/>
-      <c r="B115" s="14"/>
-      <c r="C115" s="16"/>
-      <c r="D115" s="16"/>
-      <c r="E115" s="16"/>
-      <c r="F115" s="16"/>
+    <row r="115" spans="1:7" ht="24">
+      <c r="A115" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B115" s="21"/>
+      <c r="C115" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D115" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E115" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F115" s="16" t="s">
+        <v>116</v>
+      </c>
       <c r="G115" s="16"/>
     </row>
     <row r="116" spans="1:7">
@@ -5552,6 +5815,69 @@
       <c r="E126" s="16"/>
       <c r="F126" s="16"/>
       <c r="G126" s="16"/>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" s="14"/>
+      <c r="B127" s="14"/>
+      <c r="C127" s="16"/>
+      <c r="D127" s="16"/>
+      <c r="E127" s="16"/>
+      <c r="F127" s="16"/>
+      <c r="G127" s="16"/>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" s="14"/>
+      <c r="B128" s="14"/>
+      <c r="C128" s="16"/>
+      <c r="D128" s="16"/>
+      <c r="E128" s="16"/>
+      <c r="F128" s="16"/>
+      <c r="G128" s="16"/>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" s="14"/>
+      <c r="B129" s="14"/>
+      <c r="C129" s="16"/>
+      <c r="D129" s="16"/>
+      <c r="E129" s="16"/>
+      <c r="F129" s="16"/>
+      <c r="G129" s="16"/>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" s="14"/>
+      <c r="B130" s="14"/>
+      <c r="C130" s="16"/>
+      <c r="D130" s="16"/>
+      <c r="E130" s="16"/>
+      <c r="F130" s="16"/>
+      <c r="G130" s="16"/>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" s="14"/>
+      <c r="B131" s="14"/>
+      <c r="C131" s="16"/>
+      <c r="D131" s="16"/>
+      <c r="E131" s="16"/>
+      <c r="F131" s="16"/>
+      <c r="G131" s="16"/>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" s="14"/>
+      <c r="B132" s="14"/>
+      <c r="C132" s="16"/>
+      <c r="D132" s="16"/>
+      <c r="E132" s="16"/>
+      <c r="F132" s="16"/>
+      <c r="G132" s="16"/>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" s="14"/>
+      <c r="B133" s="14"/>
+      <c r="C133" s="16"/>
+      <c r="D133" s="16"/>
+      <c r="E133" s="16"/>
+      <c r="F133" s="16"/>
+      <c r="G133" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:G3"/>

--- a/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
+++ b/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="376">
   <si>
     <t>测试功能点：查询、插入、更新、分区</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -523,10 +523,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sequoiadb_fault_001_003_001_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>sequoiadb_fault_001_003_002_001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -912,10 +908,6 @@
   </si>
   <si>
     <t>是否做split</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>操作会报失败，自动恢复</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1086,10 +1078,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>操作会报失败，自动恢复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10个线程并发做插入、更新（3.3:6.7）过程中，强杀一个主节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1536,6 +1524,22 @@
   </si>
   <si>
     <t>1.kill -15 三个不同组的备节点; 2.过一定时间恢复故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_fault_001_003_001_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作会报失败，自动恢复，恢复后要求各个组内的数据一致（使用sdbinspect检测）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作有可能（当从该主读时）会报失败，自动恢复，恢复后要求各个组内的数据一致（使用sdbinspect检测）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作会报失败，被强杀的节点自动恢复，恢复后要求各个组内的数据一致（使用sdbinspect检测）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1820,6 +1824,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1838,9 +1845,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1849,74 +1853,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -2262,7 +2198,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2601,10 +2537,10 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="33" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -2618,8 +2554,8 @@
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="33"/>
-      <c r="B3" s="33"/>
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
@@ -2627,8 +2563,8 @@
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="33"/>
-      <c r="B4" s="34"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="35"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
@@ -2636,8 +2572,8 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="33"/>
-      <c r="B5" s="32" t="s">
+      <c r="A5" s="34"/>
+      <c r="B5" s="33" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -2651,8 +2587,8 @@
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="33"/>
-      <c r="B6" s="33"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="5" t="s">
         <v>32</v>
       </c>
@@ -2664,8 +2600,8 @@
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="33"/>
-      <c r="B7" s="34"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -2673,7 +2609,7 @@
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="33"/>
+      <c r="A8" s="34"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -2682,7 +2618,7 @@
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="34"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -2691,10 +2627,10 @@
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="33" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -2708,8 +2644,8 @@
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -2717,8 +2653,8 @@
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="33"/>
-      <c r="B12" s="34"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -2726,8 +2662,8 @@
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="33"/>
-      <c r="B13" s="32" t="s">
+      <c r="A13" s="34"/>
+      <c r="B13" s="33" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -2741,8 +2677,8 @@
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="33"/>
-      <c r="B14" s="33"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
       <c r="C14" s="5" t="s">
         <v>34</v>
       </c>
@@ -2754,8 +2690,8 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="33"/>
-      <c r="B15" s="33"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -2763,8 +2699,8 @@
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="33"/>
-      <c r="B16" s="34"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="35"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -2772,8 +2708,8 @@
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="33"/>
-      <c r="B17" s="32" t="s">
+      <c r="A17" s="34"/>
+      <c r="B17" s="33" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -2787,8 +2723,8 @@
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="33"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="34"/>
       <c r="C18" s="5" t="s">
         <v>14</v>
       </c>
@@ -2800,8 +2736,8 @@
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="33"/>
-      <c r="B19" s="33"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -2809,8 +2745,8 @@
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="34"/>
-      <c r="B20" s="34"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="35"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -2818,10 +2754,10 @@
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="33" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="5" t="s">
@@ -2835,8 +2771,8 @@
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="33"/>
-      <c r="B22" s="33"/>
+      <c r="A22" s="34"/>
+      <c r="B22" s="34"/>
       <c r="C22" s="5" t="s">
         <v>37</v>
       </c>
@@ -2848,8 +2784,8 @@
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="33"/>
-      <c r="B23" s="33"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="34"/>
       <c r="C23" s="5" t="s">
         <v>38</v>
       </c>
@@ -2861,8 +2797,8 @@
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="33"/>
-      <c r="B24" s="33"/>
+      <c r="A24" s="34"/>
+      <c r="B24" s="34"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -2870,8 +2806,8 @@
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="33"/>
-      <c r="B25" s="34"/>
+      <c r="A25" s="34"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -2879,8 +2815,8 @@
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="33"/>
-      <c r="B26" s="32" t="s">
+      <c r="A26" s="34"/>
+      <c r="B26" s="33" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="5" t="s">
@@ -2894,8 +2830,8 @@
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="33"/>
-      <c r="B27" s="33"/>
+      <c r="A27" s="34"/>
+      <c r="B27" s="34"/>
       <c r="C27" s="5" t="s">
         <v>40</v>
       </c>
@@ -2907,8 +2843,8 @@
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="34"/>
-      <c r="B28" s="34"/>
+      <c r="A28" s="35"/>
+      <c r="B28" s="35"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -2916,7 +2852,7 @@
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="32" t="s">
+      <c r="A29" s="33" t="s">
         <v>19</v>
       </c>
       <c r="B29" s="5"/>
@@ -2931,7 +2867,7 @@
       <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="33"/>
+      <c r="A30" s="34"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
         <v>41</v>
@@ -2944,7 +2880,7 @@
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="33"/>
+      <c r="A31" s="34"/>
       <c r="B31" s="3"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -2953,7 +2889,7 @@
       <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="34"/>
+      <c r="A32" s="35"/>
       <c r="B32" s="3"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -3008,13 +2944,13 @@
       <c r="A3" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="36"/>
-      <c r="D3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="38"/>
       <c r="E3" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>43</v>
@@ -3037,10 +2973,10 @@
         <v>47</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>48</v>
@@ -3165,7 +3101,7 @@
         <v>5</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K8" s="3">
         <v>5</v>
@@ -3223,7 +3159,7 @@
         <v>7</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K10" s="3">
         <v>7</v>
@@ -3560,7 +3496,7 @@
         <v>99</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="23" customFormat="1" ht="24">
@@ -3581,7 +3517,7 @@
         <v>99</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="23" customFormat="1" ht="24">
@@ -3602,7 +3538,7 @@
         <v>99</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="23" customFormat="1" ht="24">
@@ -3623,7 +3559,7 @@
         <v>102</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="24">
@@ -3644,7 +3580,7 @@
         <v>100</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="24">
@@ -3665,7 +3601,7 @@
         <v>102</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="24">
@@ -3686,12 +3622,12 @@
         <v>102</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="24">
       <c r="A11" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="20"/>
@@ -3702,128 +3638,128 @@
     </row>
     <row r="12" spans="1:7" ht="48">
       <c r="A12" s="21" t="s">
-        <v>125</v>
+        <v>372</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D12" s="22" t="s">
         <v>98</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>223</v>
+        <v>373</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="48">
       <c r="A13" s="21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D13" s="22" t="s">
         <v>98</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>259</v>
+        <v>144</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="24">
       <c r="A14" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D14" s="22" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="24">
       <c r="A15" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D15" s="22" t="s">
         <v>98</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="24">
       <c r="A16" s="21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D16" s="22" t="s">
         <v>98</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="24">
       <c r="A17" s="21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D17" s="22" t="s">
         <v>98</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="24">
@@ -3832,1476 +3768,1476 @@
       </c>
       <c r="B18" s="21"/>
       <c r="C18" s="22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D18" s="22" t="s">
         <v>98</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="24">
       <c r="A19" s="19" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="20" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="24">
       <c r="A20" s="19" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="20" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="24">
       <c r="A21" s="19" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="20" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="24">
       <c r="A22" s="19" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="20" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="24">
       <c r="A23" s="19" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="20" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="24">
       <c r="A24" s="19" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="20" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="24">
       <c r="A25" s="19" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B25" s="19"/>
       <c r="C25" s="20" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="36">
       <c r="A26" s="21" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="22" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>260</v>
+        <v>373</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="36">
       <c r="A27" s="21" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="22" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="36">
       <c r="A28" s="21" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="22" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="36">
       <c r="A29" s="21" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="72">
       <c r="A30" s="21" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B30" s="21"/>
       <c r="C30" s="22" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G30" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="36">
       <c r="A31" s="21" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B31" s="21"/>
       <c r="C31" s="22" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G31" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="36">
       <c r="A32" s="21" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="22" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="36">
       <c r="A33" s="19" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B33" s="19"/>
       <c r="C33" s="20" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>260</v>
+        <v>373</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="36">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="24">
       <c r="A34" s="19" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="20" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G34" s="20" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="36">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="24">
       <c r="A35" s="19" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B35" s="19"/>
       <c r="C35" s="20" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="36">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="24">
       <c r="A36" s="19" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B36" s="19"/>
       <c r="C36" s="20" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="72">
       <c r="A37" s="19" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B37" s="19"/>
       <c r="C37" s="20" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D37" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="36">
       <c r="A38" s="19" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B38" s="19"/>
       <c r="C38" s="20" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G38" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="36">
       <c r="A39" s="19" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B39" s="19"/>
       <c r="C39" s="20" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="36">
       <c r="A40" s="21" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B40" s="21"/>
       <c r="C40" s="22" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F40" s="22" t="s">
-        <v>260</v>
+        <v>373</v>
       </c>
       <c r="G40" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="36">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="24">
       <c r="A41" s="21" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B41" s="21"/>
       <c r="C41" s="22" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D41" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G41" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="36">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="24">
       <c r="A42" s="21" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B42" s="21"/>
       <c r="C42" s="22" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="36">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="24">
       <c r="A43" s="21" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B43" s="21"/>
       <c r="C43" s="22" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="72">
       <c r="A44" s="21" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="22" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G44" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="36">
       <c r="A45" s="21" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="22" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="36">
       <c r="A46" s="21" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B46" s="21"/>
       <c r="C46" s="22" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G46" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="36">
       <c r="A47" s="19" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B47" s="19"/>
       <c r="C47" s="20" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>260</v>
+        <v>373</v>
       </c>
       <c r="G47" s="20" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="36">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="24">
       <c r="A48" s="19" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B48" s="19"/>
       <c r="C48" s="20" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="F48" s="38" t="s">
-        <v>260</v>
+        <v>138</v>
+      </c>
+      <c r="F48" s="32" t="s">
+        <v>257</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="36">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="24">
       <c r="A49" s="19" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B49" s="19"/>
       <c r="C49" s="20" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G49" s="20" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="36">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="24">
       <c r="A50" s="19" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B50" s="19"/>
       <c r="C50" s="20" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G50" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="36">
       <c r="A51" s="19" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B51" s="19"/>
       <c r="C51" s="20" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="36">
       <c r="A52" s="19" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B52" s="19"/>
       <c r="C52" s="20" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G52" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="36">
       <c r="A53" s="19" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="20" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G53" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="36">
       <c r="A54" s="21" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B54" s="21"/>
       <c r="C54" s="22" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D54" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F54" s="22" t="s">
-        <v>260</v>
+        <v>373</v>
       </c>
       <c r="G54" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="36">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="24">
       <c r="A55" s="21" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B55" s="21"/>
       <c r="C55" s="22" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D55" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G55" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="36">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="24">
       <c r="A56" s="21" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B56" s="21"/>
       <c r="C56" s="22" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D56" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G56" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="36">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="24">
       <c r="A57" s="21" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B57" s="21"/>
       <c r="C57" s="22" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E57" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G57" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="36">
       <c r="A58" s="21" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B58" s="21"/>
       <c r="C58" s="22" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D58" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E58" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G58" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="36">
       <c r="A59" s="21" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B59" s="21"/>
       <c r="C59" s="22" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D59" s="22" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G59" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="36">
       <c r="A60" s="21" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="22" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D60" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G60" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="24">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="36">
       <c r="A61" s="19" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B61" s="19"/>
       <c r="C61" s="20" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D61" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F61" s="20" t="s">
+        <v>374</v>
+      </c>
+      <c r="G61" s="20" t="s">
         <v>237</v>
-      </c>
-      <c r="G61" s="20" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="24">
       <c r="A62" s="19" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B62" s="19"/>
       <c r="C62" s="20" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D62" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="F62" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="E62" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="F62" s="20" t="s">
+      <c r="G62" s="20" t="s">
         <v>237</v>
-      </c>
-      <c r="G62" s="20" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="24">
       <c r="A63" s="19" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B63" s="19"/>
       <c r="C63" s="20" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D63" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F63" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="E63" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="F63" s="20" t="s">
+      <c r="G63" s="20" t="s">
         <v>237</v>
-      </c>
-      <c r="G63" s="20" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="24">
       <c r="A64" s="19" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B64" s="19"/>
       <c r="C64" s="20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D64" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F64" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G64" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="24">
       <c r="A65" s="19" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B65" s="19"/>
       <c r="C65" s="20" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D65" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G65" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="24">
       <c r="A66" s="19" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B66" s="19"/>
       <c r="C66" s="20" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D66" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="E66" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="F66" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="E66" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="F66" s="20" t="s">
-        <v>238</v>
-      </c>
       <c r="G66" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="24">
       <c r="A67" s="19" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B67" s="19"/>
       <c r="C67" s="20" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D67" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G67" s="20" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="24">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="36">
       <c r="A68" s="21" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B68" s="21"/>
       <c r="C68" s="22" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D68" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F68" s="22" t="s">
-        <v>256</v>
+        <v>375</v>
       </c>
       <c r="G68" s="22" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="24">
       <c r="A69" s="21" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B69" s="21"/>
       <c r="C69" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D69" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E69" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F69" s="22" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G69" s="22" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="24">
       <c r="A70" s="21" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B70" s="21"/>
       <c r="C70" s="22" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D70" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E70" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F70" s="22" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G70" s="22" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="24">
       <c r="A71" s="21" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B71" s="21"/>
       <c r="C71" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D71" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E71" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F71" s="22" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G71" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="72">
       <c r="A72" s="21" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B72" s="21"/>
       <c r="C72" s="22" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D72" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F72" s="22" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G72" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="24">
       <c r="A73" s="21" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B73" s="21"/>
       <c r="C73" s="22" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D73" s="22" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E73" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F73" s="22" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G73" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="24">
       <c r="A74" s="21" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B74" s="21"/>
       <c r="C74" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="D74" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="E74" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F74" s="22" t="s">
         <v>255</v>
       </c>
-      <c r="D74" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="E74" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="F74" s="22" t="s">
-        <v>257</v>
-      </c>
       <c r="G74" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="24">
       <c r="A75" s="19" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B75" s="19"/>
       <c r="C75" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D75" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F75" s="20"/>
       <c r="G75" s="20" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="24">
       <c r="A76" s="19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B76" s="19"/>
       <c r="C76" s="20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D76" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F76" s="20"/>
       <c r="G76" s="20" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="24">
       <c r="A77" s="19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B77" s="19"/>
       <c r="C77" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D77" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F77" s="20"/>
       <c r="G77" s="20" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="24">
       <c r="A78" s="19" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B78" s="19"/>
       <c r="C78" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D78" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F78" s="20"/>
       <c r="G78" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="24">
       <c r="A79" s="19" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B79" s="19"/>
       <c r="C79" s="20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D79" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F79" s="20"/>
       <c r="G79" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="24">
       <c r="A80" s="19" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B80" s="19"/>
       <c r="C80" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D80" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E80" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F80" s="20"/>
       <c r="G80" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="24">
       <c r="A81" s="19" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B81" s="19"/>
       <c r="C81" s="20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D81" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F81" s="20"/>
       <c r="G81" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="24">
       <c r="A82" s="21" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B82" s="21"/>
       <c r="C82" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D82" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E82" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F82" s="22"/>
       <c r="G82" s="22" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="24">
       <c r="A83" s="21" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B83" s="21"/>
       <c r="C83" s="22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D83" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E83" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F83" s="22"/>
       <c r="G83" s="22" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="24">
       <c r="A84" s="21" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B84" s="21"/>
       <c r="C84" s="22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D84" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E84" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F84" s="22"/>
       <c r="G84" s="22" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="24">
       <c r="A85" s="21" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B85" s="21"/>
       <c r="C85" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D85" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E85" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F85" s="22"/>
       <c r="G85" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="24">
       <c r="A86" s="21" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B86" s="21"/>
       <c r="C86" s="22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D86" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E86" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F86" s="22"/>
       <c r="G86" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="24">
       <c r="A87" s="21" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B87" s="21"/>
       <c r="C87" s="22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D87" s="22" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E87" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F87" s="22"/>
       <c r="G87" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="24">
       <c r="A88" s="21" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B88" s="21"/>
       <c r="C88" s="22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D88" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E88" s="22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F88" s="22"/>
       <c r="G88" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="24">
       <c r="A89" s="19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B89" s="19"/>
       <c r="C89" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D89" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F89" s="20" t="s">
         <v>29</v>
@@ -5310,17 +5246,17 @@
     </row>
     <row r="90" spans="1:7" ht="24">
       <c r="A90" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B90" s="19"/>
       <c r="C90" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D90" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E90" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F90" s="20" t="s">
         <v>29</v>
@@ -5329,17 +5265,17 @@
     </row>
     <row r="91" spans="1:7" ht="24">
       <c r="A91" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B91" s="19"/>
       <c r="C91" s="20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D91" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F91" s="20" t="s">
         <v>29</v>
@@ -5348,17 +5284,17 @@
     </row>
     <row r="92" spans="1:7" ht="24">
       <c r="A92" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B92" s="19"/>
       <c r="C92" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D92" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F92" s="20" t="s">
         <v>102</v>
@@ -5367,17 +5303,17 @@
     </row>
     <row r="93" spans="1:7" ht="24">
       <c r="A93" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B93" s="19"/>
       <c r="C93" s="20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D93" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E93" s="20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F93" s="20" t="s">
         <v>102</v>
@@ -5386,17 +5322,17 @@
     </row>
     <row r="94" spans="1:7" ht="24">
       <c r="A94" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B94" s="19"/>
       <c r="C94" s="20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D94" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E94" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F94" s="20" t="s">
         <v>102</v>
@@ -5405,17 +5341,17 @@
     </row>
     <row r="95" spans="1:7" ht="24">
       <c r="A95" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B95" s="19"/>
       <c r="C95" s="20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D95" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F95" s="20" t="s">
         <v>102</v>
@@ -5424,7 +5360,7 @@
     </row>
     <row r="96" spans="1:7" ht="24">
       <c r="A96" s="25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B96" s="14"/>
       <c r="C96" s="16"/>
@@ -5435,7 +5371,7 @@
     </row>
     <row r="97" spans="1:7" ht="24">
       <c r="A97" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B97" s="14"/>
       <c r="C97" s="16"/>
@@ -5446,74 +5382,74 @@
     </row>
     <row r="98" spans="1:7" ht="24">
       <c r="A98" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B98" s="19"/>
       <c r="C98" s="20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D98" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E98" s="20" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F98" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G98" s="20"/>
     </row>
     <row r="99" spans="1:7" ht="24">
       <c r="A99" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B99" s="19"/>
       <c r="C99" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D99" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E99" s="20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F99" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G99" s="20"/>
     </row>
     <row r="100" spans="1:7" ht="24">
       <c r="A100" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B100" s="19"/>
       <c r="C100" s="20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D100" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E100" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F100" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G100" s="20"/>
     </row>
     <row r="101" spans="1:7" ht="24">
       <c r="A101" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B101" s="19"/>
       <c r="C101" s="20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D101" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F101" s="20" t="s">
         <v>101</v>
@@ -5522,36 +5458,36 @@
     </row>
     <row r="102" spans="1:7" ht="24">
       <c r="A102" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B102" s="19"/>
       <c r="C102" s="20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D102" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E102" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F102" s="20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G102" s="20"/>
     </row>
     <row r="103" spans="1:7" ht="24">
       <c r="A103" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B103" s="19"/>
       <c r="C103" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D103" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E103" s="20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F103" s="20" t="s">
         <v>101</v>
@@ -5560,17 +5496,17 @@
     </row>
     <row r="104" spans="1:7" ht="24">
       <c r="A104" s="19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B104" s="19"/>
       <c r="C104" s="20" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D104" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E104" s="20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F104" s="20" t="s">
         <v>101</v>
@@ -5579,7 +5515,7 @@
     </row>
     <row r="105" spans="1:7" ht="24">
       <c r="A105" s="25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B105" s="14"/>
       <c r="C105" s="16"/>
@@ -5590,7 +5526,7 @@
     </row>
     <row r="106" spans="1:7" ht="24">
       <c r="A106" s="27" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B106" s="14"/>
       <c r="C106" s="16"/>
@@ -5601,17 +5537,17 @@
     </row>
     <row r="107" spans="1:7" ht="24">
       <c r="A107" s="21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B107" s="21"/>
       <c r="C107" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D107" s="16" t="s">
         <v>98</v>
       </c>
       <c r="E107" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F107" s="16" t="s">
         <v>110</v>
@@ -5902,16 +5838,16 @@
     <row r="1" spans="1:4">
       <c r="A1" s="28"/>
       <c r="B1" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1" s="29" t="s">
         <v>201</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>202</v>
       </c>
       <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="28" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -5919,7 +5855,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="28" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -5933,10 +5869,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="29" t="s">
         <v>205</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>206</v>
       </c>
       <c r="C5" s="29"/>
       <c r="D5" s="28"/>
@@ -5949,72 +5885,72 @@
     </row>
     <row r="7" spans="1:4" ht="81">
       <c r="A7" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="C7" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="D7" s="28" t="s">
         <v>209</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="81">
       <c r="A8" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" s="28" t="s">
         <v>211</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="D9" s="28" t="s">
         <v>213</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="54">
       <c r="A10" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="D10" s="28" t="s">
         <v>215</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="D11" s="28" t="s">
         <v>217</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -6043,7 +5979,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="28" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B16" s="29"/>
       <c r="C16" s="29"/>
@@ -6051,12 +5987,12 @@
     </row>
     <row r="28" spans="1:1" ht="27">
       <c r="A28" s="31" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="31" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
+++ b/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="总体描述" sheetId="1" r:id="rId1"/>
@@ -1853,6 +1853,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -2198,7 +2266,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>

--- a/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
+++ b/internal_doc/05.测试设计/sequoiadb/sequoiadb故障注入测试1.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="总体描述" sheetId="1" r:id="rId1"/>
@@ -149,10 +149,6 @@
   </si>
   <si>
     <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进程异常 kill -9</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1540,6 +1536,10 @@
   </si>
   <si>
     <t>操作会报失败，被强杀的节点自动恢复，恢复后要求各个组内的数据一致（使用sdbinspect检测）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进程异常 kill -9</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2645,7 +2645,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>21</v>
@@ -2658,7 +2658,7 @@
       <c r="A6" s="34"/>
       <c r="B6" s="34"/>
       <c r="C6" s="5" t="s">
-        <v>32</v>
+        <v>375</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>21</v>
@@ -2748,7 +2748,7 @@
       <c r="A14" s="34"/>
       <c r="B14" s="34"/>
       <c r="C14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>23</v>
@@ -2781,7 +2781,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>25</v>
@@ -2829,7 +2829,7 @@
         <v>10</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>27</v>
@@ -2842,7 +2842,7 @@
       <c r="A22" s="34"/>
       <c r="B22" s="34"/>
       <c r="C22" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>28</v>
@@ -2855,7 +2855,7 @@
       <c r="A23" s="34"/>
       <c r="B23" s="34"/>
       <c r="C23" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>28</v>
@@ -2888,7 +2888,7 @@
         <v>18</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>29</v>
@@ -2901,7 +2901,7 @@
       <c r="A27" s="34"/>
       <c r="B27" s="34"/>
       <c r="C27" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>29</v>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>30</v>
@@ -2938,7 +2938,7 @@
       <c r="A30" s="34"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>30</v>
@@ -3005,32 +3005,32 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="D1" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="36" t="s">
         <v>43</v>
-      </c>
-      <c r="B3" s="36" t="s">
-        <v>44</v>
       </c>
       <c r="C3" s="37"/>
       <c r="D3" s="38"/>
       <c r="E3" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K3" s="10" t="s">
         <v>31</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -3038,28 +3038,28 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="H4" s="3">
         <v>1</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K4" s="3">
         <v>1</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -3067,28 +3067,28 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="H5" s="3">
         <v>2</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K5" s="3">
         <v>2</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -3096,28 +3096,28 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>47</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>48</v>
       </c>
       <c r="H6" s="3">
         <v>3</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K6" s="3">
         <v>3</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3125,28 +3125,28 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="H7" s="3">
         <v>4</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K7" s="3">
         <v>4</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -3154,28 +3154,28 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H8" s="3">
         <v>5</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K8" s="3">
         <v>5</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -3183,28 +3183,28 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H9" s="3">
         <v>6</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K9" s="3">
         <v>6</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -3212,28 +3212,28 @@
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H10" s="3">
         <v>7</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K10" s="3">
         <v>7</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -3241,22 +3241,22 @@
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H11" s="3">
         <v>8</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -3264,16 +3264,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -3281,16 +3281,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C13" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>51</v>
-      </c>
       <c r="E13" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -3298,28 +3298,28 @@
         <v>11</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H14" s="3">
         <v>9</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K14" s="3">
         <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -3327,28 +3327,28 @@
         <v>12</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H15" s="3">
         <v>10</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K15" s="3">
         <v>9</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -3356,22 +3356,22 @@
         <v>13</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H16" s="3">
         <v>11</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -3379,22 +3379,22 @@
         <v>14</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H17" s="3">
         <v>12</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -3402,22 +3402,22 @@
         <v>15</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H18" s="3">
         <v>13</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -3425,16 +3425,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -3454,13 +3454,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K21" s="3">
         <v>10</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -3468,13 +3468,13 @@
         <v>15</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K22" s="3">
         <v>11</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -3482,15 +3482,15 @@
         <v>12</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -3520,182 +3520,182 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>76</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A4" s="21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4" s="21"/>
       <c r="C4" s="22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D4" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="E4" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>99</v>
-      </c>
       <c r="G4" s="21" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A5" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D5" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="E5" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>99</v>
-      </c>
       <c r="G5" s="21" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A6" s="21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D6" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>99</v>
-      </c>
       <c r="G6" s="21" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="23" customFormat="1" ht="24">
       <c r="A7" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B7" s="21"/>
       <c r="C7" s="22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="24">
       <c r="A8" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B8" s="21"/>
       <c r="C8" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="24">
       <c r="A9" s="21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B9" s="21"/>
       <c r="C9" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="24">
       <c r="A10" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="22" t="s">
-        <v>98</v>
-      </c>
       <c r="E10" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="24">
       <c r="A11" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="20"/>
@@ -3706,1606 +3706,1606 @@
     </row>
     <row r="12" spans="1:7" ht="48">
       <c r="A12" s="21" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="48">
       <c r="A13" s="21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="24">
       <c r="A14" s="21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="24">
       <c r="A15" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="24">
       <c r="A16" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="24">
       <c r="A17" s="21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="24">
       <c r="A18" s="21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B18" s="21"/>
       <c r="C18" s="22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="24">
       <c r="A19" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="20" t="s">
+        <v>354</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="E19" s="20" t="s">
         <v>355</v>
       </c>
-      <c r="D19" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="E19" s="20" t="s">
+      <c r="F19" s="20" t="s">
         <v>356</v>
       </c>
-      <c r="F19" s="20" t="s">
-        <v>357</v>
-      </c>
       <c r="G19" s="19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="24">
       <c r="A20" s="19" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="20" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="24">
       <c r="A21" s="19" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="20" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="24">
       <c r="A22" s="19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="20" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E22" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="F22" s="20" t="s">
         <v>363</v>
       </c>
-      <c r="F22" s="20" t="s">
-        <v>364</v>
-      </c>
       <c r="G22" s="19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="24">
       <c r="A23" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="20" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E23" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="F23" s="20" t="s">
         <v>366</v>
       </c>
-      <c r="F23" s="20" t="s">
-        <v>367</v>
-      </c>
       <c r="G23" s="19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="24">
       <c r="A24" s="19" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="24">
       <c r="A25" s="19" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B25" s="19"/>
       <c r="C25" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="36">
       <c r="A26" s="21" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="22" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="36">
       <c r="A27" s="21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="22" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="36">
       <c r="A28" s="21" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="36">
       <c r="A29" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="72">
       <c r="A30" s="21" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B30" s="21"/>
       <c r="C30" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G30" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="36">
       <c r="A31" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B31" s="21"/>
       <c r="C31" s="22" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G31" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="36">
       <c r="A32" s="21" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="22" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="36">
       <c r="A33" s="19" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B33" s="19"/>
       <c r="C33" s="20" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="24">
       <c r="A34" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G34" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="24">
       <c r="A35" s="19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B35" s="19"/>
       <c r="C35" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="24">
       <c r="A36" s="19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B36" s="19"/>
       <c r="C36" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="72">
       <c r="A37" s="19" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B37" s="19"/>
       <c r="C37" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D37" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="36">
       <c r="A38" s="19" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B38" s="19"/>
       <c r="C38" s="20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G38" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="36">
       <c r="A39" s="19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B39" s="19"/>
       <c r="C39" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="F39" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="D39" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>265</v>
-      </c>
       <c r="G39" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="36">
       <c r="A40" s="21" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B40" s="21"/>
       <c r="C40" s="22" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F40" s="22" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G40" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="24">
       <c r="A41" s="21" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B41" s="21"/>
       <c r="C41" s="22" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D41" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G41" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="24">
       <c r="A42" s="21" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B42" s="21"/>
       <c r="C42" s="22" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="24">
       <c r="A43" s="21" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B43" s="21"/>
       <c r="C43" s="22" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="72">
       <c r="A44" s="21" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G44" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="36">
       <c r="A45" s="21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="22" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="36">
       <c r="A46" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B46" s="21"/>
       <c r="C46" s="22" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G46" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="36">
       <c r="A47" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B47" s="19"/>
       <c r="C47" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G47" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="24">
       <c r="A48" s="19" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B48" s="19"/>
       <c r="C48" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F48" s="32" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="24">
       <c r="A49" s="19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B49" s="19"/>
       <c r="C49" s="20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G49" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="24">
       <c r="A50" s="19" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B50" s="19"/>
       <c r="C50" s="20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G50" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="36">
       <c r="A51" s="19" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B51" s="19"/>
       <c r="C51" s="20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="36">
       <c r="A52" s="19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B52" s="19"/>
       <c r="C52" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G52" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="36">
       <c r="A53" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G53" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="36">
       <c r="A54" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B54" s="21"/>
       <c r="C54" s="22" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D54" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F54" s="22" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G54" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="24">
       <c r="A55" s="21" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B55" s="21"/>
       <c r="C55" s="22" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D55" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G55" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="24">
       <c r="A56" s="21" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B56" s="21"/>
       <c r="C56" s="22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D56" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G56" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="24">
       <c r="A57" s="21" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B57" s="21"/>
       <c r="C57" s="22" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E57" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G57" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="36">
       <c r="A58" s="21" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B58" s="21"/>
       <c r="C58" s="22" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D58" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E58" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G58" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="36">
       <c r="A59" s="21" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B59" s="21"/>
       <c r="C59" s="22" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D59" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G59" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="36">
       <c r="A60" s="21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D60" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G60" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="36">
       <c r="A61" s="19" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B61" s="19"/>
       <c r="C61" s="20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D61" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F61" s="20" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="24">
       <c r="A62" s="19" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B62" s="19"/>
       <c r="C62" s="20" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D62" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E62" s="20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F62" s="20" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G62" s="20" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="24">
       <c r="A63" s="19" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B63" s="19"/>
       <c r="C63" s="20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D63" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G63" s="20" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="24">
       <c r="A64" s="19" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B64" s="19"/>
       <c r="C64" s="20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D64" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F64" s="20" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G64" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="24">
       <c r="A65" s="19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B65" s="19"/>
       <c r="C65" s="20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D65" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G65" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="24">
       <c r="A66" s="19" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B66" s="19"/>
       <c r="C66" s="20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D66" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E66" s="20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F66" s="20" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G66" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="24">
       <c r="A67" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B67" s="19"/>
       <c r="C67" s="20" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D67" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G67" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="36">
       <c r="A68" s="21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B68" s="21"/>
       <c r="C68" s="22" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D68" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F68" s="22" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G68" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="24">
       <c r="A69" s="21" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B69" s="21"/>
       <c r="C69" s="22" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D69" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E69" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F69" s="22" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G69" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="24">
       <c r="A70" s="21" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B70" s="21"/>
       <c r="C70" s="22" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D70" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E70" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F70" s="22" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G70" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="24">
       <c r="A71" s="21" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B71" s="21"/>
       <c r="C71" s="22" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D71" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E71" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F71" s="22" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G71" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="72">
       <c r="A72" s="21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B72" s="21"/>
       <c r="C72" s="22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D72" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F72" s="22" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G72" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="24">
       <c r="A73" s="21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B73" s="21"/>
       <c r="C73" s="22" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D73" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E73" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F73" s="22" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G73" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="24">
       <c r="A74" s="21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B74" s="21"/>
       <c r="C74" s="22" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D74" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E74" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F74" s="22" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G74" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="24">
       <c r="A75" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B75" s="19"/>
       <c r="C75" s="20" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D75" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F75" s="20"/>
       <c r="G75" s="20" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="24">
       <c r="A76" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B76" s="19"/>
       <c r="C76" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D76" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F76" s="20"/>
       <c r="G76" s="20" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="24">
       <c r="A77" s="19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B77" s="19"/>
       <c r="C77" s="20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D77" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F77" s="20"/>
       <c r="G77" s="20" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="24">
       <c r="A78" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B78" s="19"/>
       <c r="C78" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D78" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F78" s="20"/>
       <c r="G78" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="24">
       <c r="A79" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B79" s="19"/>
       <c r="C79" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D79" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F79" s="20"/>
       <c r="G79" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="24">
       <c r="A80" s="19" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B80" s="19"/>
       <c r="C80" s="20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D80" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E80" s="20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F80" s="20"/>
       <c r="G80" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="24">
       <c r="A81" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B81" s="19"/>
       <c r="C81" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D81" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F81" s="20"/>
       <c r="G81" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="24">
       <c r="A82" s="21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B82" s="21"/>
       <c r="C82" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D82" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E82" s="22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F82" s="22"/>
       <c r="G82" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="24">
       <c r="A83" s="21" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B83" s="21"/>
       <c r="C83" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D83" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E83" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F83" s="22"/>
       <c r="G83" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="24">
       <c r="A84" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B84" s="21"/>
       <c r="C84" s="22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D84" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E84" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F84" s="22"/>
       <c r="G84" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="24">
       <c r="A85" s="21" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B85" s="21"/>
       <c r="C85" s="22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D85" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E85" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F85" s="22"/>
       <c r="G85" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="24">
       <c r="A86" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B86" s="21"/>
       <c r="C86" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D86" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E86" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F86" s="22"/>
       <c r="G86" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="24">
       <c r="A87" s="21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B87" s="21"/>
       <c r="C87" s="22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D87" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E87" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F87" s="22"/>
       <c r="G87" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="24">
       <c r="A88" s="21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B88" s="21"/>
       <c r="C88" s="22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D88" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E88" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F88" s="22"/>
       <c r="G88" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="24">
       <c r="A89" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B89" s="19"/>
       <c r="C89" s="20" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D89" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F89" s="20" t="s">
         <v>29</v>
@@ -5314,17 +5314,17 @@
     </row>
     <row r="90" spans="1:7" ht="24">
       <c r="A90" s="19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B90" s="19"/>
       <c r="C90" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D90" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E90" s="20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F90" s="20" t="s">
         <v>29</v>
@@ -5333,17 +5333,17 @@
     </row>
     <row r="91" spans="1:7" ht="24">
       <c r="A91" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B91" s="19"/>
       <c r="C91" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D91" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F91" s="20" t="s">
         <v>29</v>
@@ -5352,83 +5352,83 @@
     </row>
     <row r="92" spans="1:7" ht="24">
       <c r="A92" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B92" s="19"/>
       <c r="C92" s="20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D92" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F92" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G92" s="20"/>
     </row>
     <row r="93" spans="1:7" ht="24">
       <c r="A93" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B93" s="19"/>
       <c r="C93" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D93" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E93" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F93" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G93" s="20"/>
     </row>
     <row r="94" spans="1:7" ht="24">
       <c r="A94" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B94" s="19"/>
       <c r="C94" s="20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D94" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E94" s="20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F94" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G94" s="20"/>
     </row>
     <row r="95" spans="1:7" ht="24">
       <c r="A95" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B95" s="19"/>
       <c r="C95" s="20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D95" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F95" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G95" s="20"/>
     </row>
     <row r="96" spans="1:7" ht="24">
       <c r="A96" s="25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B96" s="14"/>
       <c r="C96" s="16"/>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="97" spans="1:7" ht="24">
       <c r="A97" s="26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B97" s="14"/>
       <c r="C97" s="16"/>
@@ -5450,140 +5450,140 @@
     </row>
     <row r="98" spans="1:7" ht="24">
       <c r="A98" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B98" s="19"/>
       <c r="C98" s="20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D98" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E98" s="20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F98" s="20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G98" s="20"/>
     </row>
     <row r="99" spans="1:7" ht="24">
       <c r="A99" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B99" s="19"/>
       <c r="C99" s="20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D99" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E99" s="20" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F99" s="20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G99" s="20"/>
     </row>
     <row r="100" spans="1:7" ht="24">
       <c r="A100" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B100" s="19"/>
       <c r="C100" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D100" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E100" s="20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F100" s="20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G100" s="20"/>
     </row>
     <row r="101" spans="1:7" ht="24">
       <c r="A101" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B101" s="19"/>
       <c r="C101" s="20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D101" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F101" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G101" s="20"/>
     </row>
     <row r="102" spans="1:7" ht="24">
       <c r="A102" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B102" s="19"/>
       <c r="C102" s="20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D102" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E102" s="20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F102" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G102" s="20"/>
     </row>
     <row r="103" spans="1:7" ht="24">
       <c r="A103" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B103" s="19"/>
       <c r="C103" s="20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D103" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E103" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F103" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G103" s="20"/>
     </row>
     <row r="104" spans="1:7" ht="24">
       <c r="A104" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B104" s="19"/>
       <c r="C104" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D104" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E104" s="20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F104" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G104" s="20"/>
     </row>
     <row r="105" spans="1:7" ht="24">
       <c r="A105" s="25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B105" s="14"/>
       <c r="C105" s="16"/>
@@ -5594,7 +5594,7 @@
     </row>
     <row r="106" spans="1:7" ht="24">
       <c r="A106" s="27" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B106" s="14"/>
       <c r="C106" s="16"/>
@@ -5605,20 +5605,20 @@
     </row>
     <row r="107" spans="1:7" ht="24">
       <c r="A107" s="21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B107" s="21"/>
       <c r="C107" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="D107" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E107" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="D107" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E107" s="16" t="s">
-        <v>199</v>
-      </c>
       <c r="F107" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G107" s="16"/>
     </row>
@@ -5666,58 +5666,58 @@
     </row>
     <row r="113" spans="1:7" ht="24">
       <c r="A113" s="21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B113" s="21"/>
       <c r="C113" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D113" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E113" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="D113" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E113" s="16" t="s">
+      <c r="F113" s="16" t="s">
         <v>115</v>
-      </c>
-      <c r="F113" s="16" t="s">
-        <v>116</v>
       </c>
       <c r="G113" s="16"/>
     </row>
     <row r="114" spans="1:7" ht="24">
       <c r="A114" s="21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B114" s="21"/>
       <c r="C114" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D114" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E114" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F114" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G114" s="16"/>
     </row>
     <row r="115" spans="1:7" ht="24">
       <c r="A115" s="21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B115" s="21"/>
       <c r="C115" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D115" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E115" s="16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F115" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G115" s="16"/>
     </row>
@@ -5906,16 +5906,16 @@
     <row r="1" spans="1:4">
       <c r="A1" s="28"/>
       <c r="B1" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1" s="29" t="s">
         <v>200</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>201</v>
       </c>
       <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="28" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -5923,7 +5923,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="28" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -5937,10 +5937,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5" s="29" t="s">
         <v>204</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>205</v>
       </c>
       <c r="C5" s="29"/>
       <c r="D5" s="28"/>
@@ -5953,72 +5953,72 @@
     </row>
     <row r="7" spans="1:4" ht="81">
       <c r="A7" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="C7" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="D7" s="28" t="s">
         <v>208</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="81">
       <c r="A8" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="D8" s="28" t="s">
         <v>210</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="D9" s="28" t="s">
         <v>212</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="54">
       <c r="A10" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="D10" s="28" t="s">
         <v>214</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="D11" s="28" t="s">
         <v>216</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -6047,7 +6047,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="28" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B16" s="29"/>
       <c r="C16" s="29"/>
@@ -6055,12 +6055,12 @@
     </row>
     <row r="28" spans="1:1" ht="27">
       <c r="A28" s="31" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="31" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
